--- a/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="28810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18431"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/asset/assetImport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\asset\assetImport\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20220"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="38400" windowHeight="20220"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <definedName name="资金来源">设备分类!$D$2:$D$6</definedName>
     <definedName name="风险等级">设备分类!$E$2:$E$6</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -100,10 +100,34 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Tang, Quan (GE Healthcare)</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>tie:each(items="assetList", var="asset", length="1" allowAdd="True")</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
     <author>Luan, Da (GE Healthcare)</author>
   </authors>
   <commentList>
-    <comment ref="E4" authorId="0">
+    <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -494,9 +518,6 @@
       <t>设备型号</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SBBH0001</t>
   </si>
   <si>
     <t>XXXX</t>
@@ -2433,11 +2454,14 @@
   <si>
     <t>v2.0</t>
   </si>
+  <si>
+    <t>${asset.departNum}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
@@ -2446,7 +2470,7 @@
     <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00;[$¥-804]\-#,##0.00"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.14993743705557422"/>
@@ -2731,6 +2755,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3539,174 +3570,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4210,6 +4073,174 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-4.9989318521683403E-2"/>
@@ -4310,7 +4341,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory Pick List worksheet"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4407,7 +4438,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4504,7 +4535,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4581,64 +4612,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="106" totalsRowDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="78" totalsRowDxfId="77">
   <sortState ref="A3:D8">
     <sortCondition ref="B2:B8"/>
   </sortState>
   <tableColumns count="53">
-    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="104" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="76" dataCellStyle="Table details left aligned"/>
     <tableColumn id="2" name="设备名称" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="11" name="设备别名" dataDxfId="103" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="11" name="设备别名" dataDxfId="75" dataCellStyle="Table details left aligned"/>
     <tableColumn id="3" name="维修负责人" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="32" name="维修负责人2" dataDxfId="102" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="32" name="维修负责人2" dataDxfId="74" dataCellStyle="Table details left aligned"/>
     <tableColumn id="50" name="维修负责人3" dataCellStyle="Table details left aligned"/>
     <tableColumn id="5" name="使用科室" dataCellStyle="Table details left aligned"/>
     <tableColumn id="8" name="制造商" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="101" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="52" name="设备标准名称" dataDxfId="100" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="35" name="注册证号" dataDxfId="99" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="7" name="供应商" dataDxfId="98" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="23" name="医疗器械分类" dataDxfId="97" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="4" name="医疗器械子分类" dataDxfId="96" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="24" name="设备分类" dataDxfId="95" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="25" name="功能等级" dataDxfId="94" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="53" name="维修类型" dataDxfId="93" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="26" name="设备型号" dataDxfId="92" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="30" name="制造商序列号" dataDxfId="91" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="90" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="41" name="2010国家编码" dataDxfId="89" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="29" name="资产编号" dataDxfId="88" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="28" name="条码" dataDxfId="87" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="27" name="IT系统编号" dataDxfId="86" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="73" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="52" name="设备标准名称" dataDxfId="72" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="35" name="注册证号" dataDxfId="71" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="7" name="供应商" dataDxfId="70" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="23" name="医疗器械分类" dataDxfId="69" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="4" name="医疗器械子分类" dataDxfId="68" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="24" name="设备分类" dataDxfId="67" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="25" name="功能等级" dataDxfId="66" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="53" name="维修类型" dataDxfId="65" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="26" name="设备型号" dataDxfId="64" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="30" name="制造商序列号" dataDxfId="63" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="62" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="41" name="2010国家编码" dataDxfId="61" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="29" name="资产编号" dataDxfId="60" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="28" name="条码" dataDxfId="59" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="27" name="IT系统编号" dataDxfId="58" dataCellStyle="Table details right aligned"/>
     <tableColumn id="10" name="采购价格" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="13" name="最终残值" dataDxfId="85" totalsRowDxfId="84" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="14" name="折旧算法" dataDxfId="83" totalsRowDxfId="82" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="15" name="使用年限" dataDxfId="81" totalsRowDxfId="80" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="16" name="出厂日期" dataDxfId="79" totalsRowDxfId="78" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="17" name="采购日期" dataDxfId="77" totalsRowDxfId="76" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="18" name="到货日期" dataDxfId="75" totalsRowDxfId="74" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="19" name="启用日期" dataDxfId="73" totalsRowDxfId="72" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="39" name="质保日期" dataDxfId="71" totalsRowDxfId="70" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="20" name="维保截止日期" dataDxfId="69" totalsRowDxfId="68" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="21" name="报废日期" dataDxfId="67" totalsRowDxfId="66" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="22" name="上次维护日期" dataDxfId="65" totalsRowDxfId="64" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="6" name="上次计量日期" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="12" name="上次质检日期" dataDxfId="61" totalsRowDxfId="60" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="31" name="维护商" dataDxfId="59" totalsRowDxfId="58" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="33" name="维护商电话" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="34" name="二维码" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="36" name="安装位置编码" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="37" name="安装位置" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="38" name="使用责任人" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="40" name="备注" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="42" name="用途分类" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="43" name="资金来源" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="44" name="风险等级" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="45" name="计量等级" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="46" name="计量项目类别" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="47" name="是否急救设备" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="48" name="是否进口设备" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="49" name="当前状态" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="13" name="最终残值" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="14" name="折旧算法" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="15" name="使用年限" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="16" name="出厂日期" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="17" name="采购日期" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="18" name="到货日期" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="19" name="启用日期" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="39" name="质保日期" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="20" name="维保截止日期" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="21" name="报废日期" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="22" name="上次维护日期" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="6" name="上次计量日期" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="12" name="上次质检日期" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="31" name="维护商" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="33" name="维护商电话" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="34" name="二维码" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="36" name="安装位置编码" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="37" name="安装位置" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="38" name="使用责任人" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="40" name="备注" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="42" name="用途分类" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="43" name="资金来源" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="44" name="风险等级" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="45" name="计量等级" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="46" name="计量项目类别" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="47" name="是否急救设备" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="48" name="是否进口设备" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="49" name="当前状态" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Table details right aligned"/>
   </tableColumns>
   <tableStyleInfo name="Warehouse Inventory" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4892,63 +4923,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtInventoryList" enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="shtInventoryList">
     <tabColor theme="4"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BA100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="105" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" style="105" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="105" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="105" customWidth="1"/>
-    <col min="11" max="11" width="9.1640625" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" style="113" customWidth="1"/>
-    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" style="113" customWidth="1"/>
+    <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="10" style="105" customWidth="1"/>
-    <col min="18" max="19" width="10.1640625" customWidth="1"/>
-    <col min="20" max="20" width="19.1640625" customWidth="1"/>
-    <col min="21" max="21" width="19.1640625" style="105" customWidth="1"/>
+    <col min="18" max="19" width="10.109375" customWidth="1"/>
+    <col min="20" max="20" width="19.109375" customWidth="1"/>
+    <col min="21" max="21" width="19.109375" style="105" customWidth="1"/>
     <col min="22" max="22" width="14.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.1640625" customWidth="1"/>
+    <col min="23" max="24" width="10.109375" customWidth="1"/>
     <col min="25" max="25" width="13.6640625" customWidth="1"/>
-    <col min="26" max="26" width="17.5" customWidth="1"/>
-    <col min="27" max="27" width="14.5" customWidth="1"/>
-    <col min="28" max="28" width="11.1640625" customWidth="1"/>
+    <col min="26" max="26" width="17.44140625" customWidth="1"/>
+    <col min="27" max="27" width="14.44140625" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
     <col min="29" max="29" width="9" customWidth="1"/>
-    <col min="30" max="30" width="11.5" customWidth="1"/>
-    <col min="31" max="31" width="10.1640625" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
-    <col min="33" max="33" width="11.5" style="105" customWidth="1"/>
-    <col min="34" max="34" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" customWidth="1"/>
+    <col min="31" max="31" width="10.109375" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" customWidth="1"/>
+    <col min="33" max="33" width="11.44140625" style="105" customWidth="1"/>
+    <col min="34" max="34" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="13.33203125" customWidth="1"/>
     <col min="36" max="36" width="14.6640625" customWidth="1"/>
-    <col min="37" max="37" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="12.44140625" customWidth="1"/>
     <col min="38" max="38" width="12.6640625" customWidth="1"/>
     <col min="39" max="40" width="12.33203125" style="113" customWidth="1"/>
-    <col min="41" max="41" width="16.1640625" style="113" customWidth="1"/>
-    <col min="42" max="42" width="12.83203125" style="113" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.1640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.109375" style="113" customWidth="1"/>
+    <col min="42" max="42" width="12.77734375" style="113" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" style="113" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="11.6640625" customWidth="1"/>
-    <col min="51" max="52" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:53" ht="27">
       <c r="A1" s="24" t="s">
         <v>43</v>
       </c>
@@ -4957,7 +4988,7 @@
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E1" s="124"/>
       <c r="F1" s="124"/>
@@ -4968,7 +4999,7 @@
       <c r="K1" s="124"/>
       <c r="L1" s="124"/>
     </row>
-    <row r="2" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:53" ht="15.75">
       <c r="A2" s="25" t="s">
         <v>44</v>
       </c>
@@ -4976,7 +5007,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D2" s="124"/>
       <c r="E2" s="124"/>
@@ -4988,7 +5019,7 @@
       <c r="K2" s="124"/>
       <c r="L2" s="124"/>
     </row>
-    <row r="3" spans="1:53" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:53" ht="33.75" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -5045,7 +5076,7 @@
       <c r="AZ3" s="1"/>
       <c r="BA3" s="106"/>
     </row>
-    <row r="4" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:53" ht="15.75">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5058,7 +5089,7 @@
       <c r="F4" s="11"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:53" ht="20" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:53" ht="21">
       <c r="A5" s="120">
         <f>COUNTA('Asset List'!$B$7:$B$100)</f>
         <v>1</v>
@@ -5072,7 +5103,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
     </row>
-    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1">
       <c r="A6" s="30" t="s">
         <v>45</v>
       </c>
@@ -5086,43 +5117,43 @@
         <v>111</v>
       </c>
       <c r="E6" s="118" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K6" s="31" t="s">
         <v>112</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M6" s="30" t="s">
+        <v>520</v>
+      </c>
+      <c r="N6" s="93" t="s">
         <v>521</v>
       </c>
-      <c r="N6" s="93" t="s">
-        <v>522</v>
-      </c>
       <c r="O6" s="93" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>36</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R6" s="30" t="s">
         <v>113</v>
@@ -5134,7 +5165,7 @@
         <v>86</v>
       </c>
       <c r="U6" s="30" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>38</v>
@@ -5158,7 +5189,7 @@
         <v>21</v>
       </c>
       <c r="AC6" s="30" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>23</v>
@@ -5167,10 +5198,10 @@
         <v>24</v>
       </c>
       <c r="AF6" s="93" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG6" s="93" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AH6" s="30" t="s">
         <v>26</v>
@@ -5194,90 +5225,90 @@
         <v>32</v>
       </c>
       <c r="AO6" s="32" t="s">
+        <v>497</v>
+      </c>
+      <c r="AP6" s="32" t="s">
         <v>498</v>
       </c>
-      <c r="AP6" s="32" t="s">
+      <c r="AQ6" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="AQ6" s="32" t="s">
+      <c r="AR6" s="32" t="s">
         <v>500</v>
       </c>
-      <c r="AR6" s="32" t="s">
+      <c r="AS6" s="32" t="s">
         <v>501</v>
       </c>
-      <c r="AS6" s="32" t="s">
+      <c r="AT6" s="32" t="s">
         <v>502</v>
       </c>
-      <c r="AT6" s="32" t="s">
+      <c r="AU6" s="32" t="s">
         <v>503</v>
       </c>
-      <c r="AU6" s="32" t="s">
+      <c r="AV6" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="AV6" s="32" t="s">
+      <c r="AW6" s="32" t="s">
         <v>505</v>
       </c>
-      <c r="AW6" s="32" t="s">
+      <c r="AX6" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="AY6" s="32" t="s">
         <v>506</v>
       </c>
-      <c r="AX6" s="109" t="s">
-        <v>444</v>
-      </c>
-      <c r="AY6" s="32" t="s">
+      <c r="AZ6" s="32" t="s">
         <v>507</v>
       </c>
-      <c r="AZ6" s="32" t="s">
-        <v>508</v>
-      </c>
       <c r="BA6" s="109" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="7" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="15.75">
       <c r="A7" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>533</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>115</v>
-      </c>
       <c r="D7" s="110" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="94" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
       <c r="K7" s="16"/>
       <c r="L7" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M7" s="17" t="s">
         <v>55</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S7" s="28" t="s">
         <v>118</v>
-      </c>
-      <c r="S7" s="28" t="s">
-        <v>119</v>
       </c>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
@@ -5291,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AB7" s="19"/>
       <c r="AC7" s="20"/>
@@ -5312,31 +5343,31 @@
       <c r="AR7" s="114"/>
       <c r="AS7" s="114"/>
       <c r="AT7" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU7" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AV7" s="23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AW7" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AX7" s="23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AY7" s="23" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AZ7" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BA7" s="23" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="8" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A8" s="35"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -5391,7 +5422,7 @@
       <c r="AZ8" s="23"/>
       <c r="BA8" s="23"/>
     </row>
-    <row r="9" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A9" s="35"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -5446,7 +5477,7 @@
       <c r="AZ9" s="23"/>
       <c r="BA9" s="23"/>
     </row>
-    <row r="10" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A10" s="35"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -5501,7 +5532,7 @@
       <c r="AZ10" s="23"/>
       <c r="BA10" s="23"/>
     </row>
-    <row r="11" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A11" s="35"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -5556,7 +5587,7 @@
       <c r="AZ11" s="23"/>
       <c r="BA11" s="23"/>
     </row>
-    <row r="12" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A12" s="35"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -5611,7 +5642,7 @@
       <c r="AZ12" s="23"/>
       <c r="BA12" s="23"/>
     </row>
-    <row r="13" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A13" s="35"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -5666,7 +5697,7 @@
       <c r="AZ13" s="23"/>
       <c r="BA13" s="23"/>
     </row>
-    <row r="14" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A14" s="35"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -5721,7 +5752,7 @@
       <c r="AZ14" s="23"/>
       <c r="BA14" s="23"/>
     </row>
-    <row r="15" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A15" s="35"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -5776,7 +5807,7 @@
       <c r="AZ15" s="23"/>
       <c r="BA15" s="23"/>
     </row>
-    <row r="16" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A16" s="35"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -5831,7 +5862,7 @@
       <c r="AZ16" s="23"/>
       <c r="BA16" s="23"/>
     </row>
-    <row r="17" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A17" s="35"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -5886,7 +5917,7 @@
       <c r="AZ17" s="23"/>
       <c r="BA17" s="23"/>
     </row>
-    <row r="18" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A18" s="35"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -5941,7 +5972,7 @@
       <c r="AZ18" s="23"/>
       <c r="BA18" s="23"/>
     </row>
-    <row r="19" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A19" s="35"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -5996,7 +6027,7 @@
       <c r="AZ19" s="23"/>
       <c r="BA19" s="23"/>
     </row>
-    <row r="20" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A20" s="35"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -6051,7 +6082,7 @@
       <c r="AZ20" s="23"/>
       <c r="BA20" s="23"/>
     </row>
-    <row r="21" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A21" s="35"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -6106,7 +6137,7 @@
       <c r="AZ21" s="23"/>
       <c r="BA21" s="23"/>
     </row>
-    <row r="22" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A22" s="35"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -6161,7 +6192,7 @@
       <c r="AZ22" s="23"/>
       <c r="BA22" s="23"/>
     </row>
-    <row r="23" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A23" s="35"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -6216,7 +6247,7 @@
       <c r="AZ23" s="23"/>
       <c r="BA23" s="23"/>
     </row>
-    <row r="24" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A24" s="35"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -6271,7 +6302,7 @@
       <c r="AZ24" s="23"/>
       <c r="BA24" s="23"/>
     </row>
-    <row r="25" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A25" s="35"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -6326,7 +6357,7 @@
       <c r="AZ25" s="23"/>
       <c r="BA25" s="23"/>
     </row>
-    <row r="26" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A26" s="35"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
@@ -6381,7 +6412,7 @@
       <c r="AZ26" s="23"/>
       <c r="BA26" s="23"/>
     </row>
-    <row r="27" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A27" s="35"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -6436,7 +6467,7 @@
       <c r="AZ27" s="23"/>
       <c r="BA27" s="23"/>
     </row>
-    <row r="28" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A28" s="35"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -6491,7 +6522,7 @@
       <c r="AZ28" s="23"/>
       <c r="BA28" s="23"/>
     </row>
-    <row r="29" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A29" s="35"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -6546,7 +6577,7 @@
       <c r="AZ29" s="23"/>
       <c r="BA29" s="23"/>
     </row>
-    <row r="30" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A30" s="35"/>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -6601,7 +6632,7 @@
       <c r="AZ30" s="23"/>
       <c r="BA30" s="23"/>
     </row>
-    <row r="31" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A31" s="35"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -6656,7 +6687,7 @@
       <c r="AZ31" s="23"/>
       <c r="BA31" s="23"/>
     </row>
-    <row r="32" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A32" s="35"/>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -6711,7 +6742,7 @@
       <c r="AZ32" s="23"/>
       <c r="BA32" s="23"/>
     </row>
-    <row r="33" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A33" s="35"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -6766,7 +6797,7 @@
       <c r="AZ33" s="23"/>
       <c r="BA33" s="23"/>
     </row>
-    <row r="34" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A34" s="35"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -6821,7 +6852,7 @@
       <c r="AZ34" s="23"/>
       <c r="BA34" s="23"/>
     </row>
-    <row r="35" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A35" s="35"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -6876,7 +6907,7 @@
       <c r="AZ35" s="23"/>
       <c r="BA35" s="23"/>
     </row>
-    <row r="36" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A36" s="35"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -6931,7 +6962,7 @@
       <c r="AZ36" s="23"/>
       <c r="BA36" s="23"/>
     </row>
-    <row r="37" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A37" s="35"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -6986,7 +7017,7 @@
       <c r="AZ37" s="23"/>
       <c r="BA37" s="23"/>
     </row>
-    <row r="38" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A38" s="35"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -7041,7 +7072,7 @@
       <c r="AZ38" s="23"/>
       <c r="BA38" s="23"/>
     </row>
-    <row r="39" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A39" s="35"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -7096,7 +7127,7 @@
       <c r="AZ39" s="23"/>
       <c r="BA39" s="23"/>
     </row>
-    <row r="40" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A40" s="35"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -7151,7 +7182,7 @@
       <c r="AZ40" s="23"/>
       <c r="BA40" s="23"/>
     </row>
-    <row r="41" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A41" s="35"/>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -7206,7 +7237,7 @@
       <c r="AZ41" s="23"/>
       <c r="BA41" s="23"/>
     </row>
-    <row r="42" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A42" s="35"/>
       <c r="B42" s="34"/>
       <c r="C42" s="34"/>
@@ -7261,7 +7292,7 @@
       <c r="AZ42" s="23"/>
       <c r="BA42" s="23"/>
     </row>
-    <row r="43" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A43" s="35"/>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -7316,7 +7347,7 @@
       <c r="AZ43" s="23"/>
       <c r="BA43" s="23"/>
     </row>
-    <row r="44" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A44" s="35"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -7371,7 +7402,7 @@
       <c r="AZ44" s="23"/>
       <c r="BA44" s="23"/>
     </row>
-    <row r="45" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A45" s="35"/>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -7426,7 +7457,7 @@
       <c r="AZ45" s="23"/>
       <c r="BA45" s="23"/>
     </row>
-    <row r="46" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A46" s="35"/>
       <c r="B46" s="34"/>
       <c r="C46" s="34"/>
@@ -7481,7 +7512,7 @@
       <c r="AZ46" s="23"/>
       <c r="BA46" s="23"/>
     </row>
-    <row r="47" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A47" s="35"/>
       <c r="B47" s="34"/>
       <c r="C47" s="34"/>
@@ -7536,7 +7567,7 @@
       <c r="AZ47" s="23"/>
       <c r="BA47" s="23"/>
     </row>
-    <row r="48" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A48" s="35"/>
       <c r="B48" s="34"/>
       <c r="C48" s="34"/>
@@ -7591,7 +7622,7 @@
       <c r="AZ48" s="23"/>
       <c r="BA48" s="23"/>
     </row>
-    <row r="49" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A49" s="35"/>
       <c r="B49" s="34"/>
       <c r="C49" s="34"/>
@@ -7646,7 +7677,7 @@
       <c r="AZ49" s="23"/>
       <c r="BA49" s="23"/>
     </row>
-    <row r="50" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A50" s="35"/>
       <c r="B50" s="34"/>
       <c r="C50" s="34"/>
@@ -7701,7 +7732,7 @@
       <c r="AZ50" s="23"/>
       <c r="BA50" s="23"/>
     </row>
-    <row r="51" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A51" s="35"/>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
@@ -7756,7 +7787,7 @@
       <c r="AZ51" s="23"/>
       <c r="BA51" s="23"/>
     </row>
-    <row r="52" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A52" s="35"/>
       <c r="B52" s="34"/>
       <c r="C52" s="34"/>
@@ -7811,7 +7842,7 @@
       <c r="AZ52" s="23"/>
       <c r="BA52" s="23"/>
     </row>
-    <row r="53" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A53" s="35"/>
       <c r="B53" s="34"/>
       <c r="C53" s="34"/>
@@ -7866,7 +7897,7 @@
       <c r="AZ53" s="23"/>
       <c r="BA53" s="23"/>
     </row>
-    <row r="54" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A54" s="35"/>
       <c r="B54" s="34"/>
       <c r="C54" s="34"/>
@@ -7921,7 +7952,7 @@
       <c r="AZ54" s="23"/>
       <c r="BA54" s="23"/>
     </row>
-    <row r="55" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A55" s="35"/>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -7976,7 +8007,7 @@
       <c r="AZ55" s="23"/>
       <c r="BA55" s="23"/>
     </row>
-    <row r="56" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A56" s="35"/>
       <c r="B56" s="34"/>
       <c r="C56" s="34"/>
@@ -8031,7 +8062,7 @@
       <c r="AZ56" s="23"/>
       <c r="BA56" s="23"/>
     </row>
-    <row r="57" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A57" s="35"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -8086,7 +8117,7 @@
       <c r="AZ57" s="23"/>
       <c r="BA57" s="23"/>
     </row>
-    <row r="58" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A58" s="35"/>
       <c r="B58" s="34"/>
       <c r="C58" s="34"/>
@@ -8141,7 +8172,7 @@
       <c r="AZ58" s="23"/>
       <c r="BA58" s="23"/>
     </row>
-    <row r="59" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A59" s="35"/>
       <c r="B59" s="34"/>
       <c r="C59" s="34"/>
@@ -8196,7 +8227,7 @@
       <c r="AZ59" s="23"/>
       <c r="BA59" s="23"/>
     </row>
-    <row r="60" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A60" s="35"/>
       <c r="B60" s="34"/>
       <c r="C60" s="34"/>
@@ -8251,7 +8282,7 @@
       <c r="AZ60" s="23"/>
       <c r="BA60" s="23"/>
     </row>
-    <row r="61" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A61" s="35"/>
       <c r="B61" s="34"/>
       <c r="C61" s="34"/>
@@ -8306,7 +8337,7 @@
       <c r="AZ61" s="23"/>
       <c r="BA61" s="23"/>
     </row>
-    <row r="62" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A62" s="35"/>
       <c r="B62" s="34"/>
       <c r="C62" s="34"/>
@@ -8361,7 +8392,7 @@
       <c r="AZ62" s="23"/>
       <c r="BA62" s="23"/>
     </row>
-    <row r="63" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A63" s="35"/>
       <c r="B63" s="34"/>
       <c r="C63" s="34"/>
@@ -8416,7 +8447,7 @@
       <c r="AZ63" s="23"/>
       <c r="BA63" s="23"/>
     </row>
-    <row r="64" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A64" s="35"/>
       <c r="B64" s="34"/>
       <c r="C64" s="34"/>
@@ -8471,7 +8502,7 @@
       <c r="AZ64" s="23"/>
       <c r="BA64" s="23"/>
     </row>
-    <row r="65" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A65" s="35"/>
       <c r="B65" s="34"/>
       <c r="C65" s="34"/>
@@ -8526,7 +8557,7 @@
       <c r="AZ65" s="23"/>
       <c r="BA65" s="23"/>
     </row>
-    <row r="66" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A66" s="35"/>
       <c r="B66" s="34"/>
       <c r="C66" s="34"/>
@@ -8581,7 +8612,7 @@
       <c r="AZ66" s="23"/>
       <c r="BA66" s="23"/>
     </row>
-    <row r="67" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A67" s="35"/>
       <c r="B67" s="34"/>
       <c r="C67" s="34"/>
@@ -8636,7 +8667,7 @@
       <c r="AZ67" s="23"/>
       <c r="BA67" s="23"/>
     </row>
-    <row r="68" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A68" s="35"/>
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
@@ -8691,7 +8722,7 @@
       <c r="AZ68" s="23"/>
       <c r="BA68" s="23"/>
     </row>
-    <row r="69" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A69" s="35"/>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
@@ -8746,7 +8777,7 @@
       <c r="AZ69" s="23"/>
       <c r="BA69" s="23"/>
     </row>
-    <row r="70" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A70" s="35"/>
       <c r="B70" s="34"/>
       <c r="C70" s="34"/>
@@ -8801,7 +8832,7 @@
       <c r="AZ70" s="23"/>
       <c r="BA70" s="23"/>
     </row>
-    <row r="71" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A71" s="35"/>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -8856,7 +8887,7 @@
       <c r="AZ71" s="23"/>
       <c r="BA71" s="23"/>
     </row>
-    <row r="72" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A72" s="35"/>
       <c r="B72" s="34"/>
       <c r="C72" s="34"/>
@@ -8911,7 +8942,7 @@
       <c r="AZ72" s="23"/>
       <c r="BA72" s="23"/>
     </row>
-    <row r="73" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A73" s="35"/>
       <c r="B73" s="34"/>
       <c r="C73" s="34"/>
@@ -8966,7 +8997,7 @@
       <c r="AZ73" s="23"/>
       <c r="BA73" s="23"/>
     </row>
-    <row r="74" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A74" s="35"/>
       <c r="B74" s="34"/>
       <c r="C74" s="34"/>
@@ -9021,7 +9052,7 @@
       <c r="AZ74" s="23"/>
       <c r="BA74" s="23"/>
     </row>
-    <row r="75" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A75" s="35"/>
       <c r="B75" s="34"/>
       <c r="C75" s="34"/>
@@ -9076,7 +9107,7 @@
       <c r="AZ75" s="23"/>
       <c r="BA75" s="23"/>
     </row>
-    <row r="76" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A76" s="35"/>
       <c r="B76" s="34"/>
       <c r="C76" s="34"/>
@@ -9131,7 +9162,7 @@
       <c r="AZ76" s="23"/>
       <c r="BA76" s="23"/>
     </row>
-    <row r="77" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A77" s="35"/>
       <c r="B77" s="34"/>
       <c r="C77" s="34"/>
@@ -9186,7 +9217,7 @@
       <c r="AZ77" s="23"/>
       <c r="BA77" s="23"/>
     </row>
-    <row r="78" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A78" s="35"/>
       <c r="B78" s="34"/>
       <c r="C78" s="34"/>
@@ -9241,7 +9272,7 @@
       <c r="AZ78" s="23"/>
       <c r="BA78" s="23"/>
     </row>
-    <row r="79" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A79" s="35"/>
       <c r="B79" s="34"/>
       <c r="C79" s="34"/>
@@ -9296,7 +9327,7 @@
       <c r="AZ79" s="23"/>
       <c r="BA79" s="23"/>
     </row>
-    <row r="80" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A80" s="35"/>
       <c r="B80" s="34"/>
       <c r="C80" s="34"/>
@@ -9351,7 +9382,7 @@
       <c r="AZ80" s="23"/>
       <c r="BA80" s="23"/>
     </row>
-    <row r="81" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A81" s="35"/>
       <c r="B81" s="34"/>
       <c r="C81" s="34"/>
@@ -9406,7 +9437,7 @@
       <c r="AZ81" s="23"/>
       <c r="BA81" s="23"/>
     </row>
-    <row r="82" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A82" s="35"/>
       <c r="B82" s="34"/>
       <c r="C82" s="34"/>
@@ -9461,7 +9492,7 @@
       <c r="AZ82" s="23"/>
       <c r="BA82" s="23"/>
     </row>
-    <row r="83" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A83" s="35"/>
       <c r="B83" s="34"/>
       <c r="C83" s="34"/>
@@ -9516,7 +9547,7 @@
       <c r="AZ83" s="23"/>
       <c r="BA83" s="23"/>
     </row>
-    <row r="84" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A84" s="35"/>
       <c r="B84" s="34"/>
       <c r="C84" s="34"/>
@@ -9571,7 +9602,7 @@
       <c r="AZ84" s="23"/>
       <c r="BA84" s="23"/>
     </row>
-    <row r="85" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A85" s="35"/>
       <c r="B85" s="34"/>
       <c r="C85" s="34"/>
@@ -9626,7 +9657,7 @@
       <c r="AZ85" s="23"/>
       <c r="BA85" s="23"/>
     </row>
-    <row r="86" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A86" s="35"/>
       <c r="B86" s="34"/>
       <c r="C86" s="34"/>
@@ -9681,7 +9712,7 @@
       <c r="AZ86" s="23"/>
       <c r="BA86" s="23"/>
     </row>
-    <row r="87" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A87" s="35"/>
       <c r="B87" s="34"/>
       <c r="C87" s="34"/>
@@ -9736,7 +9767,7 @@
       <c r="AZ87" s="23"/>
       <c r="BA87" s="23"/>
     </row>
-    <row r="88" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A88" s="35"/>
       <c r="B88" s="34"/>
       <c r="C88" s="34"/>
@@ -9791,7 +9822,7 @@
       <c r="AZ88" s="23"/>
       <c r="BA88" s="23"/>
     </row>
-    <row r="89" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A89" s="35"/>
       <c r="B89" s="34"/>
       <c r="C89" s="34"/>
@@ -9846,7 +9877,7 @@
       <c r="AZ89" s="23"/>
       <c r="BA89" s="23"/>
     </row>
-    <row r="90" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A90" s="35"/>
       <c r="B90" s="34"/>
       <c r="C90" s="34"/>
@@ -9901,7 +9932,7 @@
       <c r="AZ90" s="23"/>
       <c r="BA90" s="23"/>
     </row>
-    <row r="91" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A91" s="35"/>
       <c r="B91" s="34"/>
       <c r="C91" s="34"/>
@@ -9956,7 +9987,7 @@
       <c r="AZ91" s="23"/>
       <c r="BA91" s="23"/>
     </row>
-    <row r="92" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A92" s="35"/>
       <c r="B92" s="34"/>
       <c r="C92" s="34"/>
@@ -10011,7 +10042,7 @@
       <c r="AZ92" s="23"/>
       <c r="BA92" s="23"/>
     </row>
-    <row r="93" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A93" s="35"/>
       <c r="B93" s="34"/>
       <c r="C93" s="34"/>
@@ -10066,7 +10097,7 @@
       <c r="AZ93" s="23"/>
       <c r="BA93" s="23"/>
     </row>
-    <row r="94" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A94" s="35"/>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -10121,7 +10152,7 @@
       <c r="AZ94" s="23"/>
       <c r="BA94" s="23"/>
     </row>
-    <row r="95" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A95" s="35"/>
       <c r="B95" s="34"/>
       <c r="C95" s="34"/>
@@ -10176,7 +10207,7 @@
       <c r="AZ95" s="23"/>
       <c r="BA95" s="23"/>
     </row>
-    <row r="96" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A96" s="35"/>
       <c r="B96" s="34"/>
       <c r="C96" s="34"/>
@@ -10231,7 +10262,7 @@
       <c r="AZ96" s="23"/>
       <c r="BA96" s="23"/>
     </row>
-    <row r="97" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A97" s="35"/>
       <c r="B97" s="34"/>
       <c r="C97" s="34"/>
@@ -10286,7 +10317,7 @@
       <c r="AZ97" s="23"/>
       <c r="BA97" s="23"/>
     </row>
-    <row r="98" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A98" s="35"/>
       <c r="B98" s="34"/>
       <c r="C98" s="34"/>
@@ -10341,7 +10372,7 @@
       <c r="AZ98" s="23"/>
       <c r="BA98" s="23"/>
     </row>
-    <row r="99" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A99" s="35"/>
       <c r="B99" s="34"/>
       <c r="C99" s="34"/>
@@ -10396,7 +10427,7 @@
       <c r="AZ99" s="23"/>
       <c r="BA99" s="23"/>
     </row>
-    <row r="100" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A100" s="35"/>
       <c r="B100" s="34"/>
       <c r="C100" s="34"/>
@@ -10457,17 +10488,17 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="D1 E4:F6 P7:R7">
-    <cfRule type="expression" dxfId="29" priority="78">
+    <cfRule type="expression" dxfId="106" priority="78">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="28" priority="51">
+    <cfRule type="expression" dxfId="105" priority="51">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:AI7 M7:N7">
-    <cfRule type="expression" dxfId="27" priority="49">
+    <cfRule type="expression" dxfId="104" priority="49">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10486,7 +10517,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7">
-    <cfRule type="expression" dxfId="26" priority="47">
+    <cfRule type="expression" dxfId="103" priority="47">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10505,12 +10536,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL7:AN7">
-    <cfRule type="expression" dxfId="25" priority="33">
+    <cfRule type="expression" dxfId="102" priority="33">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE7">
-    <cfRule type="expression" dxfId="24" priority="45">
+    <cfRule type="expression" dxfId="101" priority="45">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10529,7 +10560,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF7:AG7">
-    <cfRule type="expression" dxfId="23" priority="43">
+    <cfRule type="expression" dxfId="100" priority="43">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10548,7 +10579,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH7">
-    <cfRule type="expression" dxfId="22" priority="41">
+    <cfRule type="expression" dxfId="99" priority="41">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10567,7 +10598,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI7">
-    <cfRule type="expression" dxfId="21" priority="39">
+    <cfRule type="expression" dxfId="98" priority="39">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10586,7 +10617,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ7">
-    <cfRule type="expression" dxfId="20" priority="37">
+    <cfRule type="expression" dxfId="97" priority="37">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10605,7 +10636,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK7">
-    <cfRule type="expression" dxfId="19" priority="35">
+    <cfRule type="expression" dxfId="96" priority="35">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10638,87 +10669,87 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="18" priority="30">
+    <cfRule type="expression" dxfId="95" priority="30">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7">
-    <cfRule type="expression" dxfId="17" priority="28">
+    <cfRule type="expression" dxfId="94" priority="28">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:L7">
-    <cfRule type="expression" dxfId="16" priority="27">
+    <cfRule type="expression" dxfId="93" priority="27">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="expression" dxfId="15" priority="24">
+    <cfRule type="expression" dxfId="92" priority="24">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:A100">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="91" priority="1">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:R100">
-    <cfRule type="expression" dxfId="13" priority="22">
+    <cfRule type="expression" dxfId="90" priority="22">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S8:AI100 M8:N100">
-    <cfRule type="expression" dxfId="12" priority="20">
+    <cfRule type="expression" dxfId="89" priority="20">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD8:AD100">
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="88" priority="18">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL8:AN100">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="87" priority="4">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE8:AE100">
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="86" priority="16">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF8:AG100">
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="85" priority="14">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH8:AH100">
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="84" priority="12">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8:AI100">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="83" priority="10">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8:AJ100">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="82" priority="8">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK100">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="81" priority="6">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O100">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="80" priority="3">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:L100">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10902,8 +10933,9 @@
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -11106,150 +11138,150 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtPickList" enableFormatConditionsCalculation="0">
+  <sheetPr codeName="shtPickList">
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="33.75" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="13"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="119" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="14"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="14"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="14"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="14"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="14"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="14"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="14"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="14"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="14"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="14"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="14"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="14"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="14"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="14"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="14"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="14"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="14"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1">
       <c r="A33" s="14"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1">
       <c r="A34" s="14"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1">
       <c r="A35" s="14"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1">
       <c r="A36" s="14"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1">
       <c r="A37" s="14"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1">
       <c r="A38" s="14"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1">
       <c r="A39" s="14"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1">
       <c r="A40" s="14"/>
     </row>
   </sheetData>
@@ -11272,19 +11304,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtBinLookup" enableFormatConditionsCalculation="0">
+  <sheetPr codeName="shtBinLookup">
     <tabColor theme="4" tint="-0.499984740745262"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="33.75" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -11292,16 +11324,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -11318,7 +11350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5">
       <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
@@ -11335,7 +11367,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
@@ -11352,207 +11384,207 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4">
       <c r="A18" s="14"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4">
       <c r="A19" s="14"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4">
       <c r="A20" s="14"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4">
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4">
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -11583,302 +11615,302 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="57" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="57" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="57"/>
-    <col min="4" max="4" width="27.83203125" style="57" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="57"/>
+    <col min="3" max="3" width="8.77734375" style="57"/>
+    <col min="4" max="4" width="27.77734375" style="57" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1">
       <c r="A1" s="125" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
       <c r="D1" s="125"/>
     </row>
-    <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="C2" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="D2" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="59" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="60">
         <v>1</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1">
       <c r="A4" s="64">
         <v>2</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="66"/>
       <c r="D4" s="67" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
       <c r="A5" s="68"/>
       <c r="B5" s="69"/>
       <c r="C5" s="70"/>
       <c r="D5" s="70"/>
     </row>
-    <row r="6" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" s="71" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="126" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B6" s="127"/>
       <c r="C6" s="127"/>
       <c r="D6" s="128"/>
     </row>
-    <row r="7" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
       <c r="A7" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="C7" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="D7" s="73" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="73" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="74">
         <v>3</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="76"/>
       <c r="D8" s="77"/>
     </row>
-    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="60">
         <v>4</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="78"/>
       <c r="D9" s="79"/>
     </row>
-    <row r="10" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17.25" thickBot="1">
       <c r="A10" s="60">
         <v>5</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" s="78"/>
       <c r="D10" s="79"/>
     </row>
-    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="74">
         <v>6</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="78"/>
       <c r="D11" s="79"/>
     </row>
-    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="60">
         <v>7</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="78"/>
       <c r="D12" s="79"/>
     </row>
-    <row r="13" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="17.25" thickBot="1">
       <c r="A13" s="60">
         <v>8</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="78"/>
       <c r="D13" s="79"/>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4">
       <c r="A14" s="74">
         <v>9</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="79"/>
     </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="60">
         <v>10</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="79"/>
     </row>
-    <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="17.25" thickBot="1">
       <c r="A16" s="60">
         <v>11</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="79" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="74">
         <v>12</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="79"/>
     </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="60">
         <v>13</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C18" s="78"/>
       <c r="D18" s="79"/>
     </row>
-    <row r="19" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" thickBot="1">
       <c r="A19" s="60">
         <v>14</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="78"/>
       <c r="D19" s="79"/>
     </row>
-    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="74">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="79"/>
     </row>
-    <row r="21" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" thickBot="1">
       <c r="A21" s="60">
         <v>16</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="80"/>
       <c r="D21" s="81"/>
     </row>
-    <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="16.5" thickBot="1">
       <c r="A22" s="82"/>
     </row>
-    <row r="23" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="16.5" thickBot="1">
       <c r="A23" s="129" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B23" s="130"/>
       <c r="C23" s="130"/>
       <c r="D23" s="131"/>
     </row>
-    <row r="24" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" thickBot="1">
       <c r="A24" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="C24" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="84" t="s">
+      <c r="D24" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="84" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:4" ht="16.5" thickBot="1">
       <c r="A25" s="60">
         <v>17</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="86"/>
       <c r="D25" s="87" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" thickBot="1">
       <c r="A26" s="60">
         <v>18</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="60">
         <v>19</v>
       </c>
       <c r="B27" s="85" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C27" s="88"/>
       <c r="D27" s="89" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" thickBot="1">
       <c r="A28" s="60">
         <v>20</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C28" s="91"/>
       <c r="D28" s="92" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -11899,63 +11931,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
+  <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="52" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="52" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4">
       <c r="A1" s="132" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="132" t="s">
         <v>122</v>
-      </c>
-      <c r="B1" s="132" t="s">
-        <v>123</v>
       </c>
       <c r="C1" s="132"/>
       <c r="D1" s="132" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="132"/>
       <c r="B2" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>126</v>
-      </c>
       <c r="D2" s="132"/>
     </row>
-    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="45" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="40"/>
       <c r="C3" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" s="41"/>
     </row>
-    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="16.5">
       <c r="A4" s="39" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D4" s="41"/>
     </row>
-    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="43" t="s">
         <v>15</v>
       </c>
@@ -11963,59 +11995,59 @@
       <c r="C5" s="44"/>
       <c r="D5" s="41"/>
     </row>
-    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="41" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="16.5">
+      <c r="A7" s="43" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.15">
-      <c r="A7" s="43" t="s">
-        <v>132</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="46"/>
       <c r="D7" s="41"/>
     </row>
-    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" s="41"/>
     </row>
-    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="48" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="49" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="16.5">
+      <c r="A10" s="45" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.15">
-      <c r="A10" s="45" t="s">
-        <v>136</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="43" t="s">
         <v>18</v>
       </c>
@@ -12023,29 +12055,29 @@
       <c r="C11" s="47"/>
       <c r="D11" s="41"/>
     </row>
-    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" s="41"/>
     </row>
-    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" s="41"/>
     </row>
-    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="16.5">
       <c r="A14" s="43" t="s">
         <v>36</v>
       </c>
@@ -12053,17 +12085,17 @@
       <c r="C14" s="47"/>
       <c r="D14" s="41"/>
     </row>
-    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15" s="47"/>
       <c r="C15" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" s="41"/>
     </row>
-    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="43" t="s">
         <v>37</v>
       </c>
@@ -12071,27 +12103,27 @@
       <c r="C16" s="47"/>
       <c r="D16" s="41"/>
     </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" s="41"/>
     </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D18" s="41"/>
     </row>
-    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="43" t="s">
         <v>39</v>
       </c>
@@ -12099,27 +12131,27 @@
       <c r="C19" s="47"/>
       <c r="D19" s="41"/>
     </row>
-    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="45" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D20" s="41"/>
     </row>
-    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="48" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="41"/>
     </row>
-    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" ht="16.5">
       <c r="A22" s="43" t="s">
         <v>19</v>
       </c>
@@ -12127,7 +12159,7 @@
       <c r="C22" s="47"/>
       <c r="D22" s="41"/>
     </row>
-    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" ht="16.5">
       <c r="A23" s="43" t="s">
         <v>20</v>
       </c>
@@ -12135,7 +12167,7 @@
       <c r="C23" s="47"/>
       <c r="D23" s="41"/>
     </row>
-    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" ht="16.5">
       <c r="A24" s="43" t="s">
         <v>21</v>
       </c>
@@ -12143,7 +12175,7 @@
       <c r="C24" s="47"/>
       <c r="D24" s="41"/>
     </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" ht="16.5">
       <c r="A25" s="43" t="s">
         <v>22</v>
       </c>
@@ -12151,7 +12183,7 @@
       <c r="C25" s="47"/>
       <c r="D25" s="41"/>
     </row>
-    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4" ht="16.5">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -12159,7 +12191,7 @@
       <c r="C26" s="47"/>
       <c r="D26" s="41"/>
     </row>
-    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" ht="16.5">
       <c r="A27" s="43" t="s">
         <v>24</v>
       </c>
@@ -12167,27 +12199,27 @@
       <c r="C27" s="47"/>
       <c r="D27" s="41"/>
     </row>
-    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" ht="16.5">
       <c r="A28" s="45" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" s="41"/>
     </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" ht="16.5">
       <c r="A29" s="45" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="41"/>
     </row>
-    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4" ht="16.5">
       <c r="A30" s="43" t="s">
         <v>27</v>
       </c>
@@ -12195,7 +12227,7 @@
       <c r="C30" s="47"/>
       <c r="D30" s="41"/>
     </row>
-    <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" ht="16.5">
       <c r="A31" s="43" t="s">
         <v>28</v>
       </c>
@@ -12203,7 +12235,7 @@
       <c r="C31" s="47"/>
       <c r="D31" s="41"/>
     </row>
-    <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" ht="16.5">
       <c r="A32" s="43" t="s">
         <v>29</v>
       </c>
@@ -12211,7 +12243,7 @@
       <c r="C32" s="47"/>
       <c r="D32" s="41"/>
     </row>
-    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" ht="16.5">
       <c r="A33" s="43" t="s">
         <v>30</v>
       </c>
@@ -12219,7 +12251,7 @@
       <c r="C33" s="47"/>
       <c r="D33" s="41"/>
     </row>
-    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" ht="16.5">
       <c r="A34" s="43" t="s">
         <v>31</v>
       </c>
@@ -12227,7 +12259,7 @@
       <c r="C34" s="47"/>
       <c r="D34" s="41"/>
     </row>
-    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" ht="16.5">
       <c r="A35" s="43" t="s">
         <v>32</v>
       </c>
@@ -12235,46 +12267,46 @@
       <c r="C35" s="47"/>
       <c r="D35" s="41"/>
     </row>
-    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="51"/>
       <c r="C36" s="51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="41"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4">
       <c r="A39" s="52" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="53"/>
       <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C40" s="54" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="55"/>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="56"/>
       <c r="B42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="54" t="s">
         <v>146</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -12307,484 +12339,484 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="31.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" s="27" customFormat="1">
       <c r="A1" s="96" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="96" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="96" t="s">
         <v>432</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="E1" s="96" t="s">
         <v>433</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="F1" s="96" t="s">
         <v>434</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="G1" s="96" t="s">
         <v>435</v>
       </c>
-      <c r="G1" s="96" t="s">
+      <c r="H1" s="96" t="s">
         <v>436</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="I1" s="100" t="s">
+        <v>443</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="95" t="s">
+        <v>420</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>428</v>
+      </c>
+      <c r="D2" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="I1" s="100" t="s">
+      <c r="E2" s="98" t="s">
+        <v>509</v>
+      </c>
+      <c r="F2" s="107" t="s">
         <v>444</v>
       </c>
-      <c r="J1" s="102" t="s">
-        <v>495</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>496</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>497</v>
-      </c>
-      <c r="M1" s="122" t="s">
+      <c r="G2" s="97" t="s">
+        <v>513</v>
+      </c>
+      <c r="H2" s="95" t="s">
+        <v>441</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>450</v>
+      </c>
+      <c r="J2" s="101" t="s">
+        <v>481</v>
+      </c>
+      <c r="K2" s="103" t="s">
+        <v>485</v>
+      </c>
+      <c r="L2" s="107" t="s">
+        <v>488</v>
+      </c>
+      <c r="M2" s="116" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A2" s="95" t="s">
+    <row r="3" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A3" s="95" t="s">
         <v>421</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B3" s="107" t="s">
         <v>421</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C3" s="95" t="s">
         <v>429</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D3" s="95" t="s">
         <v>438</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E3" s="98" t="s">
         <v>510</v>
       </c>
-      <c r="F2" s="107" t="s">
+      <c r="F3" s="107" t="s">
         <v>445</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G3" s="97" t="s">
         <v>514</v>
       </c>
-      <c r="H2" s="95" t="s">
+      <c r="H3" s="95" t="s">
         <v>442</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I3" s="99" t="s">
         <v>451</v>
       </c>
-      <c r="J2" s="101" t="s">
+      <c r="J3" s="101" t="s">
         <v>482</v>
       </c>
-      <c r="K2" s="103" t="s">
+      <c r="K3" s="103" t="s">
         <v>486</v>
       </c>
-      <c r="L2" s="107" t="s">
+      <c r="L3" s="107" t="s">
         <v>489</v>
       </c>
-      <c r="M2" s="116" t="s">
+      <c r="M3" s="116" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="95" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="95" t="s">
         <v>422</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B4" s="107" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C4" s="95" t="s">
         <v>430</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D4" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="E3" s="98" t="s">
+      <c r="E4" s="98" t="s">
         <v>511</v>
       </c>
-      <c r="F3" s="107" t="s">
+      <c r="F4" s="107" t="s">
         <v>446</v>
       </c>
-      <c r="G3" s="97" t="s">
-        <v>515</v>
-      </c>
-      <c r="H3" s="95" t="s">
-        <v>443</v>
-      </c>
-      <c r="I3" s="99" t="s">
+      <c r="G4" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="H4" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="I4" s="99" t="s">
         <v>452</v>
       </c>
-      <c r="J3" s="101" t="s">
+      <c r="J4" s="101" t="s">
         <v>483</v>
       </c>
-      <c r="K3" s="103" t="s">
+      <c r="K4" s="103" t="s">
         <v>487</v>
       </c>
-      <c r="L3" s="107" t="s">
+      <c r="L4" s="107" t="s">
         <v>490</v>
       </c>
-      <c r="M3" s="116" t="s">
+      <c r="M4" s="116" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A4" s="95" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="95" t="s">
         <v>423</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B5" s="107" t="s">
         <v>423</v>
       </c>
-      <c r="C4" s="95" t="s">
-        <v>431</v>
-      </c>
-      <c r="D4" s="95" t="s">
+      <c r="C5" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="D5" s="95" t="s">
         <v>440</v>
       </c>
-      <c r="E4" s="98" t="s">
+      <c r="E5" s="98" t="s">
         <v>512</v>
       </c>
-      <c r="F4" s="107" t="s">
+      <c r="F5" s="107" t="s">
         <v>447</v>
       </c>
-      <c r="G4" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="H4" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="I4" s="99" t="s">
+      <c r="I5" s="99" t="s">
         <v>453</v>
       </c>
-      <c r="J4" s="101" t="s">
+      <c r="J5" s="101" t="s">
         <v>484</v>
       </c>
-      <c r="K4" s="103" t="s">
-        <v>488</v>
-      </c>
-      <c r="L4" s="107" t="s">
+      <c r="K5" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="L5" s="107" t="s">
         <v>491</v>
       </c>
-      <c r="M4" s="116" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="95" t="s">
+      <c r="M5" s="116" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="D6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="E6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="F6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="I6" s="99" t="s">
+        <v>454</v>
+      </c>
+      <c r="J6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="L6" s="107" t="s">
+        <v>492</v>
+      </c>
+      <c r="M6" s="116" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="116" t="s">
+        <v>528</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>528</v>
+      </c>
+      <c r="I7" s="99" t="s">
+        <v>455</v>
+      </c>
+      <c r="L7" s="107" t="s">
+        <v>493</v>
+      </c>
+      <c r="M7" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="116" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="116" t="s">
+        <v>529</v>
+      </c>
+      <c r="I8" s="99" t="s">
+        <v>456</v>
+      </c>
+      <c r="L8" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="95" t="s">
         <v>424</v>
       </c>
-      <c r="B5" s="107" t="s">
+      <c r="B9" s="107" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>441</v>
-      </c>
-      <c r="E5" s="98" t="s">
-        <v>513</v>
-      </c>
-      <c r="F5" s="107" t="s">
-        <v>448</v>
-      </c>
-      <c r="I5" s="99" t="s">
-        <v>454</v>
-      </c>
-      <c r="J5" s="101" t="s">
-        <v>485</v>
-      </c>
-      <c r="K5" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="L5" s="107" t="s">
-        <v>492</v>
-      </c>
-      <c r="M5" s="116" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="116" t="s">
-        <v>528</v>
-      </c>
-      <c r="B6" s="116" t="s">
-        <v>528</v>
-      </c>
-      <c r="D6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="E6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="F6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="I6" s="99" t="s">
-        <v>455</v>
-      </c>
-      <c r="J6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="L6" s="107" t="s">
-        <v>493</v>
-      </c>
-      <c r="M6" s="116" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A7" s="116" t="s">
-        <v>529</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>529</v>
-      </c>
-      <c r="I7" s="99" t="s">
-        <v>456</v>
-      </c>
-      <c r="L7" s="107" t="s">
-        <v>494</v>
-      </c>
-      <c r="M7" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="116" t="s">
-        <v>530</v>
-      </c>
-      <c r="B8" s="116" t="s">
-        <v>530</v>
-      </c>
-      <c r="I8" s="99" t="s">
+      <c r="I9" s="99" t="s">
         <v>457</v>
       </c>
-      <c r="L8" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="95" t="s">
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="95" t="s">
         <v>425</v>
       </c>
-      <c r="B9" s="107" t="s">
+      <c r="B10" s="107" t="s">
         <v>425</v>
       </c>
-      <c r="I9" s="99" t="s">
+      <c r="I10" s="99" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A10" s="95" t="s">
-        <v>426</v>
-      </c>
-      <c r="B10" s="107" t="s">
-        <v>426</v>
-      </c>
-      <c r="I10" s="99" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13">
       <c r="A11" s="117" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B11" s="117" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H11" s="107"/>
       <c r="I11" s="99" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="117" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H12" s="107"/>
       <c r="I12" s="99" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="117" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H13" s="107"/>
       <c r="I13" s="99" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="95" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H14" s="107"/>
       <c r="I14" s="99" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15" s="116"/>
       <c r="H15" s="107"/>
       <c r="I15" s="99" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16" s="107"/>
       <c r="H16" s="107"/>
       <c r="I16" s="99" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="107"/>
       <c r="H17" s="107"/>
       <c r="I17" s="99" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="107"/>
       <c r="H18" s="107"/>
       <c r="I18" s="99" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="107"/>
       <c r="H19" s="107"/>
       <c r="I19" s="99" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="107"/>
       <c r="H20" s="107"/>
       <c r="I20" s="99" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="107"/>
       <c r="H21" s="107"/>
       <c r="I21" s="99" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.15">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="107"/>
       <c r="H22" s="107"/>
       <c r="I22" s="99" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="107"/>
       <c r="H23" s="107"/>
       <c r="I23" s="99" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
       <c r="B24" s="107"/>
       <c r="H24" s="107"/>
       <c r="I24" s="99" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="107"/>
       <c r="H25" s="107"/>
       <c r="I25" s="99" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
       <c r="H26" s="107"/>
       <c r="I26" s="99" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.15">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="H27" s="107"/>
       <c r="I27" s="99" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.15">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="H28" s="107"/>
       <c r="I28" s="99" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.15">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="H29" s="107"/>
       <c r="I29" s="99" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.15">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="H30" s="107"/>
       <c r="I30" s="99" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="H31" s="107"/>
       <c r="I31" s="99" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="H32" s="107"/>
       <c r="I32" s="99" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.15">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9">
       <c r="H33" s="107"/>
       <c r="I33" s="99" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.15">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9">
       <c r="H34" s="107"/>
       <c r="I34" s="115" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9">
+      <c r="I35" s="115" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.15">
-      <c r="I35" s="115" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="8:9">
       <c r="I36" s="116" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -12797,134 +12829,134 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="107" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="107" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="107" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="107" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="107" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="107" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="107" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="107" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="107" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="107" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="107" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="107" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="107" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="107" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="107" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="107" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="107" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="107" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="107" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="107" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="107" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="107" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="107" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="105"/>
     </row>
   </sheetData>
@@ -12935,52 +12967,52 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" t="s">
         <v>419</v>
-      </c>
-      <c r="B1" t="s">
-        <v>420</v>
       </c>
       <c r="C1" t="s">
         <v>46</v>
@@ -12995,7 +13027,7 @@
         <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1" t="s">
         <v>50</v>
@@ -13010,7 +13042,7 @@
         <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="M1" t="s">
         <v>54</v>
@@ -13043,7 +13075,7 @@
         <v>63</v>
       </c>
       <c r="W1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="X1" t="s">
         <v>64</v>
@@ -13097,884 +13129,884 @@
         <v>80</v>
       </c>
       <c r="AO1" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.15">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41">
       <c r="A2" s="95" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" s="95" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="95" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="95" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="95" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="95" t="s">
+        <v>225</v>
+      </c>
+      <c r="J2" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="K2" s="95" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" s="95" t="s">
+        <v>231</v>
+      </c>
+      <c r="M2" s="95" t="s">
+        <v>238</v>
+      </c>
+      <c r="N2" s="95" t="s">
+        <v>257</v>
+      </c>
+      <c r="O2" s="95" t="s">
+        <v>265</v>
+      </c>
+      <c r="P2" s="95" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q2" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="R2" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="S2" s="95" t="s">
+        <v>292</v>
+      </c>
+      <c r="T2" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="U2" t="s">
+        <v>296</v>
+      </c>
+      <c r="V2" s="95" t="s">
+        <v>300</v>
+      </c>
+      <c r="W2" s="95" t="s">
+        <v>307</v>
+      </c>
+      <c r="X2" s="95" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y2" s="95" t="s">
+        <v>313</v>
+      </c>
+      <c r="Z2" s="95" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA2" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB2" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="AC2" s="95" t="s">
+        <v>335</v>
+      </c>
+      <c r="AD2" s="95" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE2" s="95" t="s">
+        <v>353</v>
+      </c>
+      <c r="AF2" s="95" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG2" s="95" t="s">
+        <v>364</v>
+      </c>
+      <c r="AH2" s="95" t="s">
+        <v>372</v>
+      </c>
+      <c r="AI2" s="95" t="s">
+        <v>377</v>
+      </c>
+      <c r="AJ2" s="95" t="s">
+        <v>393</v>
+      </c>
+      <c r="AK2" s="95" t="s">
+        <v>397</v>
+      </c>
+      <c r="AL2" s="95" t="s">
+        <v>401</v>
+      </c>
+      <c r="AM2" s="95" t="s">
+        <v>410</v>
+      </c>
+      <c r="AN2" s="95" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" s="95" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B3" s="95" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C3" s="95" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D3" s="95" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="95" t="s">
+      <c r="E3" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="F3" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="G2" s="95" t="s">
+      <c r="G3" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="95" t="s">
+      <c r="H3" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I3" s="95" t="s">
         <v>226</v>
       </c>
-      <c r="J2" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="K2" s="95" t="s">
+      <c r="K3" s="95" t="s">
         <v>228</v>
       </c>
-      <c r="L2" s="95" t="s">
+      <c r="L3" s="95" t="s">
         <v>232</v>
       </c>
-      <c r="M2" s="95" t="s">
+      <c r="M3" s="95" t="s">
         <v>239</v>
       </c>
-      <c r="N2" s="95" t="s">
+      <c r="N3" s="95" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="95" t="s">
+      <c r="O3" s="95" t="s">
         <v>266</v>
       </c>
-      <c r="P2" s="95" t="s">
+      <c r="P3" s="95" t="s">
         <v>273</v>
       </c>
-      <c r="Q2" s="95" t="s">
+      <c r="Q3" s="95" t="s">
         <v>279</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R3" s="95" t="s">
         <v>284</v>
       </c>
-      <c r="S2" s="95" t="s">
+      <c r="S3" s="95" t="s">
         <v>293</v>
       </c>
-      <c r="T2" s="95" t="s">
-        <v>296</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="T3" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="U3" t="s">
         <v>297</v>
       </c>
-      <c r="V2" s="95" t="s">
+      <c r="V3" s="95" t="s">
         <v>301</v>
       </c>
-      <c r="W2" s="95" t="s">
+      <c r="W3" s="95" t="s">
         <v>308</v>
       </c>
-      <c r="X2" s="95" t="s">
+      <c r="X3" s="95" t="s">
         <v>310</v>
       </c>
-      <c r="Y2" s="95" t="s">
+      <c r="Y3" s="95" t="s">
         <v>314</v>
       </c>
-      <c r="Z2" s="95" t="s">
+      <c r="Z3" s="95" t="s">
         <v>316</v>
       </c>
-      <c r="AA2" s="95" t="s">
+      <c r="AA3" s="95" t="s">
         <v>325</v>
       </c>
-      <c r="AB2" s="95" t="s">
+      <c r="AB3" s="95" t="s">
         <v>329</v>
       </c>
-      <c r="AC2" s="95" t="s">
+      <c r="AC3" s="95" t="s">
         <v>336</v>
       </c>
-      <c r="AD2" s="95" t="s">
+      <c r="AD3" s="95" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" s="95" t="s">
+      <c r="AE3" s="95" t="s">
         <v>354</v>
       </c>
-      <c r="AF2" s="95" t="s">
+      <c r="AF3" s="95" t="s">
         <v>362</v>
       </c>
-      <c r="AG2" s="95" t="s">
+      <c r="AG3" s="95" t="s">
         <v>365</v>
       </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AH3" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="AI2" s="95" t="s">
+      <c r="AI3" s="95" t="s">
         <v>378</v>
       </c>
-      <c r="AJ2" s="95" t="s">
+      <c r="AJ3" s="95" t="s">
         <v>394</v>
       </c>
-      <c r="AK2" s="95" t="s">
+      <c r="AK3" s="95" t="s">
         <v>398</v>
       </c>
-      <c r="AL2" s="95" t="s">
+      <c r="AL3" s="95" t="s">
         <v>402</v>
       </c>
-      <c r="AM2" s="95" t="s">
+      <c r="AM3" s="95" t="s">
         <v>411</v>
       </c>
-      <c r="AN2" s="95" t="s">
+      <c r="AN3" s="95" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A3" s="95" t="s">
+    <row r="4" spans="1:41">
+      <c r="A4" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B4" s="95" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C4" s="95" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D4" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E4" s="95" t="s">
         <v>205</v>
       </c>
-      <c r="F3" s="95" t="s">
+      <c r="F4" s="95" t="s">
         <v>209</v>
       </c>
-      <c r="G3" s="95" t="s">
+      <c r="G4" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="95" t="s">
+      <c r="H4" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="I3" s="95" t="s">
-        <v>227</v>
-      </c>
-      <c r="K3" s="95" t="s">
+      <c r="I4" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="K4" s="95" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="95" t="s">
+      <c r="L4" s="95" t="s">
         <v>233</v>
       </c>
-      <c r="M3" s="95" t="s">
+      <c r="M4" s="95" t="s">
         <v>240</v>
       </c>
-      <c r="N3" s="95" t="s">
+      <c r="N4" s="95" t="s">
         <v>259</v>
       </c>
-      <c r="O3" s="95" t="s">
+      <c r="O4" s="95" t="s">
         <v>267</v>
       </c>
-      <c r="P3" s="95" t="s">
+      <c r="P4" s="95" t="s">
         <v>274</v>
       </c>
-      <c r="Q3" s="95" t="s">
+      <c r="Q4" s="95" t="s">
         <v>280</v>
       </c>
-      <c r="R3" s="95" t="s">
+      <c r="R4" s="95" t="s">
         <v>285</v>
       </c>
-      <c r="S3" s="95" t="s">
+      <c r="S4" s="95" t="s">
         <v>294</v>
       </c>
-      <c r="T3" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="U4" t="s">
         <v>298</v>
       </c>
-      <c r="V3" s="95" t="s">
+      <c r="V4" t="s">
         <v>302</v>
       </c>
-      <c r="W3" s="95" t="s">
-        <v>309</v>
-      </c>
-      <c r="X3" s="95" t="s">
+      <c r="W4" t="s">
+        <v>538</v>
+      </c>
+      <c r="X4" s="95" t="s">
         <v>311</v>
       </c>
-      <c r="Y3" s="95" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z3" s="95" t="s">
+      <c r="Y4" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z4" s="95" t="s">
         <v>317</v>
       </c>
-      <c r="AA3" s="95" t="s">
+      <c r="AA4" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="AB3" s="95" t="s">
+      <c r="AB4" s="95" t="s">
         <v>330</v>
       </c>
-      <c r="AC3" s="95" t="s">
+      <c r="AC4" s="95" t="s">
         <v>337</v>
       </c>
-      <c r="AD3" s="95" t="s">
+      <c r="AD4" s="95" t="s">
         <v>342</v>
       </c>
-      <c r="AE3" s="95" t="s">
+      <c r="AE4" s="95" t="s">
         <v>355</v>
       </c>
-      <c r="AF3" s="95" t="s">
+      <c r="AF4" s="95" t="s">
         <v>363</v>
       </c>
-      <c r="AG3" s="95" t="s">
+      <c r="AG4" s="95" t="s">
         <v>366</v>
       </c>
-      <c r="AH3" s="95" t="s">
+      <c r="AH4" s="95" t="s">
         <v>374</v>
       </c>
-      <c r="AI3" s="95" t="s">
+      <c r="AI4" s="95" t="s">
         <v>379</v>
       </c>
-      <c r="AJ3" s="95" t="s">
+      <c r="AJ4" s="95" t="s">
         <v>395</v>
       </c>
-      <c r="AK3" s="95" t="s">
+      <c r="AK4" s="95" t="s">
         <v>399</v>
       </c>
-      <c r="AL3" s="95" t="s">
+      <c r="AL4" s="95" t="s">
         <v>403</v>
       </c>
-      <c r="AM3" s="95" t="s">
+      <c r="AM4" s="95" t="s">
         <v>412</v>
       </c>
-      <c r="AN3" s="95" t="s">
+      <c r="AN4" s="95" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A4" s="95" t="s">
+    <row r="5" spans="1:41">
+      <c r="A5" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B5" s="95" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C5" s="95" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D5" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E5" s="95" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F5" s="95" t="s">
         <v>210</v>
       </c>
-      <c r="G4" s="95" t="s">
+      <c r="G5" s="95" t="s">
         <v>214</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H5" s="95" t="s">
         <v>222</v>
       </c>
-      <c r="I4" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="K4" s="95" t="s">
+      <c r="K5" s="95" t="s">
         <v>230</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L5" s="95" t="s">
         <v>234</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M5" s="95" t="s">
         <v>241</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N5" s="95" t="s">
         <v>260</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O5" s="95" t="s">
         <v>268</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P5" s="95" t="s">
         <v>275</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q5" s="95" t="s">
         <v>281</v>
       </c>
-      <c r="R4" s="95" t="s">
+      <c r="R5" s="95" t="s">
         <v>286</v>
       </c>
-      <c r="S4" s="95" t="s">
-        <v>295</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="S5" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="U5" t="s">
         <v>299</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V5" t="s">
         <v>303</v>
       </c>
-      <c r="W4" t="s">
-        <v>539</v>
-      </c>
-      <c r="X4" s="95" t="s">
+      <c r="X5" s="95" t="s">
         <v>312</v>
       </c>
-      <c r="Y4" t="s">
-        <v>539</v>
-      </c>
-      <c r="Z4" s="95" t="s">
+      <c r="Z5" s="95" t="s">
         <v>318</v>
       </c>
-      <c r="AA4" s="95" t="s">
+      <c r="AA5" s="95" t="s">
         <v>327</v>
       </c>
-      <c r="AB4" s="95" t="s">
+      <c r="AB5" s="95" t="s">
         <v>331</v>
       </c>
-      <c r="AC4" s="95" t="s">
+      <c r="AC5" s="95" t="s">
         <v>338</v>
       </c>
-      <c r="AD4" s="95" t="s">
+      <c r="AD5" s="95" t="s">
         <v>343</v>
       </c>
-      <c r="AE4" s="95" t="s">
+      <c r="AE5" s="95" t="s">
         <v>356</v>
       </c>
-      <c r="AF4" s="95" t="s">
-        <v>364</v>
-      </c>
-      <c r="AG4" s="95" t="s">
+      <c r="AF5" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AG5" s="95" t="s">
         <v>367</v>
       </c>
-      <c r="AH4" s="95" t="s">
+      <c r="AH5" s="95" t="s">
         <v>375</v>
       </c>
-      <c r="AI4" s="95" t="s">
+      <c r="AI5" s="95" t="s">
         <v>380</v>
       </c>
-      <c r="AJ4" s="95" t="s">
+      <c r="AJ5" s="95" t="s">
         <v>396</v>
       </c>
-      <c r="AK4" s="95" t="s">
+      <c r="AK5" s="95" t="s">
         <v>400</v>
       </c>
-      <c r="AL4" s="95" t="s">
+      <c r="AL5" s="95" t="s">
         <v>404</v>
       </c>
-      <c r="AM4" s="95" t="s">
+      <c r="AM5" s="95" t="s">
         <v>413</v>
       </c>
-      <c r="AN4" s="95" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A5" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="95" t="s">
+      <c r="AN5" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" s="95" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="95" t="s">
+      <c r="C6" s="95" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="95" t="s">
+      <c r="D6" s="95" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="95" t="s">
-        <v>207</v>
-      </c>
-      <c r="F5" s="95" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="95" t="s">
+      <c r="E6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="F6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="G6" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="H5" s="95" t="s">
+      <c r="H6" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="K5" s="95" t="s">
-        <v>231</v>
-      </c>
-      <c r="L5" s="95" t="s">
+      <c r="K6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="L6" s="95" t="s">
         <v>235</v>
       </c>
-      <c r="M5" s="95" t="s">
+      <c r="M6" s="95" t="s">
         <v>242</v>
       </c>
-      <c r="N5" s="95" t="s">
+      <c r="N6" s="95" t="s">
         <v>261</v>
       </c>
-      <c r="O5" s="95" t="s">
+      <c r="O6" s="95" t="s">
         <v>269</v>
       </c>
-      <c r="P5" s="95" t="s">
+      <c r="P6" s="95" t="s">
         <v>276</v>
       </c>
-      <c r="Q5" s="95" t="s">
+      <c r="Q6" s="95" t="s">
         <v>282</v>
       </c>
-      <c r="R5" s="95" t="s">
+      <c r="R6" s="95" t="s">
         <v>287</v>
       </c>
-      <c r="S5" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="U5" t="s">
-        <v>300</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="U6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="V6" t="s">
         <v>304</v>
       </c>
-      <c r="X5" s="95" t="s">
-        <v>313</v>
-      </c>
-      <c r="Z5" s="95" t="s">
+      <c r="X6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z6" s="95" t="s">
         <v>319</v>
       </c>
-      <c r="AA5" s="95" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB5" s="95" t="s">
+      <c r="AA6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AB6" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="AC5" s="95" t="s">
+      <c r="AC6" s="95" t="s">
         <v>339</v>
       </c>
-      <c r="AD5" s="95" t="s">
+      <c r="AD6" s="95" t="s">
         <v>344</v>
       </c>
-      <c r="AE5" s="95" t="s">
+      <c r="AE6" s="95" t="s">
         <v>357</v>
       </c>
-      <c r="AF5" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AG5" s="95" t="s">
+      <c r="AG6" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="AH5" s="95" t="s">
+      <c r="AH6" s="95" t="s">
         <v>376</v>
       </c>
-      <c r="AI5" s="95" t="s">
+      <c r="AI6" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="AJ5" s="95" t="s">
-        <v>397</v>
-      </c>
-      <c r="AK5" s="95" t="s">
-        <v>401</v>
-      </c>
-      <c r="AL5" s="95" t="s">
+      <c r="AJ6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AK6" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AL6" s="95" t="s">
         <v>405</v>
       </c>
-      <c r="AM5" s="95" t="s">
+      <c r="AM6" s="95" t="s">
         <v>414</v>
       </c>
-      <c r="AN5" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A6" s="95" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="95" t="s">
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="B7" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="95" t="s">
+      <c r="C7" s="95" t="s">
         <v>195</v>
       </c>
-      <c r="D6" s="95" t="s">
+      <c r="D7" s="95" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="F6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="G6" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="H6" s="95" t="s">
+      <c r="H7" s="95" t="s">
         <v>224</v>
       </c>
-      <c r="K6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="L6" s="95" t="s">
+      <c r="L7" s="95" t="s">
         <v>236</v>
       </c>
-      <c r="M6" s="95" t="s">
+      <c r="M7" s="95" t="s">
         <v>243</v>
       </c>
-      <c r="N6" s="95" t="s">
+      <c r="N7" s="95" t="s">
         <v>262</v>
       </c>
-      <c r="O6" s="95" t="s">
+      <c r="O7" s="95" t="s">
         <v>270</v>
       </c>
-      <c r="P6" s="95" t="s">
+      <c r="P7" s="95" t="s">
         <v>277</v>
       </c>
-      <c r="Q6" s="95" t="s">
-        <v>283</v>
-      </c>
-      <c r="R6" s="95" t="s">
+      <c r="Q7" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="R7" s="95" t="s">
         <v>288</v>
       </c>
-      <c r="U6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="V7" s="95" t="s">
         <v>305</v>
       </c>
-      <c r="X6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="Z6" s="95" t="s">
+      <c r="Z7" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="AA6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AB6" s="95" t="s">
+      <c r="AB7" s="95" t="s">
         <v>333</v>
       </c>
-      <c r="AC6" s="95" t="s">
-        <v>340</v>
-      </c>
-      <c r="AD6" s="95" t="s">
+      <c r="AC7" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD7" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="AE6" s="95" t="s">
+      <c r="AE7" s="95" t="s">
         <v>358</v>
       </c>
-      <c r="AG6" s="95" t="s">
+      <c r="AG7" s="95" t="s">
         <v>369</v>
       </c>
-      <c r="AH6" s="95" t="s">
-        <v>377</v>
-      </c>
-      <c r="AI6" s="95" t="s">
+      <c r="AH7" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AI7" s="95" t="s">
         <v>382</v>
       </c>
-      <c r="AJ6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AK6" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AL6" s="95" t="s">
+      <c r="AL7" s="95" t="s">
         <v>406</v>
       </c>
-      <c r="AM6" s="95" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A7" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="95" t="s">
+      <c r="AM7" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="B8" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="C8" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="D8" s="95" t="s">
         <v>202</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="G8" s="95" t="s">
         <v>217</v>
       </c>
-      <c r="H7" s="95" t="s">
-        <v>225</v>
-      </c>
-      <c r="L7" s="95" t="s">
+      <c r="H8" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="L8" s="95" t="s">
         <v>237</v>
       </c>
-      <c r="M7" s="95" t="s">
+      <c r="M8" s="95" t="s">
         <v>244</v>
       </c>
-      <c r="N7" s="95" t="s">
+      <c r="N8" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="O7" s="95" t="s">
+      <c r="O8" s="95" t="s">
         <v>271</v>
       </c>
-      <c r="P7" s="95" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q7" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="R7" s="95" t="s">
+      <c r="P8" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="R8" s="95" t="s">
         <v>289</v>
       </c>
-      <c r="V7" s="95" t="s">
+      <c r="V8" s="95" t="s">
         <v>306</v>
       </c>
-      <c r="Z7" s="95" t="s">
+      <c r="Z8" s="95" t="s">
         <v>321</v>
       </c>
-      <c r="AB7" s="95" t="s">
+      <c r="AB8" s="95" t="s">
         <v>334</v>
       </c>
-      <c r="AC7" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AD7" s="95" t="s">
+      <c r="AD8" s="95" t="s">
         <v>346</v>
       </c>
-      <c r="AE7" s="95" t="s">
+      <c r="AE8" s="95" t="s">
         <v>359</v>
       </c>
-      <c r="AG7" s="95" t="s">
+      <c r="AG8" s="95" t="s">
         <v>370</v>
       </c>
-      <c r="AH7" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AI7" s="95" t="s">
+      <c r="AI8" s="95" t="s">
         <v>383</v>
       </c>
-      <c r="AL7" s="95" t="s">
+      <c r="AL8" s="95" t="s">
         <v>407</v>
       </c>
-      <c r="AM7" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="B8" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="C8" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>203</v>
-      </c>
-      <c r="G8" s="95" t="s">
+    </row>
+    <row r="9" spans="1:41">
+      <c r="D9" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="G9" s="95" t="s">
         <v>218</v>
       </c>
-      <c r="H8" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="L8" s="95" t="s">
-        <v>238</v>
-      </c>
-      <c r="M8" s="95" t="s">
+      <c r="L9" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="M9" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="N8" s="95" t="s">
+      <c r="N9" s="95" t="s">
         <v>264</v>
       </c>
-      <c r="O8" s="95" t="s">
-        <v>272</v>
-      </c>
-      <c r="P8" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="R8" s="95" t="s">
+      <c r="O9" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="R9" s="95" t="s">
         <v>290</v>
       </c>
-      <c r="V8" s="95" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z8" s="95" t="s">
+      <c r="V9" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z9" s="95" t="s">
         <v>322</v>
       </c>
-      <c r="AB8" s="95" t="s">
-        <v>335</v>
-      </c>
-      <c r="AD8" s="95" t="s">
+      <c r="AB9" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD9" s="95" t="s">
         <v>347</v>
       </c>
-      <c r="AE8" s="95" t="s">
+      <c r="AE9" s="95" t="s">
         <v>360</v>
       </c>
-      <c r="AG8" s="95" t="s">
+      <c r="AG9" s="95" t="s">
         <v>371</v>
       </c>
-      <c r="AI8" s="95" t="s">
+      <c r="AI9" s="95" t="s">
         <v>384</v>
       </c>
-      <c r="AL8" s="95" t="s">
+      <c r="AL9" s="95" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="D9" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="G9" s="95" t="s">
-        <v>219</v>
-      </c>
-      <c r="L9" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="M9" s="95" t="s">
+    <row r="10" spans="1:41">
+      <c r="G10" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="M10" s="95" t="s">
         <v>246</v>
       </c>
-      <c r="N9" s="95" t="s">
-        <v>265</v>
-      </c>
-      <c r="O9" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="R9" s="95" t="s">
+      <c r="N10" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="R10" s="95" t="s">
         <v>291</v>
       </c>
-      <c r="V9" t="s">
-        <v>539</v>
-      </c>
-      <c r="Z9" s="95" t="s">
+      <c r="Z10" s="95" t="s">
         <v>323</v>
       </c>
-      <c r="AB9" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AD9" s="95" t="s">
+      <c r="AD10" s="95" t="s">
         <v>348</v>
       </c>
-      <c r="AE9" s="95" t="s">
-        <v>361</v>
-      </c>
-      <c r="AG9" s="95" t="s">
-        <v>372</v>
-      </c>
-      <c r="AI9" s="95" t="s">
+      <c r="AE10" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AG10" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AI10" s="95" t="s">
         <v>385</v>
       </c>
-      <c r="AL9" s="95" t="s">
+      <c r="AL10" s="95" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="G10" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="M10" s="95" t="s">
+    <row r="11" spans="1:41">
+      <c r="M11" s="95" t="s">
         <v>247</v>
       </c>
-      <c r="N10" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="R10" s="95" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z10" s="95" t="s">
-        <v>324</v>
-      </c>
-      <c r="AD10" s="95" t="s">
+      <c r="R11" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z11" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD11" s="95" t="s">
         <v>349</v>
       </c>
-      <c r="AE10" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AG10" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AI10" s="95" t="s">
+      <c r="AI11" s="95" t="s">
         <v>386</v>
       </c>
-      <c r="AL10" s="95" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M11" s="95" t="s">
+      <c r="AL11" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="M12" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="R11" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="Z11" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AD11" s="95" t="s">
+      <c r="AD12" s="95" t="s">
         <v>350</v>
       </c>
-      <c r="AI11" s="95" t="s">
+      <c r="AI12" s="95" t="s">
         <v>387</v>
       </c>
-      <c r="AL11" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M12" s="95" t="s">
+    </row>
+    <row r="13" spans="1:41">
+      <c r="M13" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="AD12" s="95" t="s">
+      <c r="AD13" s="95" t="s">
         <v>351</v>
       </c>
-      <c r="AI12" s="95" t="s">
+      <c r="AI13" s="95" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M13" s="95" t="s">
+    <row r="14" spans="1:41">
+      <c r="M14" s="95" t="s">
         <v>250</v>
       </c>
-      <c r="AD13" s="95" t="s">
+      <c r="AD14" s="95" t="s">
         <v>352</v>
       </c>
-      <c r="AI13" s="95" t="s">
+      <c r="AI14" s="95" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M14" s="95" t="s">
+    <row r="15" spans="1:41">
+      <c r="M15" s="95" t="s">
         <v>251</v>
       </c>
-      <c r="AD14" s="95" t="s">
-        <v>353</v>
-      </c>
-      <c r="AI14" s="95" t="s">
+      <c r="AD15" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="AI15" s="95" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M15" s="95" t="s">
+    <row r="16" spans="1:41">
+      <c r="M16" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="AD15" s="116" t="s">
-        <v>539</v>
-      </c>
-      <c r="AI15" s="95" t="s">
+      <c r="AI16" s="95" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M16" s="95" t="s">
+    <row r="17" spans="13:35">
+      <c r="M17" s="95" t="s">
         <v>253</v>
       </c>
-      <c r="AI16" s="95" t="s">
+      <c r="AI17" s="95" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="17" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M17" s="95" t="s">
+    <row r="18" spans="13:35">
+      <c r="M18" s="95" t="s">
         <v>254</v>
       </c>
-      <c r="AI17" s="95" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M18" s="95" t="s">
+      <c r="AI18" s="116" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="19" spans="13:35">
+      <c r="M19" s="95" t="s">
         <v>255</v>
       </c>
-      <c r="AI18" s="116" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="19" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M19" s="95" t="s">
+    </row>
+    <row r="20" spans="13:35">
+      <c r="M20" s="95" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M20" s="95" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="21" spans="13:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="13:35">
       <c r="M21" s="116" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18431"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="28810"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\asset\assetImport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/asset/assetImport/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="38400" windowHeight="20220"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20220"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <definedName name="资金来源">设备分类!$D$2:$D$6</definedName>
     <definedName name="风险等级">设备分类!$E$2:$E$6</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="150001" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -103,7 +103,7 @@
     <author>Tang, Quan (GE Healthcare)</author>
   </authors>
   <commentList>
-    <comment ref="A7" authorId="0" shapeId="0">
+    <comment ref="A7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>tie:each(items="assetList", var="asset", length="1" allowAdd="True")</t>
         </r>
@@ -127,7 +127,7 @@
     <author>Luan, Da (GE Healthcare)</author>
   </authors>
   <commentList>
-    <comment ref="E4" authorId="0" shapeId="0">
+    <comment ref="E4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2392,9 +2392,6 @@
     <t>生命体征监护类</t>
   </si>
   <si>
-    <t>XXXXXX</t>
-  </si>
-  <si>
     <t>2010国家编码</t>
   </si>
   <si>
@@ -2457,11 +2454,14 @@
   <si>
     <t>${asset.departNum}</t>
   </si>
+  <si>
+    <t>${asset.name}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="6">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
@@ -2470,7 +2470,7 @@
     <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00;[$¥-804]\-#,##0.00"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.14993743705557422"/>
@@ -2755,13 +2755,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3556,7 +3549,19 @@
     <cellStyle name="Total counts" xfId="14"/>
     <cellStyle name="常规 2" xfId="15"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="115">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -4299,14 +4304,14 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Warehouse Inventory" defaultPivotStyle="PivotStyleMedium2">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="114"/>
+      <tableStyleElement type="headerRow" dxfId="113"/>
+    </tableStyle>
+    <tableStyle name="Warehouse Inventory" pivot="0" count="4">
       <tableStyleElement type="wholeTable" dxfId="112"/>
       <tableStyleElement type="headerRow" dxfId="111"/>
-    </tableStyle>
-    <tableStyle name="Warehouse Inventory" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="110"/>
-      <tableStyleElement type="headerRow" dxfId="109"/>
-      <tableStyleElement type="lastColumn" dxfId="108"/>
-      <tableStyleElement type="secondRowStripe" dxfId="107"/>
+      <tableStyleElement type="lastColumn" dxfId="110"/>
+      <tableStyleElement type="secondRowStripe" dxfId="109"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4341,7 +4346,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory Pick List worksheet"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4438,7 +4443,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4535,7 +4540,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4612,64 +4617,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="78" totalsRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="80" totalsRowDxfId="79">
   <sortState ref="A3:D8">
     <sortCondition ref="B2:B8"/>
   </sortState>
   <tableColumns count="53">
-    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="76" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="78" dataCellStyle="Table details left aligned"/>
     <tableColumn id="2" name="设备名称" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="11" name="设备别名" dataDxfId="75" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="11" name="设备别名" dataDxfId="77" dataCellStyle="Table details left aligned"/>
     <tableColumn id="3" name="维修负责人" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="32" name="维修负责人2" dataDxfId="74" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="32" name="维修负责人2" dataDxfId="76" dataCellStyle="Table details left aligned"/>
     <tableColumn id="50" name="维修负责人3" dataCellStyle="Table details left aligned"/>
     <tableColumn id="5" name="使用科室" dataCellStyle="Table details left aligned"/>
     <tableColumn id="8" name="制造商" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="73" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="52" name="设备标准名称" dataDxfId="72" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="35" name="注册证号" dataDxfId="71" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="7" name="供应商" dataDxfId="70" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="23" name="医疗器械分类" dataDxfId="69" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="4" name="医疗器械子分类" dataDxfId="68" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="24" name="设备分类" dataDxfId="67" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="25" name="功能等级" dataDxfId="66" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="53" name="维修类型" dataDxfId="65" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="26" name="设备型号" dataDxfId="64" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="30" name="制造商序列号" dataDxfId="63" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="62" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="41" name="2010国家编码" dataDxfId="61" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="29" name="资产编号" dataDxfId="60" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="28" name="条码" dataDxfId="59" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="27" name="IT系统编号" dataDxfId="58" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="75" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="52" name="设备标准名称" dataDxfId="74" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="35" name="注册证号" dataDxfId="73" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="7" name="供应商" dataDxfId="72" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="23" name="医疗器械分类" dataDxfId="71" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="4" name="医疗器械子分类" dataDxfId="70" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="24" name="设备分类" dataDxfId="69" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="25" name="功能等级" dataDxfId="68" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="53" name="维修类型" dataDxfId="67" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="26" name="设备型号" dataDxfId="66" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="30" name="制造商序列号" dataDxfId="65" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="64" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="41" name="2010国家编码" dataDxfId="63" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="29" name="资产编号" dataDxfId="62" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="28" name="条码" dataDxfId="61" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="27" name="IT系统编号" dataDxfId="60" dataCellStyle="Table details right aligned"/>
     <tableColumn id="10" name="采购价格" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="13" name="最终残值" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="14" name="折旧算法" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="15" name="使用年限" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="16" name="出厂日期" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="17" name="采购日期" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="18" name="到货日期" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="19" name="启用日期" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="39" name="质保日期" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="20" name="维保截止日期" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="21" name="报废日期" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="22" name="上次维护日期" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="6" name="上次计量日期" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="12" name="上次质检日期" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="31" name="维护商" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="33" name="维护商电话" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="34" name="二维码" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="36" name="安装位置编码" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="37" name="安装位置" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="38" name="使用责任人" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="40" name="备注" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="42" name="用途分类" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="43" name="资金来源" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="44" name="风险等级" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="45" name="计量等级" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="46" name="计量项目类别" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="47" name="是否急救设备" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="48" name="是否进口设备" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="49" name="当前状态" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="13" name="最终残值" dataDxfId="59" totalsRowDxfId="58" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="14" name="折旧算法" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="15" name="使用年限" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="16" name="出厂日期" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="17" name="采购日期" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="18" name="到货日期" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="19" name="启用日期" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="39" name="质保日期" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="20" name="维保截止日期" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="21" name="报废日期" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="22" name="上次维护日期" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="6" name="上次计量日期" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="12" name="上次质检日期" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="31" name="维护商" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="33" name="维护商电话" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="34" name="二维码" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="36" name="安装位置编码" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="37" name="安装位置" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="38" name="使用责任人" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="40" name="备注" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="42" name="用途分类" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="43" name="资金来源" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="44" name="风险等级" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="45" name="计量等级" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="46" name="计量项目类别" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="47" name="是否急救设备" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="48" name="是否进口设备" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="49" name="当前状态" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Table details right aligned"/>
   </tableColumns>
   <tableStyleInfo name="Warehouse Inventory" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4924,62 +4929,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtInventoryList">
+  <sheetPr codeName="shtInventoryList" enableFormatConditionsCalculation="0">
     <tabColor theme="4"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BA100"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" style="105" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="105" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="105" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="105" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" style="113" customWidth="1"/>
-    <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" style="113" customWidth="1"/>
+    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="10" style="105" customWidth="1"/>
-    <col min="18" max="19" width="10.109375" customWidth="1"/>
-    <col min="20" max="20" width="19.109375" customWidth="1"/>
-    <col min="21" max="21" width="19.109375" style="105" customWidth="1"/>
+    <col min="18" max="19" width="10.1640625" customWidth="1"/>
+    <col min="20" max="20" width="19.1640625" customWidth="1"/>
+    <col min="21" max="21" width="19.1640625" style="105" customWidth="1"/>
     <col min="22" max="22" width="14.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.109375" customWidth="1"/>
+    <col min="23" max="24" width="10.1640625" customWidth="1"/>
     <col min="25" max="25" width="13.6640625" customWidth="1"/>
-    <col min="26" max="26" width="17.44140625" customWidth="1"/>
-    <col min="27" max="27" width="14.44140625" customWidth="1"/>
-    <col min="28" max="28" width="11.109375" customWidth="1"/>
+    <col min="26" max="26" width="17.5" customWidth="1"/>
+    <col min="27" max="27" width="14.5" customWidth="1"/>
+    <col min="28" max="28" width="11.1640625" customWidth="1"/>
     <col min="29" max="29" width="9" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" customWidth="1"/>
-    <col min="31" max="31" width="10.109375" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" customWidth="1"/>
-    <col min="33" max="33" width="11.44140625" style="105" customWidth="1"/>
-    <col min="34" max="34" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.5" customWidth="1"/>
+    <col min="31" max="31" width="10.1640625" customWidth="1"/>
+    <col min="32" max="32" width="11.5" customWidth="1"/>
+    <col min="33" max="33" width="11.5" style="105" customWidth="1"/>
+    <col min="34" max="34" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="13.33203125" customWidth="1"/>
     <col min="36" max="36" width="14.6640625" customWidth="1"/>
-    <col min="37" max="37" width="12.44140625" customWidth="1"/>
+    <col min="37" max="37" width="12.5" customWidth="1"/>
     <col min="38" max="38" width="12.6640625" customWidth="1"/>
     <col min="39" max="40" width="12.33203125" style="113" customWidth="1"/>
-    <col min="41" max="41" width="16.109375" style="113" customWidth="1"/>
-    <col min="42" max="42" width="12.77734375" style="113" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.109375" style="113" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.109375" style="113" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.1640625" style="113" customWidth="1"/>
+    <col min="42" max="42" width="12.83203125" style="113" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.1640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="11.6640625" customWidth="1"/>
-    <col min="51" max="52" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="27">
+    <row r="1" spans="1:53" ht="25" x14ac:dyDescent="0.15">
       <c r="A1" s="24" t="s">
         <v>43</v>
       </c>
@@ -4999,7 +5004,7 @@
       <c r="K1" s="124"/>
       <c r="L1" s="124"/>
     </row>
-    <row r="2" spans="1:53" ht="15.75">
+    <row r="2" spans="1:53" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="25" t="s">
         <v>44</v>
       </c>
@@ -5007,7 +5012,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2" s="124"/>
       <c r="E2" s="124"/>
@@ -5019,7 +5024,7 @@
       <c r="K2" s="124"/>
       <c r="L2" s="124"/>
     </row>
-    <row r="3" spans="1:53" ht="33.75" thickBot="1">
+    <row r="3" spans="1:53" ht="34" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -5076,7 +5081,7 @@
       <c r="AZ3" s="1"/>
       <c r="BA3" s="106"/>
     </row>
-    <row r="4" spans="1:53" ht="15.75">
+    <row r="4" spans="1:53" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5089,7 +5094,7 @@
       <c r="F4" s="11"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:53" ht="21">
+    <row r="5" spans="1:53" ht="20" x14ac:dyDescent="0.15">
       <c r="A5" s="120">
         <f>COUNTA('Asset List'!$B$7:$B$100)</f>
         <v>1</v>
@@ -5103,7 +5108,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
     </row>
-    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1">
+    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="30" t="s">
         <v>45</v>
       </c>
@@ -5117,7 +5122,7 @@
         <v>111</v>
       </c>
       <c r="E6" s="118" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F6" s="29" t="s">
         <v>515</v>
@@ -5129,10 +5134,10 @@
         <v>33</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K6" s="31" t="s">
         <v>112</v>
@@ -5153,7 +5158,7 @@
         <v>36</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R6" s="30" t="s">
         <v>113</v>
@@ -5165,7 +5170,7 @@
         <v>86</v>
       </c>
       <c r="U6" s="30" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>38</v>
@@ -5189,7 +5194,7 @@
         <v>21</v>
       </c>
       <c r="AC6" s="30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>23</v>
@@ -5261,15 +5266,15 @@
         <v>507</v>
       </c>
       <c r="BA6" s="109" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="7" spans="1:53" ht="15.75">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="B7" s="35" t="s">
         <v>547</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>532</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>114</v>
@@ -5364,10 +5369,10 @@
         <v>441</v>
       </c>
       <c r="BA7" s="23" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="8" spans="1:53" s="105" customFormat="1" ht="15.75">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="35"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -5422,7 +5427,7 @@
       <c r="AZ8" s="23"/>
       <c r="BA8" s="23"/>
     </row>
-    <row r="9" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="9" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="35"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -5477,7 +5482,7 @@
       <c r="AZ9" s="23"/>
       <c r="BA9" s="23"/>
     </row>
-    <row r="10" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="10" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="35"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -5532,7 +5537,7 @@
       <c r="AZ10" s="23"/>
       <c r="BA10" s="23"/>
     </row>
-    <row r="11" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="11" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="35"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -5587,7 +5592,7 @@
       <c r="AZ11" s="23"/>
       <c r="BA11" s="23"/>
     </row>
-    <row r="12" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="12" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="35"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -5642,7 +5647,7 @@
       <c r="AZ12" s="23"/>
       <c r="BA12" s="23"/>
     </row>
-    <row r="13" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="13" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="35"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -5697,7 +5702,7 @@
       <c r="AZ13" s="23"/>
       <c r="BA13" s="23"/>
     </row>
-    <row r="14" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="14" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="35"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -5752,7 +5757,7 @@
       <c r="AZ14" s="23"/>
       <c r="BA14" s="23"/>
     </row>
-    <row r="15" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="15" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="35"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -5807,7 +5812,7 @@
       <c r="AZ15" s="23"/>
       <c r="BA15" s="23"/>
     </row>
-    <row r="16" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="16" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="35"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -5862,7 +5867,7 @@
       <c r="AZ16" s="23"/>
       <c r="BA16" s="23"/>
     </row>
-    <row r="17" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="17" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="35"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -5917,7 +5922,7 @@
       <c r="AZ17" s="23"/>
       <c r="BA17" s="23"/>
     </row>
-    <row r="18" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="18" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="35"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -5972,7 +5977,7 @@
       <c r="AZ18" s="23"/>
       <c r="BA18" s="23"/>
     </row>
-    <row r="19" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="19" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="35"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -6027,7 +6032,7 @@
       <c r="AZ19" s="23"/>
       <c r="BA19" s="23"/>
     </row>
-    <row r="20" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="20" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="35"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -6082,7 +6087,7 @@
       <c r="AZ20" s="23"/>
       <c r="BA20" s="23"/>
     </row>
-    <row r="21" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="21" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="35"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -6137,7 +6142,7 @@
       <c r="AZ21" s="23"/>
       <c r="BA21" s="23"/>
     </row>
-    <row r="22" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="22" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="35"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -6192,7 +6197,7 @@
       <c r="AZ22" s="23"/>
       <c r="BA22" s="23"/>
     </row>
-    <row r="23" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="23" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="35"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -6247,7 +6252,7 @@
       <c r="AZ23" s="23"/>
       <c r="BA23" s="23"/>
     </row>
-    <row r="24" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="24" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="35"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -6302,7 +6307,7 @@
       <c r="AZ24" s="23"/>
       <c r="BA24" s="23"/>
     </row>
-    <row r="25" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="25" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A25" s="35"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -6357,7 +6362,7 @@
       <c r="AZ25" s="23"/>
       <c r="BA25" s="23"/>
     </row>
-    <row r="26" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="26" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A26" s="35"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
@@ -6412,7 +6417,7 @@
       <c r="AZ26" s="23"/>
       <c r="BA26" s="23"/>
     </row>
-    <row r="27" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="27" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="35"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -6467,7 +6472,7 @@
       <c r="AZ27" s="23"/>
       <c r="BA27" s="23"/>
     </row>
-    <row r="28" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="28" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="35"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -6522,7 +6527,7 @@
       <c r="AZ28" s="23"/>
       <c r="BA28" s="23"/>
     </row>
-    <row r="29" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="29" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="35"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -6577,7 +6582,7 @@
       <c r="AZ29" s="23"/>
       <c r="BA29" s="23"/>
     </row>
-    <row r="30" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="30" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="35"/>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -6632,7 +6637,7 @@
       <c r="AZ30" s="23"/>
       <c r="BA30" s="23"/>
     </row>
-    <row r="31" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="31" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A31" s="35"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -6687,7 +6692,7 @@
       <c r="AZ31" s="23"/>
       <c r="BA31" s="23"/>
     </row>
-    <row r="32" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="32" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="35"/>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -6742,7 +6747,7 @@
       <c r="AZ32" s="23"/>
       <c r="BA32" s="23"/>
     </row>
-    <row r="33" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="33" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A33" s="35"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -6797,7 +6802,7 @@
       <c r="AZ33" s="23"/>
       <c r="BA33" s="23"/>
     </row>
-    <row r="34" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="34" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A34" s="35"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -6852,7 +6857,7 @@
       <c r="AZ34" s="23"/>
       <c r="BA34" s="23"/>
     </row>
-    <row r="35" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="35" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A35" s="35"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -6907,7 +6912,7 @@
       <c r="AZ35" s="23"/>
       <c r="BA35" s="23"/>
     </row>
-    <row r="36" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="36" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A36" s="35"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -6962,7 +6967,7 @@
       <c r="AZ36" s="23"/>
       <c r="BA36" s="23"/>
     </row>
-    <row r="37" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="37" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A37" s="35"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -7017,7 +7022,7 @@
       <c r="AZ37" s="23"/>
       <c r="BA37" s="23"/>
     </row>
-    <row r="38" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="38" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A38" s="35"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -7072,7 +7077,7 @@
       <c r="AZ38" s="23"/>
       <c r="BA38" s="23"/>
     </row>
-    <row r="39" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="39" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A39" s="35"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -7127,7 +7132,7 @@
       <c r="AZ39" s="23"/>
       <c r="BA39" s="23"/>
     </row>
-    <row r="40" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="40" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A40" s="35"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -7182,7 +7187,7 @@
       <c r="AZ40" s="23"/>
       <c r="BA40" s="23"/>
     </row>
-    <row r="41" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="41" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A41" s="35"/>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -7237,7 +7242,7 @@
       <c r="AZ41" s="23"/>
       <c r="BA41" s="23"/>
     </row>
-    <row r="42" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="42" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A42" s="35"/>
       <c r="B42" s="34"/>
       <c r="C42" s="34"/>
@@ -7292,7 +7297,7 @@
       <c r="AZ42" s="23"/>
       <c r="BA42" s="23"/>
     </row>
-    <row r="43" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="43" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A43" s="35"/>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -7347,7 +7352,7 @@
       <c r="AZ43" s="23"/>
       <c r="BA43" s="23"/>
     </row>
-    <row r="44" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="44" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A44" s="35"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -7402,7 +7407,7 @@
       <c r="AZ44" s="23"/>
       <c r="BA44" s="23"/>
     </row>
-    <row r="45" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="45" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A45" s="35"/>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -7457,7 +7462,7 @@
       <c r="AZ45" s="23"/>
       <c r="BA45" s="23"/>
     </row>
-    <row r="46" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="46" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="35"/>
       <c r="B46" s="34"/>
       <c r="C46" s="34"/>
@@ -7512,7 +7517,7 @@
       <c r="AZ46" s="23"/>
       <c r="BA46" s="23"/>
     </row>
-    <row r="47" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="47" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="35"/>
       <c r="B47" s="34"/>
       <c r="C47" s="34"/>
@@ -7567,7 +7572,7 @@
       <c r="AZ47" s="23"/>
       <c r="BA47" s="23"/>
     </row>
-    <row r="48" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="48" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="35"/>
       <c r="B48" s="34"/>
       <c r="C48" s="34"/>
@@ -7622,7 +7627,7 @@
       <c r="AZ48" s="23"/>
       <c r="BA48" s="23"/>
     </row>
-    <row r="49" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="49" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="35"/>
       <c r="B49" s="34"/>
       <c r="C49" s="34"/>
@@ -7677,7 +7682,7 @@
       <c r="AZ49" s="23"/>
       <c r="BA49" s="23"/>
     </row>
-    <row r="50" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="50" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="35"/>
       <c r="B50" s="34"/>
       <c r="C50" s="34"/>
@@ -7732,7 +7737,7 @@
       <c r="AZ50" s="23"/>
       <c r="BA50" s="23"/>
     </row>
-    <row r="51" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="51" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A51" s="35"/>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
@@ -7787,7 +7792,7 @@
       <c r="AZ51" s="23"/>
       <c r="BA51" s="23"/>
     </row>
-    <row r="52" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="52" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A52" s="35"/>
       <c r="B52" s="34"/>
       <c r="C52" s="34"/>
@@ -7842,7 +7847,7 @@
       <c r="AZ52" s="23"/>
       <c r="BA52" s="23"/>
     </row>
-    <row r="53" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="53" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="35"/>
       <c r="B53" s="34"/>
       <c r="C53" s="34"/>
@@ -7897,7 +7902,7 @@
       <c r="AZ53" s="23"/>
       <c r="BA53" s="23"/>
     </row>
-    <row r="54" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="54" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="35"/>
       <c r="B54" s="34"/>
       <c r="C54" s="34"/>
@@ -7952,7 +7957,7 @@
       <c r="AZ54" s="23"/>
       <c r="BA54" s="23"/>
     </row>
-    <row r="55" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="55" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="35"/>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -8007,7 +8012,7 @@
       <c r="AZ55" s="23"/>
       <c r="BA55" s="23"/>
     </row>
-    <row r="56" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="56" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="35"/>
       <c r="B56" s="34"/>
       <c r="C56" s="34"/>
@@ -8062,7 +8067,7 @@
       <c r="AZ56" s="23"/>
       <c r="BA56" s="23"/>
     </row>
-    <row r="57" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="57" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="35"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -8117,7 +8122,7 @@
       <c r="AZ57" s="23"/>
       <c r="BA57" s="23"/>
     </row>
-    <row r="58" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="58" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A58" s="35"/>
       <c r="B58" s="34"/>
       <c r="C58" s="34"/>
@@ -8172,7 +8177,7 @@
       <c r="AZ58" s="23"/>
       <c r="BA58" s="23"/>
     </row>
-    <row r="59" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="59" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="35"/>
       <c r="B59" s="34"/>
       <c r="C59" s="34"/>
@@ -8227,7 +8232,7 @@
       <c r="AZ59" s="23"/>
       <c r="BA59" s="23"/>
     </row>
-    <row r="60" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="60" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A60" s="35"/>
       <c r="B60" s="34"/>
       <c r="C60" s="34"/>
@@ -8282,7 +8287,7 @@
       <c r="AZ60" s="23"/>
       <c r="BA60" s="23"/>
     </row>
-    <row r="61" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="61" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A61" s="35"/>
       <c r="B61" s="34"/>
       <c r="C61" s="34"/>
@@ -8337,7 +8342,7 @@
       <c r="AZ61" s="23"/>
       <c r="BA61" s="23"/>
     </row>
-    <row r="62" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="62" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A62" s="35"/>
       <c r="B62" s="34"/>
       <c r="C62" s="34"/>
@@ -8392,7 +8397,7 @@
       <c r="AZ62" s="23"/>
       <c r="BA62" s="23"/>
     </row>
-    <row r="63" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="63" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A63" s="35"/>
       <c r="B63" s="34"/>
       <c r="C63" s="34"/>
@@ -8447,7 +8452,7 @@
       <c r="AZ63" s="23"/>
       <c r="BA63" s="23"/>
     </row>
-    <row r="64" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="64" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A64" s="35"/>
       <c r="B64" s="34"/>
       <c r="C64" s="34"/>
@@ -8502,7 +8507,7 @@
       <c r="AZ64" s="23"/>
       <c r="BA64" s="23"/>
     </row>
-    <row r="65" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="65" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A65" s="35"/>
       <c r="B65" s="34"/>
       <c r="C65" s="34"/>
@@ -8557,7 +8562,7 @@
       <c r="AZ65" s="23"/>
       <c r="BA65" s="23"/>
     </row>
-    <row r="66" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="66" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A66" s="35"/>
       <c r="B66" s="34"/>
       <c r="C66" s="34"/>
@@ -8612,7 +8617,7 @@
       <c r="AZ66" s="23"/>
       <c r="BA66" s="23"/>
     </row>
-    <row r="67" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="67" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A67" s="35"/>
       <c r="B67" s="34"/>
       <c r="C67" s="34"/>
@@ -8667,7 +8672,7 @@
       <c r="AZ67" s="23"/>
       <c r="BA67" s="23"/>
     </row>
-    <row r="68" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="68" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A68" s="35"/>
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
@@ -8722,7 +8727,7 @@
       <c r="AZ68" s="23"/>
       <c r="BA68" s="23"/>
     </row>
-    <row r="69" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="69" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A69" s="35"/>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
@@ -8777,7 +8782,7 @@
       <c r="AZ69" s="23"/>
       <c r="BA69" s="23"/>
     </row>
-    <row r="70" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="70" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A70" s="35"/>
       <c r="B70" s="34"/>
       <c r="C70" s="34"/>
@@ -8832,7 +8837,7 @@
       <c r="AZ70" s="23"/>
       <c r="BA70" s="23"/>
     </row>
-    <row r="71" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="71" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A71" s="35"/>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -8887,7 +8892,7 @@
       <c r="AZ71" s="23"/>
       <c r="BA71" s="23"/>
     </row>
-    <row r="72" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="72" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A72" s="35"/>
       <c r="B72" s="34"/>
       <c r="C72" s="34"/>
@@ -8942,7 +8947,7 @@
       <c r="AZ72" s="23"/>
       <c r="BA72" s="23"/>
     </row>
-    <row r="73" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="73" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A73" s="35"/>
       <c r="B73" s="34"/>
       <c r="C73" s="34"/>
@@ -8997,7 +9002,7 @@
       <c r="AZ73" s="23"/>
       <c r="BA73" s="23"/>
     </row>
-    <row r="74" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="74" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A74" s="35"/>
       <c r="B74" s="34"/>
       <c r="C74" s="34"/>
@@ -9052,7 +9057,7 @@
       <c r="AZ74" s="23"/>
       <c r="BA74" s="23"/>
     </row>
-    <row r="75" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="75" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A75" s="35"/>
       <c r="B75" s="34"/>
       <c r="C75" s="34"/>
@@ -9107,7 +9112,7 @@
       <c r="AZ75" s="23"/>
       <c r="BA75" s="23"/>
     </row>
-    <row r="76" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="76" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A76" s="35"/>
       <c r="B76" s="34"/>
       <c r="C76" s="34"/>
@@ -9162,7 +9167,7 @@
       <c r="AZ76" s="23"/>
       <c r="BA76" s="23"/>
     </row>
-    <row r="77" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="77" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A77" s="35"/>
       <c r="B77" s="34"/>
       <c r="C77" s="34"/>
@@ -9217,7 +9222,7 @@
       <c r="AZ77" s="23"/>
       <c r="BA77" s="23"/>
     </row>
-    <row r="78" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="78" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A78" s="35"/>
       <c r="B78" s="34"/>
       <c r="C78" s="34"/>
@@ -9272,7 +9277,7 @@
       <c r="AZ78" s="23"/>
       <c r="BA78" s="23"/>
     </row>
-    <row r="79" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="79" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A79" s="35"/>
       <c r="B79" s="34"/>
       <c r="C79" s="34"/>
@@ -9327,7 +9332,7 @@
       <c r="AZ79" s="23"/>
       <c r="BA79" s="23"/>
     </row>
-    <row r="80" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="80" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A80" s="35"/>
       <c r="B80" s="34"/>
       <c r="C80" s="34"/>
@@ -9382,7 +9387,7 @@
       <c r="AZ80" s="23"/>
       <c r="BA80" s="23"/>
     </row>
-    <row r="81" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="81" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A81" s="35"/>
       <c r="B81" s="34"/>
       <c r="C81" s="34"/>
@@ -9437,7 +9442,7 @@
       <c r="AZ81" s="23"/>
       <c r="BA81" s="23"/>
     </row>
-    <row r="82" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="82" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A82" s="35"/>
       <c r="B82" s="34"/>
       <c r="C82" s="34"/>
@@ -9492,7 +9497,7 @@
       <c r="AZ82" s="23"/>
       <c r="BA82" s="23"/>
     </row>
-    <row r="83" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="83" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A83" s="35"/>
       <c r="B83" s="34"/>
       <c r="C83" s="34"/>
@@ -9547,7 +9552,7 @@
       <c r="AZ83" s="23"/>
       <c r="BA83" s="23"/>
     </row>
-    <row r="84" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="84" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A84" s="35"/>
       <c r="B84" s="34"/>
       <c r="C84" s="34"/>
@@ -9602,7 +9607,7 @@
       <c r="AZ84" s="23"/>
       <c r="BA84" s="23"/>
     </row>
-    <row r="85" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="85" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A85" s="35"/>
       <c r="B85" s="34"/>
       <c r="C85" s="34"/>
@@ -9657,7 +9662,7 @@
       <c r="AZ85" s="23"/>
       <c r="BA85" s="23"/>
     </row>
-    <row r="86" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="86" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A86" s="35"/>
       <c r="B86" s="34"/>
       <c r="C86" s="34"/>
@@ -9712,7 +9717,7 @@
       <c r="AZ86" s="23"/>
       <c r="BA86" s="23"/>
     </row>
-    <row r="87" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="87" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A87" s="35"/>
       <c r="B87" s="34"/>
       <c r="C87" s="34"/>
@@ -9767,7 +9772,7 @@
       <c r="AZ87" s="23"/>
       <c r="BA87" s="23"/>
     </row>
-    <row r="88" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="88" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A88" s="35"/>
       <c r="B88" s="34"/>
       <c r="C88" s="34"/>
@@ -9822,7 +9827,7 @@
       <c r="AZ88" s="23"/>
       <c r="BA88" s="23"/>
     </row>
-    <row r="89" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="89" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A89" s="35"/>
       <c r="B89" s="34"/>
       <c r="C89" s="34"/>
@@ -9877,7 +9882,7 @@
       <c r="AZ89" s="23"/>
       <c r="BA89" s="23"/>
     </row>
-    <row r="90" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="90" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A90" s="35"/>
       <c r="B90" s="34"/>
       <c r="C90" s="34"/>
@@ -9932,7 +9937,7 @@
       <c r="AZ90" s="23"/>
       <c r="BA90" s="23"/>
     </row>
-    <row r="91" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="91" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A91" s="35"/>
       <c r="B91" s="34"/>
       <c r="C91" s="34"/>
@@ -9987,7 +9992,7 @@
       <c r="AZ91" s="23"/>
       <c r="BA91" s="23"/>
     </row>
-    <row r="92" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="92" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="35"/>
       <c r="B92" s="34"/>
       <c r="C92" s="34"/>
@@ -10042,7 +10047,7 @@
       <c r="AZ92" s="23"/>
       <c r="BA92" s="23"/>
     </row>
-    <row r="93" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="93" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A93" s="35"/>
       <c r="B93" s="34"/>
       <c r="C93" s="34"/>
@@ -10097,7 +10102,7 @@
       <c r="AZ93" s="23"/>
       <c r="BA93" s="23"/>
     </row>
-    <row r="94" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="94" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A94" s="35"/>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -10152,7 +10157,7 @@
       <c r="AZ94" s="23"/>
       <c r="BA94" s="23"/>
     </row>
-    <row r="95" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="95" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A95" s="35"/>
       <c r="B95" s="34"/>
       <c r="C95" s="34"/>
@@ -10207,7 +10212,7 @@
       <c r="AZ95" s="23"/>
       <c r="BA95" s="23"/>
     </row>
-    <row r="96" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="96" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A96" s="35"/>
       <c r="B96" s="34"/>
       <c r="C96" s="34"/>
@@ -10262,7 +10267,7 @@
       <c r="AZ96" s="23"/>
       <c r="BA96" s="23"/>
     </row>
-    <row r="97" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="97" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A97" s="35"/>
       <c r="B97" s="34"/>
       <c r="C97" s="34"/>
@@ -10317,7 +10322,7 @@
       <c r="AZ97" s="23"/>
       <c r="BA97" s="23"/>
     </row>
-    <row r="98" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="98" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A98" s="35"/>
       <c r="B98" s="34"/>
       <c r="C98" s="34"/>
@@ -10372,7 +10377,7 @@
       <c r="AZ98" s="23"/>
       <c r="BA98" s="23"/>
     </row>
-    <row r="99" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="99" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A99" s="35"/>
       <c r="B99" s="34"/>
       <c r="C99" s="34"/>
@@ -10427,7 +10432,7 @@
       <c r="AZ99" s="23"/>
       <c r="BA99" s="23"/>
     </row>
-    <row r="100" spans="1:53" s="105" customFormat="1" ht="15.75">
+    <row r="100" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A100" s="35"/>
       <c r="B100" s="34"/>
       <c r="C100" s="34"/>
@@ -10488,22 +10493,22 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="D1 E4:F6 P7:R7">
-    <cfRule type="expression" dxfId="106" priority="78">
+    <cfRule type="expression" dxfId="108" priority="79">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="105" priority="51">
+    <cfRule type="expression" dxfId="107" priority="52">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:AI7 M7:N7">
-    <cfRule type="expression" dxfId="104" priority="49">
+    <cfRule type="expression" dxfId="106" priority="50">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7:AI7">
-    <cfRule type="dataBar" priority="50">
+    <cfRule type="dataBar" priority="51">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10517,12 +10522,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7">
-    <cfRule type="expression" dxfId="103" priority="47">
+    <cfRule type="expression" dxfId="105" priority="48">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7">
-    <cfRule type="dataBar" priority="48">
+    <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10536,17 +10541,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL7:AN7">
-    <cfRule type="expression" dxfId="102" priority="33">
+    <cfRule type="expression" dxfId="104" priority="34">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE7">
-    <cfRule type="expression" dxfId="101" priority="45">
+    <cfRule type="expression" dxfId="103" priority="46">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE7">
-    <cfRule type="dataBar" priority="46">
+    <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10560,12 +10565,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF7:AG7">
-    <cfRule type="expression" dxfId="100" priority="43">
+    <cfRule type="expression" dxfId="102" priority="44">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF7:AG7">
-    <cfRule type="dataBar" priority="44">
+    <cfRule type="dataBar" priority="45">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10579,12 +10584,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH7">
-    <cfRule type="expression" dxfId="99" priority="41">
+    <cfRule type="expression" dxfId="101" priority="42">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH7">
-    <cfRule type="dataBar" priority="42">
+    <cfRule type="dataBar" priority="43">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10598,12 +10603,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI7">
-    <cfRule type="expression" dxfId="98" priority="39">
+    <cfRule type="expression" dxfId="100" priority="40">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI7">
-    <cfRule type="dataBar" priority="40">
+    <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10617,12 +10622,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ7">
-    <cfRule type="expression" dxfId="97" priority="37">
+    <cfRule type="expression" dxfId="99" priority="38">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ7">
-    <cfRule type="dataBar" priority="38">
+    <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10636,12 +10641,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK7">
-    <cfRule type="expression" dxfId="96" priority="35">
+    <cfRule type="expression" dxfId="98" priority="36">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK7">
-    <cfRule type="dataBar" priority="36">
+    <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10655,7 +10660,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL7:AN7">
-    <cfRule type="dataBar" priority="34">
+    <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10669,92 +10674,92 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="95" priority="30">
+    <cfRule type="expression" dxfId="97" priority="31">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7">
-    <cfRule type="expression" dxfId="94" priority="28">
+    <cfRule type="expression" dxfId="96" priority="29">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:L7">
-    <cfRule type="expression" dxfId="93" priority="27">
+  <conditionalFormatting sqref="C7:L7">
+    <cfRule type="expression" dxfId="95" priority="28">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="expression" dxfId="92" priority="24">
+    <cfRule type="expression" dxfId="94" priority="25">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:A100">
-    <cfRule type="expression" dxfId="91" priority="1">
+    <cfRule type="expression" dxfId="93" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:R100">
-    <cfRule type="expression" dxfId="90" priority="22">
+    <cfRule type="expression" dxfId="92" priority="23">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S8:AI100 M8:N100">
-    <cfRule type="expression" dxfId="89" priority="20">
+    <cfRule type="expression" dxfId="91" priority="21">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD8:AD100">
-    <cfRule type="expression" dxfId="88" priority="18">
+    <cfRule type="expression" dxfId="90" priority="19">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL8:AN100">
-    <cfRule type="expression" dxfId="87" priority="4">
+    <cfRule type="expression" dxfId="89" priority="5">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE8:AE100">
-    <cfRule type="expression" dxfId="86" priority="16">
+    <cfRule type="expression" dxfId="88" priority="17">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF8:AG100">
-    <cfRule type="expression" dxfId="85" priority="14">
+    <cfRule type="expression" dxfId="87" priority="15">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH8:AH100">
-    <cfRule type="expression" dxfId="84" priority="12">
+    <cfRule type="expression" dxfId="86" priority="13">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8:AI100">
-    <cfRule type="expression" dxfId="83" priority="10">
+    <cfRule type="expression" dxfId="85" priority="11">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8:AJ100">
-    <cfRule type="expression" dxfId="82" priority="8">
+    <cfRule type="expression" dxfId="84" priority="9">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK100">
-    <cfRule type="expression" dxfId="81" priority="6">
+    <cfRule type="expression" dxfId="83" priority="7">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O100">
-    <cfRule type="expression" dxfId="80" priority="3">
+    <cfRule type="expression" dxfId="82" priority="4">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:L100">
-    <cfRule type="expression" dxfId="79" priority="2">
+    <cfRule type="expression" dxfId="81" priority="3">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y8:AI100">
-    <cfRule type="dataBar" priority="105">
+    <cfRule type="dataBar" priority="106">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10768,7 +10773,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD8:AD100">
-    <cfRule type="dataBar" priority="106">
+    <cfRule type="dataBar" priority="107">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10782,7 +10787,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE8:AE100">
-    <cfRule type="dataBar" priority="107">
+    <cfRule type="dataBar" priority="108">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10796,7 +10801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF8:AG100">
-    <cfRule type="dataBar" priority="108">
+    <cfRule type="dataBar" priority="109">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10810,7 +10815,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH8:AH100">
-    <cfRule type="dataBar" priority="109">
+    <cfRule type="dataBar" priority="110">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10824,7 +10829,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8:AI100">
-    <cfRule type="dataBar" priority="110">
+    <cfRule type="dataBar" priority="111">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10838,7 +10843,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8:AJ100">
-    <cfRule type="dataBar" priority="111">
+    <cfRule type="dataBar" priority="112">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10852,7 +10857,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK100">
-    <cfRule type="dataBar" priority="112">
+    <cfRule type="dataBar" priority="113">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10866,7 +10871,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL8:AN100">
-    <cfRule type="dataBar" priority="113">
+    <cfRule type="dataBar" priority="114">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10877,6 +10882,11 @@
           <x14:id>{EA52B864-D138-4792-8F1D-43027CA9A6EF}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="17">
@@ -11138,150 +11148,150 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtPickList">
+  <sheetPr codeName="shtPickList" enableFormatConditionsCalculation="0">
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A40"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.75" thickBot="1">
+    <row r="1" spans="1:1" ht="34" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="13"/>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="119" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="14"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="14"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="14"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="14"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="14"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="14"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="14"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="14"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="14"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="14"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="14"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="14"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="14"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="14"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="14"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="14"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="14"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33" s="14"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34" s="14"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35" s="14"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A36" s="14"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A37" s="14"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A38" s="14"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A39" s="14"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A40" s="14"/>
     </row>
   </sheetData>
@@ -11304,19 +11314,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtBinLookup">
+  <sheetPr codeName="shtBinLookup" enableFormatConditionsCalculation="0">
     <tabColor theme="4" tint="-0.499984740745262"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.75" thickBot="1">
+    <row r="1" spans="1:5" ht="34" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -11324,16 +11334,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -11350,7 +11360,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
@@ -11367,7 +11377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
@@ -11384,207 +11394,207 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="14"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="14"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="14"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -11615,16 +11625,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="57" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="57" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="57"/>
-    <col min="4" max="4" width="27.77734375" style="57" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="57"/>
+    <col min="3" max="3" width="8.83203125" style="57"/>
+    <col min="4" max="4" width="27.83203125" style="57" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" thickBot="1">
+    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="125" t="s">
         <v>147</v>
       </c>
@@ -11632,7 +11642,7 @@
       <c r="C1" s="125"/>
       <c r="D1" s="125"/>
     </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1">
+    <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>148</v>
       </c>
@@ -11646,7 +11656,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A3" s="60">
         <v>1</v>
       </c>
@@ -11658,7 +11668,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1">
+    <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="64">
         <v>2</v>
       </c>
@@ -11670,13 +11680,13 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
+    <row r="5" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="68"/>
       <c r="B5" s="69"/>
       <c r="C5" s="70"/>
       <c r="D5" s="70"/>
     </row>
-    <row r="6" spans="1:4" s="71" customFormat="1" ht="16.5" thickBot="1">
+    <row r="6" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="126" t="s">
         <v>155</v>
       </c>
@@ -11684,7 +11694,7 @@
       <c r="C6" s="127"/>
       <c r="D6" s="128"/>
     </row>
-    <row r="7" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
+    <row r="7" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="72" t="s">
         <v>148</v>
       </c>
@@ -11698,7 +11708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5">
+    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A8" s="74">
         <v>3</v>
       </c>
@@ -11708,7 +11718,7 @@
       <c r="C8" s="76"/>
       <c r="D8" s="77"/>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A9" s="60">
         <v>4</v>
       </c>
@@ -11718,7 +11728,7 @@
       <c r="C9" s="78"/>
       <c r="D9" s="79"/>
     </row>
-    <row r="10" spans="1:4" ht="17.25" thickBot="1">
+    <row r="10" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="60">
         <v>5</v>
       </c>
@@ -11728,7 +11738,7 @@
       <c r="C10" s="78"/>
       <c r="D10" s="79"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A11" s="74">
         <v>6</v>
       </c>
@@ -11738,7 +11748,7 @@
       <c r="C11" s="78"/>
       <c r="D11" s="79"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5">
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A12" s="60">
         <v>7</v>
       </c>
@@ -11748,7 +11758,7 @@
       <c r="C12" s="78"/>
       <c r="D12" s="79"/>
     </row>
-    <row r="13" spans="1:4" ht="17.25" thickBot="1">
+    <row r="13" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="60">
         <v>8</v>
       </c>
@@ -11758,7 +11768,7 @@
       <c r="C13" s="78"/>
       <c r="D13" s="79"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="74">
         <v>9</v>
       </c>
@@ -11768,7 +11778,7 @@
       <c r="C14" s="78"/>
       <c r="D14" s="79"/>
     </row>
-    <row r="15" spans="1:4" ht="16.5">
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A15" s="60">
         <v>10</v>
       </c>
@@ -11778,7 +11788,7 @@
       <c r="C15" s="78"/>
       <c r="D15" s="79"/>
     </row>
-    <row r="16" spans="1:4" ht="17.25" thickBot="1">
+    <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="60">
         <v>11</v>
       </c>
@@ -11790,7 +11800,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="16.5">
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A17" s="74">
         <v>12</v>
       </c>
@@ -11800,7 +11810,7 @@
       <c r="C17" s="78"/>
       <c r="D17" s="79"/>
     </row>
-    <row r="18" spans="1:4" ht="16.5">
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A18" s="60">
         <v>13</v>
       </c>
@@ -11810,7 +11820,7 @@
       <c r="C18" s="78"/>
       <c r="D18" s="79"/>
     </row>
-    <row r="19" spans="1:4" ht="17.25" thickBot="1">
+    <row r="19" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="60">
         <v>14</v>
       </c>
@@ -11820,7 +11830,7 @@
       <c r="C19" s="78"/>
       <c r="D19" s="79"/>
     </row>
-    <row r="20" spans="1:4" ht="16.5">
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.15">
       <c r="A20" s="74">
         <v>15</v>
       </c>
@@ -11830,7 +11840,7 @@
       <c r="C20" s="78"/>
       <c r="D20" s="79"/>
     </row>
-    <row r="21" spans="1:4" ht="17.25" thickBot="1">
+    <row r="21" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="60">
         <v>16</v>
       </c>
@@ -11840,10 +11850,10 @@
       <c r="C21" s="80"/>
       <c r="D21" s="81"/>
     </row>
-    <row r="22" spans="1:4" ht="16.5" thickBot="1">
+    <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="82"/>
     </row>
-    <row r="23" spans="1:4" ht="16.5" thickBot="1">
+    <row r="23" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="129" t="s">
         <v>171</v>
       </c>
@@ -11851,7 +11861,7 @@
       <c r="C23" s="130"/>
       <c r="D23" s="131"/>
     </row>
-    <row r="24" spans="1:4" ht="17.25" thickBot="1">
+    <row r="24" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="83" t="s">
         <v>148</v>
       </c>
@@ -11865,7 +11875,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" thickBot="1">
+    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="60">
         <v>17</v>
       </c>
@@ -11877,7 +11887,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16.5" thickBot="1">
+    <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="60">
         <v>18</v>
       </c>
@@ -11889,7 +11899,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="60">
         <v>19</v>
       </c>
@@ -11901,7 +11911,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" thickBot="1">
+    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="60">
         <v>20</v>
       </c>
@@ -11931,19 +11941,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr enableFormatConditionsCalculation="0">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="52" customWidth="1"/>
+    <col min="1" max="1" width="19.5" style="52" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="132" t="s">
         <v>121</v>
       </c>
@@ -11955,7 +11965,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="132"/>
       <c r="B2" s="38" t="s">
         <v>124</v>
@@ -11965,7 +11975,7 @@
       </c>
       <c r="D2" s="132"/>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="45" t="s">
         <v>45</v>
       </c>
@@ -11975,7 +11985,7 @@
       </c>
       <c r="D3" s="41"/>
     </row>
-    <row r="4" spans="1:4" ht="16.5">
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="39" t="s">
         <v>13</v>
       </c>
@@ -11987,7 +11997,7 @@
       </c>
       <c r="D4" s="41"/>
     </row>
-    <row r="5" spans="1:4" ht="16.5">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="43" t="s">
         <v>15</v>
       </c>
@@ -11995,7 +12005,7 @@
       <c r="C5" s="44"/>
       <c r="D5" s="41"/>
     </row>
-    <row r="6" spans="1:4" ht="16.5">
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A6" s="45" t="s">
         <v>128</v>
       </c>
@@ -12007,7 +12017,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5">
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="43" t="s">
         <v>131</v>
       </c>
@@ -12015,7 +12025,7 @@
       <c r="C7" s="46"/>
       <c r="D7" s="41"/>
     </row>
-    <row r="8" spans="1:4" ht="16.5">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A8" s="45" t="s">
         <v>132</v>
       </c>
@@ -12025,7 +12035,7 @@
       </c>
       <c r="D8" s="41"/>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A9" s="48" t="s">
         <v>33</v>
       </c>
@@ -12037,7 +12047,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A10" s="45" t="s">
         <v>135</v>
       </c>
@@ -12047,7 +12057,7 @@
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A11" s="43" t="s">
         <v>18</v>
       </c>
@@ -12055,7 +12065,7 @@
       <c r="C11" s="47"/>
       <c r="D11" s="41"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5">
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A12" s="45" t="s">
         <v>34</v>
       </c>
@@ -12065,7 +12075,7 @@
       </c>
       <c r="D12" s="41"/>
     </row>
-    <row r="13" spans="1:4" ht="16.5">
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A13" s="39" t="s">
         <v>35</v>
       </c>
@@ -12077,7 +12087,7 @@
       </c>
       <c r="D13" s="41"/>
     </row>
-    <row r="14" spans="1:4" ht="16.5">
+    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="43" t="s">
         <v>36</v>
       </c>
@@ -12085,7 +12095,7 @@
       <c r="C14" s="47"/>
       <c r="D14" s="41"/>
     </row>
-    <row r="15" spans="1:4" ht="16.5">
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="45" t="s">
         <v>137</v>
       </c>
@@ -12095,7 +12105,7 @@
       </c>
       <c r="D15" s="41"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5">
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="43" t="s">
         <v>37</v>
       </c>
@@ -12103,7 +12113,7 @@
       <c r="C16" s="47"/>
       <c r="D16" s="41"/>
     </row>
-    <row r="17" spans="1:4" ht="16.5">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="45" t="s">
         <v>138</v>
       </c>
@@ -12113,7 +12123,7 @@
       </c>
       <c r="D17" s="41"/>
     </row>
-    <row r="18" spans="1:4" ht="16.5">
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="45" t="s">
         <v>38</v>
       </c>
@@ -12123,7 +12133,7 @@
       </c>
       <c r="D18" s="41"/>
     </row>
-    <row r="19" spans="1:4" ht="16.5">
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="43" t="s">
         <v>39</v>
       </c>
@@ -12131,7 +12141,7 @@
       <c r="C19" s="47"/>
       <c r="D19" s="41"/>
     </row>
-    <row r="20" spans="1:4" ht="16.5">
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="45" t="s">
         <v>40</v>
       </c>
@@ -12141,7 +12151,7 @@
       </c>
       <c r="D20" s="41"/>
     </row>
-    <row r="21" spans="1:4" ht="16.5">
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="48" t="s">
         <v>12</v>
       </c>
@@ -12151,7 +12161,7 @@
       </c>
       <c r="D21" s="41"/>
     </row>
-    <row r="22" spans="1:4" ht="16.5">
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="43" t="s">
         <v>19</v>
       </c>
@@ -12159,7 +12169,7 @@
       <c r="C22" s="47"/>
       <c r="D22" s="41"/>
     </row>
-    <row r="23" spans="1:4" ht="16.5">
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="43" t="s">
         <v>20</v>
       </c>
@@ -12167,7 +12177,7 @@
       <c r="C23" s="47"/>
       <c r="D23" s="41"/>
     </row>
-    <row r="24" spans="1:4" ht="16.5">
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="43" t="s">
         <v>21</v>
       </c>
@@ -12175,7 +12185,7 @@
       <c r="C24" s="47"/>
       <c r="D24" s="41"/>
     </row>
-    <row r="25" spans="1:4" ht="16.5">
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="43" t="s">
         <v>22</v>
       </c>
@@ -12183,7 +12193,7 @@
       <c r="C25" s="47"/>
       <c r="D25" s="41"/>
     </row>
-    <row r="26" spans="1:4" ht="16.5">
+    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -12191,7 +12201,7 @@
       <c r="C26" s="47"/>
       <c r="D26" s="41"/>
     </row>
-    <row r="27" spans="1:4" ht="16.5">
+    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="43" t="s">
         <v>24</v>
       </c>
@@ -12199,7 +12209,7 @@
       <c r="C27" s="47"/>
       <c r="D27" s="41"/>
     </row>
-    <row r="28" spans="1:4" ht="16.5">
+    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="45" t="s">
         <v>25</v>
       </c>
@@ -12209,7 +12219,7 @@
       </c>
       <c r="D28" s="41"/>
     </row>
-    <row r="29" spans="1:4" ht="16.5">
+    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="45" t="s">
         <v>26</v>
       </c>
@@ -12219,7 +12229,7 @@
       </c>
       <c r="D29" s="41"/>
     </row>
-    <row r="30" spans="1:4" ht="16.5">
+    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="43" t="s">
         <v>27</v>
       </c>
@@ -12227,7 +12237,7 @@
       <c r="C30" s="47"/>
       <c r="D30" s="41"/>
     </row>
-    <row r="31" spans="1:4" ht="16.5">
+    <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="43" t="s">
         <v>28</v>
       </c>
@@ -12235,7 +12245,7 @@
       <c r="C31" s="47"/>
       <c r="D31" s="41"/>
     </row>
-    <row r="32" spans="1:4" ht="16.5">
+    <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="43" t="s">
         <v>29</v>
       </c>
@@ -12243,7 +12253,7 @@
       <c r="C32" s="47"/>
       <c r="D32" s="41"/>
     </row>
-    <row r="33" spans="1:4" ht="16.5">
+    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="43" t="s">
         <v>30</v>
       </c>
@@ -12251,7 +12261,7 @@
       <c r="C33" s="47"/>
       <c r="D33" s="41"/>
     </row>
-    <row r="34" spans="1:4" ht="16.5">
+    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="43" t="s">
         <v>31</v>
       </c>
@@ -12259,7 +12269,7 @@
       <c r="C34" s="47"/>
       <c r="D34" s="41"/>
     </row>
-    <row r="35" spans="1:4" ht="16.5">
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="43" t="s">
         <v>32</v>
       </c>
@@ -12267,7 +12277,7 @@
       <c r="C35" s="47"/>
       <c r="D35" s="41"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5">
+    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="50" t="s">
         <v>140</v>
       </c>
@@ -12277,12 +12287,12 @@
       </c>
       <c r="D36" s="41"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="52" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="53"/>
       <c r="B40" t="s">
         <v>142</v>
@@ -12291,7 +12301,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="55"/>
       <c r="B41" t="s">
         <v>144</v>
@@ -12300,7 +12310,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="56"/>
       <c r="B42" t="s">
         <v>145</v>
@@ -12317,12 +12327,12 @@
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12339,17 +12349,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="27" customFormat="1">
+    <row r="1" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="96" t="s">
         <v>427</v>
       </c>
@@ -12387,10 +12397,10 @@
         <v>496</v>
       </c>
       <c r="M1" s="122" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="95" t="s">
         <v>420</v>
       </c>
@@ -12428,10 +12438,10 @@
         <v>488</v>
       </c>
       <c r="M2" s="116" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="95" t="s">
         <v>421</v>
       </c>
@@ -12469,10 +12479,10 @@
         <v>489</v>
       </c>
       <c r="M3" s="116" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="95" t="s">
         <v>422</v>
       </c>
@@ -12492,10 +12502,10 @@
         <v>446</v>
       </c>
       <c r="G4" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H4" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I4" s="99" t="s">
         <v>452</v>
@@ -12510,10 +12520,10 @@
         <v>490</v>
       </c>
       <c r="M4" s="116" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="95" t="s">
         <v>423</v>
       </c>
@@ -12521,7 +12531,7 @@
         <v>423</v>
       </c>
       <c r="C5" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D5" s="95" t="s">
         <v>440</v>
@@ -12539,7 +12549,7 @@
         <v>484</v>
       </c>
       <c r="K5" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L5" s="107" t="s">
         <v>491</v>
@@ -12548,7 +12558,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="116" t="s">
         <v>527</v>
       </c>
@@ -12556,19 +12566,19 @@
         <v>527</v>
       </c>
       <c r="D6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I6" s="99" t="s">
         <v>454</v>
       </c>
       <c r="J6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L6" s="107" t="s">
         <v>492</v>
@@ -12577,7 +12587,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="116" t="s">
         <v>528</v>
       </c>
@@ -12591,10 +12601,10 @@
         <v>493</v>
       </c>
       <c r="M7" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="116" t="s">
         <v>529</v>
       </c>
@@ -12605,10 +12615,10 @@
         <v>456</v>
       </c>
       <c r="L8" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="95" t="s">
         <v>424</v>
       </c>
@@ -12619,7 +12629,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="95" t="s">
         <v>425</v>
       </c>
@@ -12630,7 +12640,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="117" t="s">
         <v>526</v>
       </c>
@@ -12642,7 +12652,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="117" t="s">
         <v>530</v>
       </c>
@@ -12654,7 +12664,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="117" t="s">
         <v>531</v>
       </c>
@@ -12666,7 +12676,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="95" t="s">
         <v>426</v>
       </c>
@@ -12678,145 +12688,145 @@
         <v>462</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B15" s="116"/>
       <c r="H15" s="107"/>
       <c r="I15" s="99" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B16" s="107"/>
       <c r="H16" s="107"/>
       <c r="I16" s="99" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B17" s="107"/>
       <c r="H17" s="107"/>
       <c r="I17" s="99" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="107"/>
       <c r="H18" s="107"/>
       <c r="I18" s="99" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="107"/>
       <c r="H19" s="107"/>
       <c r="I19" s="99" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B20" s="107"/>
       <c r="H20" s="107"/>
       <c r="I20" s="99" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B21" s="107"/>
       <c r="H21" s="107"/>
       <c r="I21" s="99" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B22" s="107"/>
       <c r="H22" s="107"/>
       <c r="I22" s="99" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="107"/>
       <c r="H23" s="107"/>
       <c r="I23" s="99" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B24" s="107"/>
       <c r="H24" s="107"/>
       <c r="I24" s="99" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="107"/>
       <c r="H25" s="107"/>
       <c r="I25" s="99" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H26" s="107"/>
       <c r="I26" s="99" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H27" s="107"/>
       <c r="I27" s="99" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H28" s="107"/>
       <c r="I28" s="99" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="2:9">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H29" s="107"/>
       <c r="I29" s="99" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="2:9">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H30" s="107"/>
       <c r="I30" s="99" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H31" s="107"/>
       <c r="I31" s="99" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H32" s="107"/>
       <c r="I32" s="99" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="8:9">
+    <row r="33" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H33" s="107"/>
       <c r="I33" s="99" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="34" spans="8:9">
+    <row r="34" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H34" s="107"/>
       <c r="I34" s="115" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="35" spans="8:9">
+    <row r="35" spans="8:9" x14ac:dyDescent="0.15">
       <c r="I35" s="115" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="36" spans="8:9">
+    <row r="36" spans="8:9" x14ac:dyDescent="0.15">
       <c r="I36" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -12829,134 +12839,134 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="107" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="107" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="107" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="107" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="107" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="107" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="107" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="107" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="107" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="107" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="107" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="107" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="107" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="107" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="107" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="107" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="107" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="107" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="107" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="107" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="107" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="107" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="107" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="105"/>
     </row>
   </sheetData>
@@ -12967,47 +12977,47 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.5" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>418</v>
       </c>
@@ -13042,7 +13052,7 @@
         <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="M1" t="s">
         <v>54</v>
@@ -13075,7 +13085,7 @@
         <v>63</v>
       </c>
       <c r="W1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="X1" t="s">
         <v>64</v>
@@ -13129,10 +13139,10 @@
         <v>80</v>
       </c>
       <c r="AO1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A2" s="95" t="s">
         <v>180</v>
       </c>
@@ -13161,7 +13171,7 @@
         <v>225</v>
       </c>
       <c r="J2" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K2" s="95" t="s">
         <v>227</v>
@@ -13254,7 +13264,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A3" s="95" t="s">
         <v>181</v>
       </c>
@@ -13310,7 +13320,7 @@
         <v>293</v>
       </c>
       <c r="T3" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U3" t="s">
         <v>297</v>
@@ -13373,7 +13383,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A4" s="95" t="s">
         <v>182</v>
       </c>
@@ -13399,7 +13409,7 @@
         <v>221</v>
       </c>
       <c r="I4" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K4" s="95" t="s">
         <v>229</v>
@@ -13435,13 +13445,13 @@
         <v>302</v>
       </c>
       <c r="W4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="X4" s="95" t="s">
         <v>311</v>
       </c>
       <c r="Y4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z4" s="95" t="s">
         <v>317</v>
@@ -13489,7 +13499,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A5" s="95" t="s">
         <v>183</v>
       </c>
@@ -13539,7 +13549,7 @@
         <v>286</v>
       </c>
       <c r="S5" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U5" t="s">
         <v>299</v>
@@ -13569,7 +13579,7 @@
         <v>356</v>
       </c>
       <c r="AF5" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG5" s="95" t="s">
         <v>367</v>
@@ -13593,10 +13603,10 @@
         <v>413</v>
       </c>
       <c r="AN5" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A6" s="95" t="s">
         <v>179</v>
       </c>
@@ -13610,10 +13620,10 @@
         <v>200</v>
       </c>
       <c r="E6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G6" s="95" t="s">
         <v>215</v>
@@ -13622,7 +13632,7 @@
         <v>223</v>
       </c>
       <c r="K6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L6" s="95" t="s">
         <v>235</v>
@@ -13646,19 +13656,19 @@
         <v>287</v>
       </c>
       <c r="U6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="V6" t="s">
         <v>304</v>
       </c>
       <c r="X6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z6" s="95" t="s">
         <v>319</v>
       </c>
       <c r="AA6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AB6" s="95" t="s">
         <v>332</v>
@@ -13682,10 +13692,10 @@
         <v>381</v>
       </c>
       <c r="AJ6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AK6" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AL6" s="95" t="s">
         <v>405</v>
@@ -13694,9 +13704,9 @@
         <v>414</v>
       </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A7" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B7" s="95" t="s">
         <v>189</v>
@@ -13729,7 +13739,7 @@
         <v>277</v>
       </c>
       <c r="Q7" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R7" s="95" t="s">
         <v>288</v>
@@ -13744,7 +13754,7 @@
         <v>333</v>
       </c>
       <c r="AC7" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD7" s="95" t="s">
         <v>345</v>
@@ -13756,7 +13766,7 @@
         <v>369</v>
       </c>
       <c r="AH7" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AI7" s="95" t="s">
         <v>382</v>
@@ -13765,15 +13775,15 @@
         <v>406</v>
       </c>
       <c r="AM7" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B8" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C8" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D8" s="95" t="s">
         <v>202</v>
@@ -13782,7 +13792,7 @@
         <v>217</v>
       </c>
       <c r="H8" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L8" s="95" t="s">
         <v>237</v>
@@ -13797,7 +13807,7 @@
         <v>271</v>
       </c>
       <c r="P8" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R8" s="95" t="s">
         <v>289</v>
@@ -13827,15 +13837,15 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.15">
       <c r="D9" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G9" s="95" t="s">
         <v>218</v>
       </c>
       <c r="L9" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M9" s="95" t="s">
         <v>245</v>
@@ -13844,19 +13854,19 @@
         <v>264</v>
       </c>
       <c r="O9" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R9" s="95" t="s">
         <v>290</v>
       </c>
       <c r="V9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z9" s="95" t="s">
         <v>322</v>
       </c>
       <c r="AB9" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD9" s="95" t="s">
         <v>347</v>
@@ -13874,15 +13884,15 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
       <c r="G10" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M10" s="95" t="s">
         <v>246</v>
       </c>
       <c r="N10" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R10" s="95" t="s">
         <v>291</v>
@@ -13894,10 +13904,10 @@
         <v>348</v>
       </c>
       <c r="AE10" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG10" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AI10" s="95" t="s">
         <v>385</v>
@@ -13906,15 +13916,15 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M11" s="95" t="s">
         <v>247</v>
       </c>
       <c r="R11" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z11" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD11" s="95" t="s">
         <v>349</v>
@@ -13923,10 +13933,10 @@
         <v>386</v>
       </c>
       <c r="AL11" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M12" s="95" t="s">
         <v>248</v>
       </c>
@@ -13937,7 +13947,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="13" spans="1:41">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M13" s="95" t="s">
         <v>249</v>
       </c>
@@ -13948,7 +13958,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:41">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M14" s="95" t="s">
         <v>250</v>
       </c>
@@ -13959,18 +13969,18 @@
         <v>389</v>
       </c>
     </row>
-    <row r="15" spans="1:41">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M15" s="95" t="s">
         <v>251</v>
       </c>
       <c r="AD15" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AI15" s="95" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="16" spans="1:41">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
       <c r="M16" s="95" t="s">
         <v>252</v>
       </c>
@@ -13978,7 +13988,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="17" spans="13:35">
+    <row r="17" spans="13:35" x14ac:dyDescent="0.15">
       <c r="M17" s="95" t="s">
         <v>253</v>
       </c>
@@ -13986,27 +13996,27 @@
         <v>392</v>
       </c>
     </row>
-    <row r="18" spans="13:35">
+    <row r="18" spans="13:35" x14ac:dyDescent="0.15">
       <c r="M18" s="95" t="s">
         <v>254</v>
       </c>
       <c r="AI18" s="116" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="19" spans="13:35">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="19" spans="13:35" x14ac:dyDescent="0.15">
       <c r="M19" s="95" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="20" spans="13:35">
+    <row r="20" spans="13:35" x14ac:dyDescent="0.15">
       <c r="M20" s="95" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="21" spans="13:35">
+    <row r="21" spans="13:35" x14ac:dyDescent="0.15">
       <c r="M21" s="116" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="28810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18431"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/asset/assetImport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\asset\assetImport\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20220"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="38400" windowHeight="20220"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <definedName name="资金来源">设备分类!$D$2:$D$6</definedName>
     <definedName name="风险等级">设备分类!$E$2:$E$6</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -103,7 +103,7 @@
     <author>Tang, Quan (GE Healthcare)</author>
   </authors>
   <commentList>
-    <comment ref="A7" authorId="0">
+    <comment ref="A7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>tie:each(items="assetList", var="asset", length="1" allowAdd="True")</t>
+          <t>tie:each(items="assetList", var="asset")</t>
         </r>
       </text>
     </comment>
@@ -127,7 +127,7 @@
     <author>Luan, Da (GE Healthcare)</author>
   </authors>
   <commentList>
-    <comment ref="E4" authorId="0">
+    <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="538">
   <si>
     <t>设备列表</t>
   </si>
@@ -518,24 +518,6 @@
       <t>设备型号</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>XXXX</t>
-  </si>
-  <si>
-    <t>XXX医疗器械有限公司</t>
-  </si>
-  <si>
-    <t>XX医疗设备有限公司</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>平均年限</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -828,10 +810,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>放射科</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>眼科手术用其他器械</t>
   </si>
   <si>
@@ -1963,12 +1941,6 @@
   </si>
   <si>
     <t>非计量设备</t>
-  </si>
-  <si>
-    <t>急救设备</t>
-  </si>
-  <si>
-    <t>二级</t>
   </si>
   <si>
     <t>医用CT</t>
@@ -2352,10 +2324,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>张三</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>医疗器械分类</t>
   </si>
   <si>
@@ -2461,7 +2429,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
@@ -2470,7 +2438,7 @@
     <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00;[$¥-804]\-#,##0.00"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.14993743705557422"/>
@@ -3549,19 +3517,7 @@
     <cellStyle name="Total counts" xfId="14"/>
     <cellStyle name="常规 2" xfId="15"/>
   </cellStyles>
-  <dxfs count="115">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="114">
     <dxf>
       <font>
         <b/>
@@ -4246,6 +4202,12 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-4.9989318521683403E-2"/>
@@ -4304,14 +4266,14 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Warehouse Inventory" defaultPivotStyle="PivotStyleMedium2">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
-      <tableStyleElement type="wholeTable" dxfId="114"/>
-      <tableStyleElement type="headerRow" dxfId="113"/>
+      <tableStyleElement type="wholeTable" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
     </tableStyle>
     <tableStyle name="Warehouse Inventory" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="112"/>
-      <tableStyleElement type="headerRow" dxfId="111"/>
-      <tableStyleElement type="lastColumn" dxfId="110"/>
-      <tableStyleElement type="secondRowStripe" dxfId="109"/>
+      <tableStyleElement type="wholeTable" dxfId="111"/>
+      <tableStyleElement type="headerRow" dxfId="110"/>
+      <tableStyleElement type="lastColumn" dxfId="109"/>
+      <tableStyleElement type="secondRowStripe" dxfId="108"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4346,7 +4308,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory Pick List worksheet"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4443,7 +4405,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4540,7 +4502,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4617,64 +4579,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="80" totalsRowDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryList" displayName="InventoryList" ref="A6:BA100" headerRowDxfId="78" totalsRowDxfId="77">
   <sortState ref="A3:D8">
     <sortCondition ref="B2:B8"/>
   </sortState>
   <tableColumns count="53">
-    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="78" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="1" name="设备编号" totalsRowLabel="Totals" dataDxfId="76" dataCellStyle="Table details left aligned"/>
     <tableColumn id="2" name="设备名称" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="11" name="设备别名" dataDxfId="77" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="11" name="设备别名" dataDxfId="75" dataCellStyle="Table details left aligned"/>
     <tableColumn id="3" name="维修负责人" dataCellStyle="Table details left aligned"/>
-    <tableColumn id="32" name="维修负责人2" dataDxfId="76" dataCellStyle="Table details left aligned"/>
+    <tableColumn id="32" name="维修负责人2" dataDxfId="74" dataCellStyle="Table details left aligned"/>
     <tableColumn id="50" name="维修负责人3" dataCellStyle="Table details left aligned"/>
     <tableColumn id="5" name="使用科室" dataCellStyle="Table details left aligned"/>
     <tableColumn id="8" name="制造商" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="75" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="52" name="设备标准名称" dataDxfId="74" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="35" name="注册证号" dataDxfId="73" dataCellStyle="Table details center aligned"/>
-    <tableColumn id="7" name="供应商" dataDxfId="72" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="23" name="医疗器械分类" dataDxfId="71" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="4" name="医疗器械子分类" dataDxfId="70" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="24" name="设备分类" dataDxfId="69" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="25" name="功能等级" dataDxfId="68" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="53" name="维修类型" dataDxfId="67" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="26" name="设备型号" dataDxfId="66" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="30" name="制造商序列号" dataDxfId="65" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="64" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="41" name="2010国家编码" dataDxfId="63" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="29" name="资产编号" dataDxfId="62" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="28" name="条码" dataDxfId="61" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="27" name="IT系统编号" dataDxfId="60" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="51" name="品牌/制造商简称" dataDxfId="73" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="52" name="设备标准名称" dataDxfId="72" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="35" name="注册证号" dataDxfId="71" dataCellStyle="Table details center aligned"/>
+    <tableColumn id="7" name="供应商" dataDxfId="70" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="23" name="医疗器械分类" dataDxfId="69" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="4" name="医疗器械子分类" dataDxfId="68" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="24" name="设备分类" dataDxfId="67" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="25" name="功能等级" dataDxfId="66" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="53" name="维修类型" dataDxfId="65" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="26" name="设备型号" dataDxfId="64" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="30" name="制造商序列号" dataDxfId="63" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="9" name="SystemID/厂商报修ID" dataDxfId="62" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="41" name="2010国家编码" dataDxfId="61" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="29" name="资产编号" dataDxfId="60" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="28" name="条码" dataDxfId="59" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="27" name="IT系统编号" dataDxfId="58" dataCellStyle="Table details right aligned"/>
     <tableColumn id="10" name="采购价格" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="13" name="最终残值" dataDxfId="59" totalsRowDxfId="58" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="14" name="折旧算法" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="15" name="使用年限" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="16" name="出厂日期" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="17" name="采购日期" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="18" name="到货日期" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="19" name="启用日期" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="39" name="质保日期" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="20" name="维保截止日期" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="21" name="报废日期" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="22" name="上次维护日期" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="6" name="上次计量日期" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="12" name="上次质检日期" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="31" name="维护商" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="33" name="维护商电话" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="34" name="二维码" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="36" name="安装位置编码" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="37" name="安装位置" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="38" name="使用责任人" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="40" name="备注" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="42" name="用途分类" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="43" name="资金来源" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="44" name="风险等级" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="45" name="计量等级" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="46" name="计量项目类别" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="47" name="是否急救设备" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="48" name="是否进口设备" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Table details right aligned"/>
-    <tableColumn id="49" name="当前状态" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="13" name="最终残值" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="14" name="折旧算法" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="15" name="使用年限" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="16" name="出厂日期" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="17" name="采购日期" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="18" name="到货日期" dataDxfId="47" totalsRowDxfId="46" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="19" name="启用日期" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="39" name="质保日期" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="20" name="维保截止日期" dataDxfId="41" totalsRowDxfId="40" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="21" name="报废日期" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="22" name="上次维护日期" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="6" name="上次计量日期" dataDxfId="35" totalsRowDxfId="34" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="12" name="上次质检日期" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="31" name="维护商" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="33" name="维护商电话" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="34" name="二维码" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="36" name="安装位置编码" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="37" name="安装位置" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="38" name="使用责任人" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="40" name="备注" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="42" name="用途分类" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="43" name="资金来源" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="44" name="风险等级" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="45" name="计量等级" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="46" name="计量项目类别" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="47" name="是否急救设备" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="48" name="是否进口设备" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Table details right aligned"/>
+    <tableColumn id="49" name="当前状态" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Table details right aligned"/>
   </tableColumns>
   <tableStyleInfo name="Warehouse Inventory" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4929,62 +4891,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtInventoryList" enableFormatConditionsCalculation="0">
+  <sheetPr codeName="shtInventoryList">
     <tabColor theme="4"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BA100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="105" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" style="105" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" style="105" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="105" customWidth="1"/>
-    <col min="11" max="11" width="9.1640625" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" style="113" customWidth="1"/>
-    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" style="113" customWidth="1"/>
+    <col min="13" max="13" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="10" style="105" customWidth="1"/>
-    <col min="18" max="19" width="10.1640625" customWidth="1"/>
-    <col min="20" max="20" width="19.1640625" customWidth="1"/>
-    <col min="21" max="21" width="19.1640625" style="105" customWidth="1"/>
+    <col min="18" max="19" width="10.109375" customWidth="1"/>
+    <col min="20" max="20" width="19.109375" customWidth="1"/>
+    <col min="21" max="21" width="19.109375" style="105" customWidth="1"/>
     <col min="22" max="22" width="14.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.1640625" customWidth="1"/>
+    <col min="23" max="24" width="10.109375" customWidth="1"/>
     <col min="25" max="25" width="13.6640625" customWidth="1"/>
-    <col min="26" max="26" width="17.5" customWidth="1"/>
-    <col min="27" max="27" width="14.5" customWidth="1"/>
-    <col min="28" max="28" width="11.1640625" customWidth="1"/>
+    <col min="26" max="26" width="17.44140625" customWidth="1"/>
+    <col min="27" max="27" width="14.44140625" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" customWidth="1"/>
     <col min="29" max="29" width="9" customWidth="1"/>
-    <col min="30" max="30" width="11.5" customWidth="1"/>
-    <col min="31" max="31" width="10.1640625" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
-    <col min="33" max="33" width="11.5" style="105" customWidth="1"/>
-    <col min="34" max="34" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" customWidth="1"/>
+    <col min="31" max="31" width="10.109375" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" customWidth="1"/>
+    <col min="33" max="33" width="11.44140625" style="105" customWidth="1"/>
+    <col min="34" max="34" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="13.33203125" customWidth="1"/>
     <col min="36" max="36" width="14.6640625" customWidth="1"/>
-    <col min="37" max="37" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="12.44140625" customWidth="1"/>
     <col min="38" max="38" width="12.6640625" customWidth="1"/>
     <col min="39" max="40" width="12.33203125" style="113" customWidth="1"/>
-    <col min="41" max="41" width="16.1640625" style="113" customWidth="1"/>
-    <col min="42" max="42" width="12.83203125" style="113" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.1640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.1640625" style="113" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.109375" style="113" customWidth="1"/>
+    <col min="42" max="42" width="12.77734375" style="113" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.109375" style="113" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" style="113" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="11.6640625" customWidth="1"/>
-    <col min="51" max="52" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:53" ht="27" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>43</v>
       </c>
@@ -4993,7 +4955,7 @@
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="123" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E1" s="124"/>
       <c r="F1" s="124"/>
@@ -5004,7 +4966,7 @@
       <c r="K1" s="124"/>
       <c r="L1" s="124"/>
     </row>
-    <row r="2" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:53" ht="15.75">
       <c r="A2" s="25" t="s">
         <v>44</v>
       </c>
@@ -5012,7 +4974,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="D2" s="124"/>
       <c r="E2" s="124"/>
@@ -5024,7 +4986,7 @@
       <c r="K2" s="124"/>
       <c r="L2" s="124"/>
     </row>
-    <row r="3" spans="1:53" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:53" ht="33.75" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -5081,7 +5043,7 @@
       <c r="AZ3" s="1"/>
       <c r="BA3" s="106"/>
     </row>
-    <row r="4" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:53" ht="15.75">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5094,21 +5056,15 @@
       <c r="F4" s="11"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:53" ht="20" x14ac:dyDescent="0.15">
-      <c r="A5" s="120">
-        <f>COUNTA('Asset List'!$B$7:$B$100)</f>
-        <v>1</v>
-      </c>
-      <c r="B5" s="121">
-        <f>SUM('Asset List'!$Y$7:$Y$100)</f>
-        <v>0</v>
-      </c>
+    <row r="5" spans="1:53" ht="21">
+      <c r="A5" s="120"/>
+      <c r="B5" s="121"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
     </row>
-    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:53" s="33" customFormat="1" ht="31.5" customHeight="1">
       <c r="A6" s="30" t="s">
         <v>45</v>
       </c>
@@ -5122,43 +5078,43 @@
         <v>111</v>
       </c>
       <c r="E6" s="118" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="K6" s="31" t="s">
         <v>112</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="M6" s="30" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="N6" s="93" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="O6" s="93" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>36</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="R6" s="30" t="s">
         <v>113</v>
@@ -5170,7 +5126,7 @@
         <v>86</v>
       </c>
       <c r="U6" s="30" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>38</v>
@@ -5194,7 +5150,7 @@
         <v>21</v>
       </c>
       <c r="AC6" s="30" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>23</v>
@@ -5203,10 +5159,10 @@
         <v>24</v>
       </c>
       <c r="AF6" s="93" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="AG6" s="93" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="AH6" s="30" t="s">
         <v>26</v>
@@ -5230,105 +5186,77 @@
         <v>32</v>
       </c>
       <c r="AO6" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="AP6" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="AQ6" s="32" t="s">
+        <v>490</v>
+      </c>
+      <c r="AR6" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="AS6" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="AT6" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="AU6" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="AV6" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="AW6" s="32" t="s">
+        <v>496</v>
+      </c>
+      <c r="AX6" s="109" t="s">
+        <v>436</v>
+      </c>
+      <c r="AY6" s="32" t="s">
         <v>497</v>
       </c>
-      <c r="AP6" s="32" t="s">
+      <c r="AZ6" s="32" t="s">
         <v>498</v>
       </c>
-      <c r="AQ6" s="32" t="s">
-        <v>499</v>
-      </c>
-      <c r="AR6" s="32" t="s">
-        <v>500</v>
-      </c>
-      <c r="AS6" s="32" t="s">
-        <v>501</v>
-      </c>
-      <c r="AT6" s="32" t="s">
-        <v>502</v>
-      </c>
-      <c r="AU6" s="32" t="s">
-        <v>503</v>
-      </c>
-      <c r="AV6" s="32" t="s">
-        <v>504</v>
-      </c>
-      <c r="AW6" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="AX6" s="109" t="s">
-        <v>443</v>
-      </c>
-      <c r="AY6" s="32" t="s">
-        <v>506</v>
-      </c>
-      <c r="AZ6" s="32" t="s">
-        <v>507</v>
-      </c>
       <c r="BA6" s="109" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="1:53" ht="14" x14ac:dyDescent="0.15">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="15.75">
       <c r="A7" s="35" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>547</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="110" t="s">
-        <v>519</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>9</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="34"/>
-      <c r="G7" s="94" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>115</v>
-      </c>
+      <c r="G7" s="94"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
       <c r="K7" s="16"/>
-      <c r="L7" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>426</v>
-      </c>
+      <c r="L7" s="28"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
-      <c r="R7" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="28" t="s">
-        <v>118</v>
-      </c>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
       <c r="V7" s="28"/>
       <c r="W7" s="17"/>
       <c r="X7" s="17"/>
-      <c r="Y7" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="36" t="s">
-        <v>119</v>
-      </c>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="18"/>
+      <c r="AA7" s="36"/>
       <c r="AB7" s="19"/>
       <c r="AC7" s="20"/>
       <c r="AD7" s="21"/>
@@ -5347,32 +5275,16 @@
       <c r="AQ7" s="114"/>
       <c r="AR7" s="114"/>
       <c r="AS7" s="114"/>
-      <c r="AT7" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="AU7" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="AV7" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="AW7" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="AX7" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="AY7" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="AZ7" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="BA7" s="23" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="8" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="AT7" s="23"/>
+      <c r="AU7" s="23"/>
+      <c r="AV7" s="23"/>
+      <c r="AW7" s="23"/>
+      <c r="AX7" s="23"/>
+      <c r="AY7" s="23"/>
+      <c r="AZ7" s="23"/>
+      <c r="BA7" s="23"/>
+    </row>
+    <row r="8" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A8" s="35"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -5427,7 +5339,7 @@
       <c r="AZ8" s="23"/>
       <c r="BA8" s="23"/>
     </row>
-    <row r="9" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A9" s="35"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -5482,7 +5394,7 @@
       <c r="AZ9" s="23"/>
       <c r="BA9" s="23"/>
     </row>
-    <row r="10" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A10" s="35"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -5537,7 +5449,7 @@
       <c r="AZ10" s="23"/>
       <c r="BA10" s="23"/>
     </row>
-    <row r="11" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A11" s="35"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -5592,7 +5504,7 @@
       <c r="AZ11" s="23"/>
       <c r="BA11" s="23"/>
     </row>
-    <row r="12" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A12" s="35"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -5647,7 +5559,7 @@
       <c r="AZ12" s="23"/>
       <c r="BA12" s="23"/>
     </row>
-    <row r="13" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A13" s="35"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -5702,7 +5614,7 @@
       <c r="AZ13" s="23"/>
       <c r="BA13" s="23"/>
     </row>
-    <row r="14" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A14" s="35"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -5757,7 +5669,7 @@
       <c r="AZ14" s="23"/>
       <c r="BA14" s="23"/>
     </row>
-    <row r="15" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A15" s="35"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -5812,7 +5724,7 @@
       <c r="AZ15" s="23"/>
       <c r="BA15" s="23"/>
     </row>
-    <row r="16" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A16" s="35"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -5867,7 +5779,7 @@
       <c r="AZ16" s="23"/>
       <c r="BA16" s="23"/>
     </row>
-    <row r="17" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A17" s="35"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -5922,7 +5834,7 @@
       <c r="AZ17" s="23"/>
       <c r="BA17" s="23"/>
     </row>
-    <row r="18" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A18" s="35"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -5977,7 +5889,7 @@
       <c r="AZ18" s="23"/>
       <c r="BA18" s="23"/>
     </row>
-    <row r="19" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A19" s="35"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -6032,7 +5944,7 @@
       <c r="AZ19" s="23"/>
       <c r="BA19" s="23"/>
     </row>
-    <row r="20" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A20" s="35"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -6087,7 +5999,7 @@
       <c r="AZ20" s="23"/>
       <c r="BA20" s="23"/>
     </row>
-    <row r="21" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A21" s="35"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -6142,7 +6054,7 @@
       <c r="AZ21" s="23"/>
       <c r="BA21" s="23"/>
     </row>
-    <row r="22" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A22" s="35"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -6197,7 +6109,7 @@
       <c r="AZ22" s="23"/>
       <c r="BA22" s="23"/>
     </row>
-    <row r="23" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A23" s="35"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -6252,7 +6164,7 @@
       <c r="AZ23" s="23"/>
       <c r="BA23" s="23"/>
     </row>
-    <row r="24" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A24" s="35"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -6307,7 +6219,7 @@
       <c r="AZ24" s="23"/>
       <c r="BA24" s="23"/>
     </row>
-    <row r="25" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A25" s="35"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -6362,7 +6274,7 @@
       <c r="AZ25" s="23"/>
       <c r="BA25" s="23"/>
     </row>
-    <row r="26" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A26" s="35"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
@@ -6417,7 +6329,7 @@
       <c r="AZ26" s="23"/>
       <c r="BA26" s="23"/>
     </row>
-    <row r="27" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A27" s="35"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -6472,7 +6384,7 @@
       <c r="AZ27" s="23"/>
       <c r="BA27" s="23"/>
     </row>
-    <row r="28" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A28" s="35"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
@@ -6527,7 +6439,7 @@
       <c r="AZ28" s="23"/>
       <c r="BA28" s="23"/>
     </row>
-    <row r="29" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A29" s="35"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -6582,7 +6494,7 @@
       <c r="AZ29" s="23"/>
       <c r="BA29" s="23"/>
     </row>
-    <row r="30" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A30" s="35"/>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
@@ -6637,7 +6549,7 @@
       <c r="AZ30" s="23"/>
       <c r="BA30" s="23"/>
     </row>
-    <row r="31" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A31" s="35"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -6692,7 +6604,7 @@
       <c r="AZ31" s="23"/>
       <c r="BA31" s="23"/>
     </row>
-    <row r="32" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A32" s="35"/>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -6747,7 +6659,7 @@
       <c r="AZ32" s="23"/>
       <c r="BA32" s="23"/>
     </row>
-    <row r="33" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A33" s="35"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -6802,7 +6714,7 @@
       <c r="AZ33" s="23"/>
       <c r="BA33" s="23"/>
     </row>
-    <row r="34" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A34" s="35"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -6857,7 +6769,7 @@
       <c r="AZ34" s="23"/>
       <c r="BA34" s="23"/>
     </row>
-    <row r="35" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A35" s="35"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -6912,7 +6824,7 @@
       <c r="AZ35" s="23"/>
       <c r="BA35" s="23"/>
     </row>
-    <row r="36" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A36" s="35"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -6967,7 +6879,7 @@
       <c r="AZ36" s="23"/>
       <c r="BA36" s="23"/>
     </row>
-    <row r="37" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A37" s="35"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -7022,7 +6934,7 @@
       <c r="AZ37" s="23"/>
       <c r="BA37" s="23"/>
     </row>
-    <row r="38" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A38" s="35"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -7077,7 +6989,7 @@
       <c r="AZ38" s="23"/>
       <c r="BA38" s="23"/>
     </row>
-    <row r="39" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A39" s="35"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -7132,7 +7044,7 @@
       <c r="AZ39" s="23"/>
       <c r="BA39" s="23"/>
     </row>
-    <row r="40" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A40" s="35"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -7187,7 +7099,7 @@
       <c r="AZ40" s="23"/>
       <c r="BA40" s="23"/>
     </row>
-    <row r="41" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A41" s="35"/>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -7242,7 +7154,7 @@
       <c r="AZ41" s="23"/>
       <c r="BA41" s="23"/>
     </row>
-    <row r="42" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A42" s="35"/>
       <c r="B42" s="34"/>
       <c r="C42" s="34"/>
@@ -7297,7 +7209,7 @@
       <c r="AZ42" s="23"/>
       <c r="BA42" s="23"/>
     </row>
-    <row r="43" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A43" s="35"/>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -7352,7 +7264,7 @@
       <c r="AZ43" s="23"/>
       <c r="BA43" s="23"/>
     </row>
-    <row r="44" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A44" s="35"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -7407,7 +7319,7 @@
       <c r="AZ44" s="23"/>
       <c r="BA44" s="23"/>
     </row>
-    <row r="45" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A45" s="35"/>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -7462,7 +7374,7 @@
       <c r="AZ45" s="23"/>
       <c r="BA45" s="23"/>
     </row>
-    <row r="46" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A46" s="35"/>
       <c r="B46" s="34"/>
       <c r="C46" s="34"/>
@@ -7517,7 +7429,7 @@
       <c r="AZ46" s="23"/>
       <c r="BA46" s="23"/>
     </row>
-    <row r="47" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A47" s="35"/>
       <c r="B47" s="34"/>
       <c r="C47" s="34"/>
@@ -7572,7 +7484,7 @@
       <c r="AZ47" s="23"/>
       <c r="BA47" s="23"/>
     </row>
-    <row r="48" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A48" s="35"/>
       <c r="B48" s="34"/>
       <c r="C48" s="34"/>
@@ -7627,7 +7539,7 @@
       <c r="AZ48" s="23"/>
       <c r="BA48" s="23"/>
     </row>
-    <row r="49" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A49" s="35"/>
       <c r="B49" s="34"/>
       <c r="C49" s="34"/>
@@ -7682,7 +7594,7 @@
       <c r="AZ49" s="23"/>
       <c r="BA49" s="23"/>
     </row>
-    <row r="50" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A50" s="35"/>
       <c r="B50" s="34"/>
       <c r="C50" s="34"/>
@@ -7737,7 +7649,7 @@
       <c r="AZ50" s="23"/>
       <c r="BA50" s="23"/>
     </row>
-    <row r="51" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A51" s="35"/>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
@@ -7792,7 +7704,7 @@
       <c r="AZ51" s="23"/>
       <c r="BA51" s="23"/>
     </row>
-    <row r="52" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A52" s="35"/>
       <c r="B52" s="34"/>
       <c r="C52" s="34"/>
@@ -7847,7 +7759,7 @@
       <c r="AZ52" s="23"/>
       <c r="BA52" s="23"/>
     </row>
-    <row r="53" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A53" s="35"/>
       <c r="B53" s="34"/>
       <c r="C53" s="34"/>
@@ -7902,7 +7814,7 @@
       <c r="AZ53" s="23"/>
       <c r="BA53" s="23"/>
     </row>
-    <row r="54" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A54" s="35"/>
       <c r="B54" s="34"/>
       <c r="C54" s="34"/>
@@ -7957,7 +7869,7 @@
       <c r="AZ54" s="23"/>
       <c r="BA54" s="23"/>
     </row>
-    <row r="55" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A55" s="35"/>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -8012,7 +7924,7 @@
       <c r="AZ55" s="23"/>
       <c r="BA55" s="23"/>
     </row>
-    <row r="56" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A56" s="35"/>
       <c r="B56" s="34"/>
       <c r="C56" s="34"/>
@@ -8067,7 +7979,7 @@
       <c r="AZ56" s="23"/>
       <c r="BA56" s="23"/>
     </row>
-    <row r="57" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A57" s="35"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -8122,7 +8034,7 @@
       <c r="AZ57" s="23"/>
       <c r="BA57" s="23"/>
     </row>
-    <row r="58" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A58" s="35"/>
       <c r="B58" s="34"/>
       <c r="C58" s="34"/>
@@ -8177,7 +8089,7 @@
       <c r="AZ58" s="23"/>
       <c r="BA58" s="23"/>
     </row>
-    <row r="59" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A59" s="35"/>
       <c r="B59" s="34"/>
       <c r="C59" s="34"/>
@@ -8232,7 +8144,7 @@
       <c r="AZ59" s="23"/>
       <c r="BA59" s="23"/>
     </row>
-    <row r="60" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A60" s="35"/>
       <c r="B60" s="34"/>
       <c r="C60" s="34"/>
@@ -8287,7 +8199,7 @@
       <c r="AZ60" s="23"/>
       <c r="BA60" s="23"/>
     </row>
-    <row r="61" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A61" s="35"/>
       <c r="B61" s="34"/>
       <c r="C61" s="34"/>
@@ -8342,7 +8254,7 @@
       <c r="AZ61" s="23"/>
       <c r="BA61" s="23"/>
     </row>
-    <row r="62" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A62" s="35"/>
       <c r="B62" s="34"/>
       <c r="C62" s="34"/>
@@ -8397,7 +8309,7 @@
       <c r="AZ62" s="23"/>
       <c r="BA62" s="23"/>
     </row>
-    <row r="63" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A63" s="35"/>
       <c r="B63" s="34"/>
       <c r="C63" s="34"/>
@@ -8452,7 +8364,7 @@
       <c r="AZ63" s="23"/>
       <c r="BA63" s="23"/>
     </row>
-    <row r="64" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A64" s="35"/>
       <c r="B64" s="34"/>
       <c r="C64" s="34"/>
@@ -8507,7 +8419,7 @@
       <c r="AZ64" s="23"/>
       <c r="BA64" s="23"/>
     </row>
-    <row r="65" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A65" s="35"/>
       <c r="B65" s="34"/>
       <c r="C65" s="34"/>
@@ -8562,7 +8474,7 @@
       <c r="AZ65" s="23"/>
       <c r="BA65" s="23"/>
     </row>
-    <row r="66" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A66" s="35"/>
       <c r="B66" s="34"/>
       <c r="C66" s="34"/>
@@ -8617,7 +8529,7 @@
       <c r="AZ66" s="23"/>
       <c r="BA66" s="23"/>
     </row>
-    <row r="67" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A67" s="35"/>
       <c r="B67" s="34"/>
       <c r="C67" s="34"/>
@@ -8672,7 +8584,7 @@
       <c r="AZ67" s="23"/>
       <c r="BA67" s="23"/>
     </row>
-    <row r="68" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A68" s="35"/>
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
@@ -8727,7 +8639,7 @@
       <c r="AZ68" s="23"/>
       <c r="BA68" s="23"/>
     </row>
-    <row r="69" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A69" s="35"/>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
@@ -8782,7 +8694,7 @@
       <c r="AZ69" s="23"/>
       <c r="BA69" s="23"/>
     </row>
-    <row r="70" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A70" s="35"/>
       <c r="B70" s="34"/>
       <c r="C70" s="34"/>
@@ -8837,7 +8749,7 @@
       <c r="AZ70" s="23"/>
       <c r="BA70" s="23"/>
     </row>
-    <row r="71" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A71" s="35"/>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -8892,7 +8804,7 @@
       <c r="AZ71" s="23"/>
       <c r="BA71" s="23"/>
     </row>
-    <row r="72" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A72" s="35"/>
       <c r="B72" s="34"/>
       <c r="C72" s="34"/>
@@ -8947,7 +8859,7 @@
       <c r="AZ72" s="23"/>
       <c r="BA72" s="23"/>
     </row>
-    <row r="73" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A73" s="35"/>
       <c r="B73" s="34"/>
       <c r="C73" s="34"/>
@@ -9002,7 +8914,7 @@
       <c r="AZ73" s="23"/>
       <c r="BA73" s="23"/>
     </row>
-    <row r="74" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A74" s="35"/>
       <c r="B74" s="34"/>
       <c r="C74" s="34"/>
@@ -9057,7 +8969,7 @@
       <c r="AZ74" s="23"/>
       <c r="BA74" s="23"/>
     </row>
-    <row r="75" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A75" s="35"/>
       <c r="B75" s="34"/>
       <c r="C75" s="34"/>
@@ -9112,7 +9024,7 @@
       <c r="AZ75" s="23"/>
       <c r="BA75" s="23"/>
     </row>
-    <row r="76" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A76" s="35"/>
       <c r="B76" s="34"/>
       <c r="C76" s="34"/>
@@ -9167,7 +9079,7 @@
       <c r="AZ76" s="23"/>
       <c r="BA76" s="23"/>
     </row>
-    <row r="77" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A77" s="35"/>
       <c r="B77" s="34"/>
       <c r="C77" s="34"/>
@@ -9222,7 +9134,7 @@
       <c r="AZ77" s="23"/>
       <c r="BA77" s="23"/>
     </row>
-    <row r="78" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A78" s="35"/>
       <c r="B78" s="34"/>
       <c r="C78" s="34"/>
@@ -9277,7 +9189,7 @@
       <c r="AZ78" s="23"/>
       <c r="BA78" s="23"/>
     </row>
-    <row r="79" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A79" s="35"/>
       <c r="B79" s="34"/>
       <c r="C79" s="34"/>
@@ -9332,7 +9244,7 @@
       <c r="AZ79" s="23"/>
       <c r="BA79" s="23"/>
     </row>
-    <row r="80" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A80" s="35"/>
       <c r="B80" s="34"/>
       <c r="C80" s="34"/>
@@ -9387,7 +9299,7 @@
       <c r="AZ80" s="23"/>
       <c r="BA80" s="23"/>
     </row>
-    <row r="81" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A81" s="35"/>
       <c r="B81" s="34"/>
       <c r="C81" s="34"/>
@@ -9442,7 +9354,7 @@
       <c r="AZ81" s="23"/>
       <c r="BA81" s="23"/>
     </row>
-    <row r="82" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A82" s="35"/>
       <c r="B82" s="34"/>
       <c r="C82" s="34"/>
@@ -9497,7 +9409,7 @@
       <c r="AZ82" s="23"/>
       <c r="BA82" s="23"/>
     </row>
-    <row r="83" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A83" s="35"/>
       <c r="B83" s="34"/>
       <c r="C83" s="34"/>
@@ -9552,7 +9464,7 @@
       <c r="AZ83" s="23"/>
       <c r="BA83" s="23"/>
     </row>
-    <row r="84" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A84" s="35"/>
       <c r="B84" s="34"/>
       <c r="C84" s="34"/>
@@ -9607,7 +9519,7 @@
       <c r="AZ84" s="23"/>
       <c r="BA84" s="23"/>
     </row>
-    <row r="85" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A85" s="35"/>
       <c r="B85" s="34"/>
       <c r="C85" s="34"/>
@@ -9662,7 +9574,7 @@
       <c r="AZ85" s="23"/>
       <c r="BA85" s="23"/>
     </row>
-    <row r="86" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A86" s="35"/>
       <c r="B86" s="34"/>
       <c r="C86" s="34"/>
@@ -9717,7 +9629,7 @@
       <c r="AZ86" s="23"/>
       <c r="BA86" s="23"/>
     </row>
-    <row r="87" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A87" s="35"/>
       <c r="B87" s="34"/>
       <c r="C87" s="34"/>
@@ -9772,7 +9684,7 @@
       <c r="AZ87" s="23"/>
       <c r="BA87" s="23"/>
     </row>
-    <row r="88" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A88" s="35"/>
       <c r="B88" s="34"/>
       <c r="C88" s="34"/>
@@ -9827,7 +9739,7 @@
       <c r="AZ88" s="23"/>
       <c r="BA88" s="23"/>
     </row>
-    <row r="89" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A89" s="35"/>
       <c r="B89" s="34"/>
       <c r="C89" s="34"/>
@@ -9882,7 +9794,7 @@
       <c r="AZ89" s="23"/>
       <c r="BA89" s="23"/>
     </row>
-    <row r="90" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A90" s="35"/>
       <c r="B90" s="34"/>
       <c r="C90" s="34"/>
@@ -9937,7 +9849,7 @@
       <c r="AZ90" s="23"/>
       <c r="BA90" s="23"/>
     </row>
-    <row r="91" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A91" s="35"/>
       <c r="B91" s="34"/>
       <c r="C91" s="34"/>
@@ -9992,7 +9904,7 @@
       <c r="AZ91" s="23"/>
       <c r="BA91" s="23"/>
     </row>
-    <row r="92" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A92" s="35"/>
       <c r="B92" s="34"/>
       <c r="C92" s="34"/>
@@ -10047,7 +9959,7 @@
       <c r="AZ92" s="23"/>
       <c r="BA92" s="23"/>
     </row>
-    <row r="93" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A93" s="35"/>
       <c r="B93" s="34"/>
       <c r="C93" s="34"/>
@@ -10102,7 +10014,7 @@
       <c r="AZ93" s="23"/>
       <c r="BA93" s="23"/>
     </row>
-    <row r="94" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A94" s="35"/>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -10157,7 +10069,7 @@
       <c r="AZ94" s="23"/>
       <c r="BA94" s="23"/>
     </row>
-    <row r="95" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A95" s="35"/>
       <c r="B95" s="34"/>
       <c r="C95" s="34"/>
@@ -10212,7 +10124,7 @@
       <c r="AZ95" s="23"/>
       <c r="BA95" s="23"/>
     </row>
-    <row r="96" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A96" s="35"/>
       <c r="B96" s="34"/>
       <c r="C96" s="34"/>
@@ -10267,7 +10179,7 @@
       <c r="AZ96" s="23"/>
       <c r="BA96" s="23"/>
     </row>
-    <row r="97" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A97" s="35"/>
       <c r="B97" s="34"/>
       <c r="C97" s="34"/>
@@ -10322,7 +10234,7 @@
       <c r="AZ97" s="23"/>
       <c r="BA97" s="23"/>
     </row>
-    <row r="98" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A98" s="35"/>
       <c r="B98" s="34"/>
       <c r="C98" s="34"/>
@@ -10377,7 +10289,7 @@
       <c r="AZ98" s="23"/>
       <c r="BA98" s="23"/>
     </row>
-    <row r="99" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A99" s="35"/>
       <c r="B99" s="34"/>
       <c r="C99" s="34"/>
@@ -10432,7 +10344,7 @@
       <c r="AZ99" s="23"/>
       <c r="BA99" s="23"/>
     </row>
-    <row r="100" spans="1:53" s="105" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A100" s="35"/>
       <c r="B100" s="34"/>
       <c r="C100" s="34"/>
@@ -10488,22 +10400,19 @@
       <c r="BA100" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:L2"/>
-  </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="D1 E4:F6 P7:R7">
-    <cfRule type="expression" dxfId="108" priority="79">
+    <cfRule type="expression" dxfId="107" priority="79">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="107" priority="52">
+    <cfRule type="expression" dxfId="106" priority="52">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:AI7 M7:N7">
-    <cfRule type="expression" dxfId="106" priority="50">
+    <cfRule type="expression" dxfId="105" priority="50">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10522,7 +10431,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7">
-    <cfRule type="expression" dxfId="105" priority="48">
+    <cfRule type="expression" dxfId="104" priority="48">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10541,12 +10450,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL7:AN7">
-    <cfRule type="expression" dxfId="104" priority="34">
+    <cfRule type="expression" dxfId="103" priority="34">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE7">
-    <cfRule type="expression" dxfId="103" priority="46">
+    <cfRule type="expression" dxfId="102" priority="46">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10565,7 +10474,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF7:AG7">
-    <cfRule type="expression" dxfId="102" priority="44">
+    <cfRule type="expression" dxfId="101" priority="44">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10584,7 +10493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH7">
-    <cfRule type="expression" dxfId="101" priority="42">
+    <cfRule type="expression" dxfId="100" priority="42">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10603,7 +10512,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI7">
-    <cfRule type="expression" dxfId="100" priority="40">
+    <cfRule type="expression" dxfId="99" priority="40">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10622,7 +10531,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ7">
-    <cfRule type="expression" dxfId="99" priority="38">
+    <cfRule type="expression" dxfId="98" priority="38">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10641,7 +10550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK7">
-    <cfRule type="expression" dxfId="98" priority="36">
+    <cfRule type="expression" dxfId="97" priority="36">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10674,87 +10583,87 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="97" priority="31">
+    <cfRule type="expression" dxfId="96" priority="31">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7">
-    <cfRule type="expression" dxfId="96" priority="29">
+    <cfRule type="expression" dxfId="95" priority="29">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:L7">
-    <cfRule type="expression" dxfId="95" priority="28">
+    <cfRule type="expression" dxfId="94" priority="28">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="expression" dxfId="94" priority="25">
+    <cfRule type="expression" dxfId="93" priority="25">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:A100">
-    <cfRule type="expression" dxfId="93" priority="2">
+    <cfRule type="expression" dxfId="92" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:R100">
-    <cfRule type="expression" dxfId="92" priority="23">
+    <cfRule type="expression" dxfId="91" priority="23">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S8:AI100 M8:N100">
-    <cfRule type="expression" dxfId="91" priority="21">
+    <cfRule type="expression" dxfId="90" priority="21">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD8:AD100">
-    <cfRule type="expression" dxfId="90" priority="19">
+    <cfRule type="expression" dxfId="89" priority="19">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL8:AN100">
-    <cfRule type="expression" dxfId="89" priority="5">
+    <cfRule type="expression" dxfId="88" priority="5">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE8:AE100">
-    <cfRule type="expression" dxfId="88" priority="17">
+    <cfRule type="expression" dxfId="87" priority="17">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF8:AG100">
-    <cfRule type="expression" dxfId="87" priority="15">
+    <cfRule type="expression" dxfId="86" priority="15">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH8:AH100">
-    <cfRule type="expression" dxfId="86" priority="13">
+    <cfRule type="expression" dxfId="85" priority="13">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8:AI100">
-    <cfRule type="expression" dxfId="85" priority="11">
+    <cfRule type="expression" dxfId="84" priority="11">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8:AJ100">
-    <cfRule type="expression" dxfId="84" priority="9">
+    <cfRule type="expression" dxfId="83" priority="9">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK100">
-    <cfRule type="expression" dxfId="83" priority="7">
+    <cfRule type="expression" dxfId="82" priority="7">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O100">
-    <cfRule type="expression" dxfId="82" priority="4">
+    <cfRule type="expression" dxfId="81" priority="4">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:L100">
-    <cfRule type="expression" dxfId="81" priority="3">
+    <cfRule type="expression" dxfId="80" priority="3">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10885,7 +10794,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11148,150 +11057,150 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtPickList" enableFormatConditionsCalculation="0">
+  <sheetPr codeName="shtPickList">
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="33.75" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="13"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="119" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="14"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="14"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="14"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="14"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="14"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="14"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="14"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="14"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="14"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="14"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="14"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="14"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="14"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="14"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="14"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="14"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="14"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1">
       <c r="A33" s="14"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1">
       <c r="A34" s="14"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1">
       <c r="A35" s="14"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1">
       <c r="A36" s="14"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1">
       <c r="A37" s="14"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1">
       <c r="A38" s="14"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1">
       <c r="A39" s="14"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1">
       <c r="A40" s="14"/>
     </row>
   </sheetData>
@@ -11314,19 +11223,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="shtBinLookup" enableFormatConditionsCalculation="0">
+  <sheetPr codeName="shtBinLookup">
     <tabColor theme="4" tint="-0.499984740745262"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="33.75" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -11334,16 +11243,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
@@ -11360,7 +11269,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5">
       <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
@@ -11377,7 +11286,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
@@ -11394,207 +11303,207 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4">
       <c r="A18" s="14"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4">
       <c r="A19" s="14"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4">
       <c r="A20" s="14"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4">
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4">
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -11625,302 +11534,302 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="57" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="57" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="57"/>
-    <col min="4" max="4" width="27.83203125" style="57" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="57"/>
+    <col min="3" max="3" width="8.77734375" style="57"/>
+    <col min="4" max="4" width="27.77734375" style="57" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1">
       <c r="A1" s="125" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
       <c r="D1" s="125"/>
     </row>
-    <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="58" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="60">
         <v>1</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="63" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1">
       <c r="A4" s="64">
         <v>2</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C4" s="66"/>
       <c r="D4" s="67" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
       <c r="A5" s="68"/>
       <c r="B5" s="69"/>
       <c r="C5" s="70"/>
       <c r="D5" s="70"/>
     </row>
-    <row r="6" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" s="71" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="126" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B6" s="127"/>
       <c r="C6" s="127"/>
       <c r="D6" s="128"/>
     </row>
-    <row r="7" spans="1:4" s="71" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
       <c r="A7" s="72" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="74">
         <v>3</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C8" s="76"/>
       <c r="D8" s="77"/>
     </row>
-    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="60">
         <v>4</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C9" s="78"/>
       <c r="D9" s="79"/>
     </row>
-    <row r="10" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17.25" thickBot="1">
       <c r="A10" s="60">
         <v>5</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C10" s="78"/>
       <c r="D10" s="79"/>
     </row>
-    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="74">
         <v>6</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C11" s="78"/>
       <c r="D11" s="79"/>
     </row>
-    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="60">
         <v>7</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C12" s="78"/>
       <c r="D12" s="79"/>
     </row>
-    <row r="13" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="17.25" thickBot="1">
       <c r="A13" s="60">
         <v>8</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C13" s="78"/>
       <c r="D13" s="79"/>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4">
       <c r="A14" s="74">
         <v>9</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="79"/>
     </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="60">
         <v>10</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="79"/>
     </row>
-    <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="17.25" thickBot="1">
       <c r="A16" s="60">
         <v>11</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="79" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="74">
         <v>12</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="79"/>
     </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="60">
         <v>13</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C18" s="78"/>
       <c r="D18" s="79"/>
     </row>
-    <row r="19" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17.25" thickBot="1">
       <c r="A19" s="60">
         <v>14</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C19" s="78"/>
       <c r="D19" s="79"/>
     </row>
-    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="74">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="79"/>
     </row>
-    <row r="21" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17.25" thickBot="1">
       <c r="A21" s="60">
         <v>16</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C21" s="80"/>
       <c r="D21" s="81"/>
     </row>
-    <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="16.5" thickBot="1">
       <c r="A22" s="82"/>
     </row>
-    <row r="23" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="16.5" thickBot="1">
       <c r="A23" s="129" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B23" s="130"/>
       <c r="C23" s="130"/>
       <c r="D23" s="131"/>
     </row>
-    <row r="24" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="17.25" thickBot="1">
       <c r="A24" s="83" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B24" s="84" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C24" s="84" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D24" s="84" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.5" thickBot="1">
       <c r="A25" s="60">
         <v>17</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C25" s="86"/>
       <c r="D25" s="87" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" thickBot="1">
       <c r="A26" s="60">
         <v>18</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="63" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="60">
         <v>19</v>
       </c>
       <c r="B27" s="85" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C27" s="88"/>
       <c r="D27" s="89" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" thickBot="1">
       <c r="A28" s="60">
         <v>20</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C28" s="91"/>
       <c r="D28" s="92" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -11941,63 +11850,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
+  <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="52" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="52" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4">
       <c r="A1" s="132" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B1" s="132" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C1" s="132"/>
       <c r="D1" s="132" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="132"/>
       <c r="B2" s="38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D2" s="132"/>
     </row>
-    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="45" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="40"/>
       <c r="C3" s="40" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D3" s="41"/>
     </row>
-    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="16.5">
       <c r="A4" s="39" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D4" s="41"/>
     </row>
-    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="43" t="s">
         <v>15</v>
       </c>
@@ -12005,59 +11914,59 @@
       <c r="C5" s="44"/>
       <c r="D5" s="41"/>
     </row>
-    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="45" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="43" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="46"/>
       <c r="D7" s="41"/>
     </row>
-    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="45" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D8" s="41"/>
     </row>
-    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="48" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="45" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="43" t="s">
         <v>18</v>
       </c>
@@ -12065,29 +11974,29 @@
       <c r="C11" s="47"/>
       <c r="D11" s="41"/>
     </row>
-    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D12" s="41"/>
     </row>
-    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D13" s="41"/>
     </row>
-    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="16.5">
       <c r="A14" s="43" t="s">
         <v>36</v>
       </c>
@@ -12095,17 +12004,17 @@
       <c r="C14" s="47"/>
       <c r="D14" s="41"/>
     </row>
-    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="45" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B15" s="47"/>
       <c r="C15" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D15" s="41"/>
     </row>
-    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="43" t="s">
         <v>37</v>
       </c>
@@ -12113,27 +12022,27 @@
       <c r="C16" s="47"/>
       <c r="D16" s="41"/>
     </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="45" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D17" s="41"/>
     </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D18" s="41"/>
     </row>
-    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="43" t="s">
         <v>39</v>
       </c>
@@ -12141,27 +12050,27 @@
       <c r="C19" s="47"/>
       <c r="D19" s="41"/>
     </row>
-    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="45" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D20" s="41"/>
     </row>
-    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="48" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="47" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D21" s="41"/>
     </row>
-    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" ht="16.5">
       <c r="A22" s="43" t="s">
         <v>19</v>
       </c>
@@ -12169,7 +12078,7 @@
       <c r="C22" s="47"/>
       <c r="D22" s="41"/>
     </row>
-    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" ht="16.5">
       <c r="A23" s="43" t="s">
         <v>20</v>
       </c>
@@ -12177,7 +12086,7 @@
       <c r="C23" s="47"/>
       <c r="D23" s="41"/>
     </row>
-    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" ht="16.5">
       <c r="A24" s="43" t="s">
         <v>21</v>
       </c>
@@ -12185,7 +12094,7 @@
       <c r="C24" s="47"/>
       <c r="D24" s="41"/>
     </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" ht="16.5">
       <c r="A25" s="43" t="s">
         <v>22</v>
       </c>
@@ -12193,7 +12102,7 @@
       <c r="C25" s="47"/>
       <c r="D25" s="41"/>
     </row>
-    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:4" ht="16.5">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -12201,7 +12110,7 @@
       <c r="C26" s="47"/>
       <c r="D26" s="41"/>
     </row>
-    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" ht="16.5">
       <c r="A27" s="43" t="s">
         <v>24</v>
       </c>
@@ -12209,27 +12118,27 @@
       <c r="C27" s="47"/>
       <c r="D27" s="41"/>
     </row>
-    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" ht="16.5">
       <c r="A28" s="45" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D28" s="41"/>
     </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" ht="16.5">
       <c r="A29" s="45" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D29" s="41"/>
     </row>
-    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:4" ht="16.5">
       <c r="A30" s="43" t="s">
         <v>27</v>
       </c>
@@ -12237,7 +12146,7 @@
       <c r="C30" s="47"/>
       <c r="D30" s="41"/>
     </row>
-    <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" ht="16.5">
       <c r="A31" s="43" t="s">
         <v>28</v>
       </c>
@@ -12245,7 +12154,7 @@
       <c r="C31" s="47"/>
       <c r="D31" s="41"/>
     </row>
-    <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" ht="16.5">
       <c r="A32" s="43" t="s">
         <v>29</v>
       </c>
@@ -12253,7 +12162,7 @@
       <c r="C32" s="47"/>
       <c r="D32" s="41"/>
     </row>
-    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" ht="16.5">
       <c r="A33" s="43" t="s">
         <v>30</v>
       </c>
@@ -12261,7 +12170,7 @@
       <c r="C33" s="47"/>
       <c r="D33" s="41"/>
     </row>
-    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" ht="16.5">
       <c r="A34" s="43" t="s">
         <v>31</v>
       </c>
@@ -12269,7 +12178,7 @@
       <c r="C34" s="47"/>
       <c r="D34" s="41"/>
     </row>
-    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" ht="16.5">
       <c r="A35" s="43" t="s">
         <v>32</v>
       </c>
@@ -12277,46 +12186,46 @@
       <c r="C35" s="47"/>
       <c r="D35" s="41"/>
     </row>
-    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="50" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B36" s="51"/>
       <c r="C36" s="51" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D36" s="41"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4">
       <c r="A39" s="52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="53"/>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="55"/>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="56"/>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -12327,12 +12236,12 @@
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12349,484 +12258,484 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="31.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" s="27" customFormat="1">
       <c r="A1" s="96" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="96" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="96" t="s">
+        <v>425</v>
+      </c>
+      <c r="E1" s="96" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="96" t="s">
+        <v>427</v>
+      </c>
+      <c r="G1" s="96" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1" s="96" t="s">
+        <v>429</v>
+      </c>
+      <c r="I1" s="100" t="s">
+        <v>436</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>485</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>486</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>487</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="95" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>430</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>500</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>437</v>
+      </c>
+      <c r="G2" s="97" t="s">
+        <v>504</v>
+      </c>
+      <c r="H2" s="95" t="s">
+        <v>434</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>441</v>
+      </c>
+      <c r="J2" s="101" t="s">
+        <v>472</v>
+      </c>
+      <c r="K2" s="103" t="s">
+        <v>476</v>
+      </c>
+      <c r="L2" s="107" t="s">
+        <v>479</v>
+      </c>
+      <c r="M2" s="116" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A3" s="95" t="s">
+        <v>414</v>
+      </c>
+      <c r="B3" s="107" t="s">
+        <v>414</v>
+      </c>
+      <c r="C3" s="95" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="95" t="s">
         <v>431</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="E3" s="98" t="s">
+        <v>501</v>
+      </c>
+      <c r="F3" s="107" t="s">
+        <v>438</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>505</v>
+      </c>
+      <c r="H3" s="95" t="s">
+        <v>435</v>
+      </c>
+      <c r="I3" s="99" t="s">
+        <v>442</v>
+      </c>
+      <c r="J3" s="101" t="s">
+        <v>473</v>
+      </c>
+      <c r="K3" s="103" t="s">
+        <v>477</v>
+      </c>
+      <c r="L3" s="107" t="s">
+        <v>480</v>
+      </c>
+      <c r="M3" s="116" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="95" t="s">
+        <v>415</v>
+      </c>
+      <c r="B4" s="107" t="s">
+        <v>415</v>
+      </c>
+      <c r="C4" s="95" t="s">
+        <v>423</v>
+      </c>
+      <c r="D4" s="95" t="s">
         <v>432</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E4" s="98" t="s">
+        <v>502</v>
+      </c>
+      <c r="F4" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="G4" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="H4" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="I4" s="99" t="s">
+        <v>443</v>
+      </c>
+      <c r="J4" s="101" t="s">
+        <v>474</v>
+      </c>
+      <c r="K4" s="103" t="s">
+        <v>478</v>
+      </c>
+      <c r="L4" s="107" t="s">
+        <v>481</v>
+      </c>
+      <c r="M4" s="116" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="95" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="D5" s="95" t="s">
         <v>433</v>
       </c>
-      <c r="F1" s="96" t="s">
-        <v>434</v>
-      </c>
-      <c r="G1" s="96" t="s">
-        <v>435</v>
-      </c>
-      <c r="H1" s="96" t="s">
-        <v>436</v>
-      </c>
-      <c r="I1" s="100" t="s">
-        <v>443</v>
-      </c>
-      <c r="J1" s="102" t="s">
-        <v>494</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>495</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>496</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A2" s="95" t="s">
-        <v>420</v>
-      </c>
-      <c r="B2" s="107" t="s">
-        <v>420</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>428</v>
-      </c>
-      <c r="D2" s="95" t="s">
-        <v>437</v>
-      </c>
-      <c r="E2" s="98" t="s">
-        <v>509</v>
-      </c>
-      <c r="F2" s="107" t="s">
+      <c r="E5" s="98" t="s">
+        <v>503</v>
+      </c>
+      <c r="F5" s="107" t="s">
+        <v>440</v>
+      </c>
+      <c r="I5" s="99" t="s">
         <v>444</v>
       </c>
-      <c r="G2" s="97" t="s">
-        <v>513</v>
-      </c>
-      <c r="H2" s="95" t="s">
-        <v>441</v>
-      </c>
-      <c r="I2" s="99" t="s">
-        <v>450</v>
-      </c>
-      <c r="J2" s="101" t="s">
-        <v>481</v>
-      </c>
-      <c r="K2" s="103" t="s">
-        <v>485</v>
-      </c>
-      <c r="L2" s="107" t="s">
-        <v>488</v>
-      </c>
-      <c r="M2" s="116" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="95" t="s">
-        <v>421</v>
-      </c>
-      <c r="B3" s="107" t="s">
-        <v>421</v>
-      </c>
-      <c r="C3" s="95" t="s">
-        <v>429</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>438</v>
-      </c>
-      <c r="E3" s="98" t="s">
-        <v>510</v>
-      </c>
-      <c r="F3" s="107" t="s">
+      <c r="J5" s="101" t="s">
+        <v>475</v>
+      </c>
+      <c r="K5" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="L5" s="107" t="s">
+        <v>482</v>
+      </c>
+      <c r="M5" s="116" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="116" t="s">
+        <v>517</v>
+      </c>
+      <c r="B6" s="116" t="s">
+        <v>517</v>
+      </c>
+      <c r="D6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="E6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="F6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="I6" s="99" t="s">
         <v>445</v>
       </c>
-      <c r="G3" s="97" t="s">
-        <v>514</v>
-      </c>
-      <c r="H3" s="95" t="s">
-        <v>442</v>
-      </c>
-      <c r="I3" s="99" t="s">
-        <v>451</v>
-      </c>
-      <c r="J3" s="101" t="s">
-        <v>482</v>
-      </c>
-      <c r="K3" s="103" t="s">
-        <v>486</v>
-      </c>
-      <c r="L3" s="107" t="s">
-        <v>489</v>
-      </c>
-      <c r="M3" s="116" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A4" s="95" t="s">
-        <v>422</v>
-      </c>
-      <c r="B4" s="107" t="s">
-        <v>422</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>430</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>439</v>
-      </c>
-      <c r="E4" s="98" t="s">
-        <v>511</v>
-      </c>
-      <c r="F4" s="107" t="s">
+      <c r="J6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="L6" s="107" t="s">
+        <v>483</v>
+      </c>
+      <c r="M6" s="116" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="116" t="s">
+        <v>518</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>518</v>
+      </c>
+      <c r="I7" s="99" t="s">
         <v>446</v>
       </c>
-      <c r="G4" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="H4" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="I4" s="99" t="s">
-        <v>452</v>
-      </c>
-      <c r="J4" s="101" t="s">
-        <v>483</v>
-      </c>
-      <c r="K4" s="103" t="s">
-        <v>487</v>
-      </c>
-      <c r="L4" s="107" t="s">
-        <v>490</v>
-      </c>
-      <c r="M4" s="116" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="95" t="s">
-        <v>423</v>
-      </c>
-      <c r="B5" s="107" t="s">
-        <v>423</v>
-      </c>
-      <c r="C5" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>440</v>
-      </c>
-      <c r="E5" s="98" t="s">
-        <v>512</v>
-      </c>
-      <c r="F5" s="107" t="s">
+      <c r="L7" s="107" t="s">
+        <v>484</v>
+      </c>
+      <c r="M7" s="116" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="116" t="s">
+        <v>519</v>
+      </c>
+      <c r="B8" s="116" t="s">
+        <v>519</v>
+      </c>
+      <c r="I8" s="99" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="99" t="s">
-        <v>453</v>
-      </c>
-      <c r="J5" s="101" t="s">
-        <v>484</v>
-      </c>
-      <c r="K5" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="L5" s="107" t="s">
-        <v>491</v>
-      </c>
-      <c r="M5" s="116" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="116" t="s">
+      <c r="L8" s="116" t="s">
         <v>527</v>
       </c>
-      <c r="B6" s="116" t="s">
-        <v>527</v>
-      </c>
-      <c r="D6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="E6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="F6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="I6" s="99" t="s">
-        <v>454</v>
-      </c>
-      <c r="J6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="L6" s="107" t="s">
-        <v>492</v>
-      </c>
-      <c r="M6" s="116" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A7" s="116" t="s">
-        <v>528</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>528</v>
-      </c>
-      <c r="I7" s="99" t="s">
-        <v>455</v>
-      </c>
-      <c r="L7" s="107" t="s">
-        <v>493</v>
-      </c>
-      <c r="M7" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="116" t="s">
-        <v>529</v>
-      </c>
-      <c r="B8" s="116" t="s">
-        <v>529</v>
-      </c>
-      <c r="I8" s="99" t="s">
-        <v>456</v>
-      </c>
-      <c r="L8" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="95" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B9" s="107" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="I9" s="99" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="95" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B10" s="107" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="I10" s="99" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="117" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="B11" s="117" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="H11" s="107"/>
       <c r="I11" s="99" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="117" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="H12" s="107"/>
       <c r="I12" s="99" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="117" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="H13" s="107"/>
       <c r="I13" s="99" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="95" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H14" s="107"/>
       <c r="I14" s="99" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15" s="116"/>
       <c r="H15" s="107"/>
       <c r="I15" s="99" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16" s="107"/>
       <c r="H16" s="107"/>
       <c r="I16" s="99" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="107"/>
       <c r="H17" s="107"/>
       <c r="I17" s="99" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="107"/>
       <c r="H18" s="107"/>
       <c r="I18" s="99" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="107"/>
       <c r="H19" s="107"/>
       <c r="I19" s="99" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="107"/>
       <c r="H20" s="107"/>
       <c r="I20" s="99" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="107"/>
       <c r="H21" s="107"/>
       <c r="I21" s="99" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.15">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="107"/>
       <c r="H22" s="107"/>
       <c r="I22" s="99" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="107"/>
       <c r="H23" s="107"/>
       <c r="I23" s="99" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
       <c r="B24" s="107"/>
       <c r="H24" s="107"/>
       <c r="I24" s="99" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="107"/>
       <c r="H25" s="107"/>
       <c r="I25" s="99" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
       <c r="H26" s="107"/>
       <c r="I26" s="99" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.15">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="H27" s="107"/>
       <c r="I27" s="99" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.15">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="H28" s="107"/>
       <c r="I28" s="99" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="H29" s="107"/>
       <c r="I29" s="99" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.15">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="H30" s="107"/>
       <c r="I30" s="99" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="H31" s="107"/>
       <c r="I31" s="99" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="H32" s="107"/>
       <c r="I32" s="99" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.15">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9">
       <c r="H33" s="107"/>
       <c r="I33" s="99" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.15">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9">
       <c r="H34" s="107"/>
       <c r="I34" s="115" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.15">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9">
       <c r="I35" s="115" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.15">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9">
       <c r="I36" s="116" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -12839,134 +12748,134 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="107" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="107" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="107" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="107" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="107" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="107" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="107" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="107" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="107" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="107" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="107" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="107" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="107" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="107" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="107" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="107" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="107" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="107" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="107" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="107" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="107" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="107" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="107" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="105"/>
     </row>
   </sheetData>
@@ -12977,52 +12886,52 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C1" t="s">
         <v>46</v>
@@ -13037,7 +12946,7 @@
         <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="H1" t="s">
         <v>50</v>
@@ -13052,7 +12961,7 @@
         <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="M1" t="s">
         <v>54</v>
@@ -13085,7 +12994,7 @@
         <v>63</v>
       </c>
       <c r="W1" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="X1" t="s">
         <v>64</v>
@@ -13139,884 +13048,884 @@
         <v>80</v>
       </c>
       <c r="AO1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.15">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41">
       <c r="A2" s="95" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="95" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="95" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="95" t="s">
+        <v>212</v>
+      </c>
+      <c r="I2" s="95" t="s">
+        <v>218</v>
+      </c>
+      <c r="J2" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="K2" s="95" t="s">
+        <v>220</v>
+      </c>
+      <c r="L2" s="95" t="s">
+        <v>224</v>
+      </c>
+      <c r="M2" s="95" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="95" t="s">
+        <v>250</v>
+      </c>
+      <c r="O2" s="95" t="s">
+        <v>258</v>
+      </c>
+      <c r="P2" s="95" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q2" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="R2" s="95" t="s">
+        <v>276</v>
+      </c>
+      <c r="S2" s="95" t="s">
+        <v>285</v>
+      </c>
+      <c r="T2" s="95" t="s">
+        <v>288</v>
+      </c>
+      <c r="U2" t="s">
+        <v>289</v>
+      </c>
+      <c r="V2" s="95" t="s">
+        <v>293</v>
+      </c>
+      <c r="W2" s="95" t="s">
+        <v>300</v>
+      </c>
+      <c r="X2" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y2" s="95" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z2" s="95" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA2" s="95" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB2" s="95" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC2" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="AD2" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="AE2" s="95" t="s">
+        <v>346</v>
+      </c>
+      <c r="AF2" s="95" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG2" s="95" t="s">
+        <v>357</v>
+      </c>
+      <c r="AH2" s="95" t="s">
+        <v>365</v>
+      </c>
+      <c r="AI2" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ2" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="AK2" s="95" t="s">
+        <v>390</v>
+      </c>
+      <c r="AL2" s="95" t="s">
+        <v>394</v>
+      </c>
+      <c r="AM2" s="95" t="s">
+        <v>403</v>
+      </c>
+      <c r="AN2" s="95" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" s="95" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="95" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="95" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="95" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="95" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" s="95" t="s">
+        <v>213</v>
+      </c>
+      <c r="I3" s="95" t="s">
+        <v>219</v>
+      </c>
+      <c r="K3" s="95" t="s">
+        <v>221</v>
+      </c>
+      <c r="L3" s="95" t="s">
+        <v>225</v>
+      </c>
+      <c r="M3" s="95" t="s">
+        <v>232</v>
+      </c>
+      <c r="N3" s="95" t="s">
+        <v>251</v>
+      </c>
+      <c r="O3" s="95" t="s">
+        <v>259</v>
+      </c>
+      <c r="P3" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q3" s="95" t="s">
+        <v>272</v>
+      </c>
+      <c r="R3" s="95" t="s">
+        <v>277</v>
+      </c>
+      <c r="S3" s="95" t="s">
+        <v>286</v>
+      </c>
+      <c r="T3" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="U3" t="s">
+        <v>290</v>
+      </c>
+      <c r="V3" s="95" t="s">
+        <v>294</v>
+      </c>
+      <c r="W3" s="95" t="s">
+        <v>301</v>
+      </c>
+      <c r="X3" s="95" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y3" s="95" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z3" s="95" t="s">
+        <v>309</v>
+      </c>
+      <c r="AA3" s="95" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB3" s="95" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC3" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="AD3" s="95" t="s">
+        <v>334</v>
+      </c>
+      <c r="AE3" s="95" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF3" s="95" t="s">
+        <v>355</v>
+      </c>
+      <c r="AG3" s="95" t="s">
+        <v>358</v>
+      </c>
+      <c r="AH3" s="95" t="s">
+        <v>366</v>
+      </c>
+      <c r="AI3" s="95" t="s">
+        <v>371</v>
+      </c>
+      <c r="AJ3" s="95" t="s">
+        <v>387</v>
+      </c>
+      <c r="AK3" s="95" t="s">
+        <v>391</v>
+      </c>
+      <c r="AL3" s="95" t="s">
+        <v>395</v>
+      </c>
+      <c r="AM3" s="95" t="s">
+        <v>404</v>
+      </c>
+      <c r="AN3" s="95" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" s="95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="95" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="95" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" s="95" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="K4" s="95" t="s">
+        <v>222</v>
+      </c>
+      <c r="L4" s="95" t="s">
+        <v>226</v>
+      </c>
+      <c r="M4" s="95" t="s">
+        <v>233</v>
+      </c>
+      <c r="N4" s="95" t="s">
+        <v>252</v>
+      </c>
+      <c r="O4" s="95" t="s">
+        <v>260</v>
+      </c>
+      <c r="P4" s="95" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q4" s="95" t="s">
+        <v>273</v>
+      </c>
+      <c r="R4" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="S4" s="95" t="s">
+        <v>287</v>
+      </c>
+      <c r="U4" t="s">
+        <v>291</v>
+      </c>
+      <c r="V4" t="s">
+        <v>295</v>
+      </c>
+      <c r="W4" t="s">
+        <v>527</v>
+      </c>
+      <c r="X4" s="95" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z4" s="95" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA4" s="95" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB4" s="95" t="s">
+        <v>323</v>
+      </c>
+      <c r="AC4" s="95" t="s">
+        <v>330</v>
+      </c>
+      <c r="AD4" s="95" t="s">
+        <v>335</v>
+      </c>
+      <c r="AE4" s="95" t="s">
+        <v>348</v>
+      </c>
+      <c r="AF4" s="95" t="s">
+        <v>356</v>
+      </c>
+      <c r="AG4" s="95" t="s">
+        <v>359</v>
+      </c>
+      <c r="AH4" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="AI4" s="95" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ4" s="95" t="s">
+        <v>388</v>
+      </c>
+      <c r="AK4" s="95" t="s">
+        <v>392</v>
+      </c>
+      <c r="AL4" s="95" t="s">
+        <v>396</v>
+      </c>
+      <c r="AM4" s="95" t="s">
+        <v>405</v>
+      </c>
+      <c r="AN4" s="95" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="95" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="D2" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="95" t="s">
+      <c r="C5" s="95" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="95" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="95" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="G5" s="95" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="95" t="s">
+      <c r="H5" s="95" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="L5" s="95" t="s">
+        <v>227</v>
+      </c>
+      <c r="M5" s="95" t="s">
+        <v>234</v>
+      </c>
+      <c r="N5" s="95" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" s="95" t="s">
+        <v>261</v>
+      </c>
+      <c r="P5" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q5" s="95" t="s">
+        <v>274</v>
+      </c>
+      <c r="R5" s="95" t="s">
+        <v>279</v>
+      </c>
+      <c r="S5" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="U5" t="s">
+        <v>292</v>
+      </c>
+      <c r="V5" t="s">
+        <v>296</v>
+      </c>
+      <c r="X5" s="95" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z5" s="95" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA5" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB5" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC5" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD5" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="AE5" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF5" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AG5" s="95" t="s">
+        <v>360</v>
+      </c>
+      <c r="AH5" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI5" s="95" t="s">
+        <v>373</v>
+      </c>
+      <c r="AJ5" s="95" t="s">
+        <v>389</v>
+      </c>
+      <c r="AK5" s="95" t="s">
+        <v>393</v>
+      </c>
+      <c r="AL5" s="95" t="s">
+        <v>397</v>
+      </c>
+      <c r="AM5" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="AN5" s="116" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" s="95" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="F6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="G6" s="95" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="95" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="L6" s="95" t="s">
+        <v>228</v>
+      </c>
+      <c r="M6" s="95" t="s">
+        <v>235</v>
+      </c>
+      <c r="N6" s="95" t="s">
+        <v>254</v>
+      </c>
+      <c r="O6" s="95" t="s">
+        <v>262</v>
+      </c>
+      <c r="P6" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q6" s="95" t="s">
+        <v>275</v>
+      </c>
+      <c r="R6" s="95" t="s">
+        <v>280</v>
+      </c>
+      <c r="U6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="V6" t="s">
+        <v>297</v>
+      </c>
+      <c r="X6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z6" s="95" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AB6" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC6" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD6" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="AE6" s="95" t="s">
+        <v>350</v>
+      </c>
+      <c r="AG6" s="95" t="s">
+        <v>361</v>
+      </c>
+      <c r="AH6" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="AI6" s="95" t="s">
+        <v>374</v>
+      </c>
+      <c r="AJ6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AK6" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AL6" s="95" t="s">
+        <v>398</v>
+      </c>
+      <c r="AM6" s="95" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="G7" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="95" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" s="95" t="s">
+        <v>229</v>
+      </c>
+      <c r="M7" s="95" t="s">
+        <v>236</v>
+      </c>
+      <c r="N7" s="95" t="s">
+        <v>255</v>
+      </c>
+      <c r="O7" s="95" t="s">
+        <v>263</v>
+      </c>
+      <c r="P7" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q7" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="R7" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="V7" s="95" t="s">
+        <v>298</v>
+      </c>
+      <c r="Z7" s="95" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB7" s="95" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC7" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AD7" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="AE7" s="95" t="s">
+        <v>351</v>
+      </c>
+      <c r="AG7" s="95" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH7" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AI7" s="95" t="s">
+        <v>375</v>
+      </c>
+      <c r="AL7" s="95" t="s">
+        <v>399</v>
+      </c>
+      <c r="AM7" s="116" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="B8" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="C8" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="D8" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="95" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="L8" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="M8" s="95" t="s">
+        <v>237</v>
+      </c>
+      <c r="N8" s="95" t="s">
+        <v>256</v>
+      </c>
+      <c r="O8" s="95" t="s">
+        <v>264</v>
+      </c>
+      <c r="P8" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="R8" s="95" t="s">
+        <v>282</v>
+      </c>
+      <c r="V8" s="95" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z8" s="95" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB8" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD8" s="95" t="s">
+        <v>339</v>
+      </c>
+      <c r="AE8" s="95" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG8" s="95" t="s">
+        <v>363</v>
+      </c>
+      <c r="AI8" s="95" t="s">
+        <v>376</v>
+      </c>
+      <c r="AL8" s="95" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="D9" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="G9" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="H2" s="95" t="s">
-        <v>219</v>
-      </c>
-      <c r="I2" s="95" t="s">
-        <v>225</v>
-      </c>
-      <c r="J2" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="K2" s="95" t="s">
-        <v>227</v>
-      </c>
-      <c r="L2" s="95" t="s">
-        <v>231</v>
-      </c>
-      <c r="M2" s="95" t="s">
+      <c r="L9" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="M9" s="95" t="s">
         <v>238</v>
       </c>
-      <c r="N2" s="95" t="s">
+      <c r="N9" s="95" t="s">
         <v>257</v>
       </c>
-      <c r="O2" s="95" t="s">
-        <v>265</v>
-      </c>
-      <c r="P2" s="95" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q2" s="95" t="s">
-        <v>278</v>
-      </c>
-      <c r="R2" s="95" t="s">
+      <c r="O9" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="R9" s="95" t="s">
         <v>283</v>
       </c>
-      <c r="S2" s="95" t="s">
-        <v>292</v>
-      </c>
-      <c r="T2" s="95" t="s">
-        <v>295</v>
-      </c>
-      <c r="U2" t="s">
-        <v>296</v>
-      </c>
-      <c r="V2" s="95" t="s">
-        <v>300</v>
-      </c>
-      <c r="W2" s="95" t="s">
-        <v>307</v>
-      </c>
-      <c r="X2" s="95" t="s">
-        <v>309</v>
-      </c>
-      <c r="Y2" s="95" t="s">
-        <v>313</v>
-      </c>
-      <c r="Z2" s="95" t="s">
+      <c r="V9" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z9" s="95" t="s">
         <v>315</v>
       </c>
-      <c r="AA2" s="95" t="s">
-        <v>324</v>
-      </c>
-      <c r="AB2" s="95" t="s">
-        <v>328</v>
-      </c>
-      <c r="AC2" s="95" t="s">
-        <v>335</v>
-      </c>
-      <c r="AD2" s="95" t="s">
+      <c r="AB9" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AD9" s="95" t="s">
         <v>340</v>
       </c>
-      <c r="AE2" s="95" t="s">
+      <c r="AE9" s="95" t="s">
         <v>353</v>
       </c>
-      <c r="AF2" s="95" t="s">
-        <v>361</v>
-      </c>
-      <c r="AG2" s="95" t="s">
+      <c r="AG9" s="95" t="s">
         <v>364</v>
       </c>
-      <c r="AH2" s="95" t="s">
-        <v>372</v>
-      </c>
-      <c r="AI2" s="95" t="s">
+      <c r="AI9" s="95" t="s">
         <v>377</v>
       </c>
-      <c r="AJ2" s="95" t="s">
-        <v>393</v>
-      </c>
-      <c r="AK2" s="95" t="s">
-        <v>397</v>
-      </c>
-      <c r="AL2" s="95" t="s">
+      <c r="AL9" s="95" t="s">
         <v>401</v>
       </c>
-      <c r="AM2" s="95" t="s">
-        <v>410</v>
-      </c>
-      <c r="AN2" s="95" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A3" s="95" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="95" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="95" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="95" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="95" t="s">
-        <v>208</v>
-      </c>
-      <c r="G3" s="95" t="s">
-        <v>212</v>
-      </c>
-      <c r="H3" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="I3" s="95" t="s">
-        <v>226</v>
-      </c>
-      <c r="K3" s="95" t="s">
-        <v>228</v>
-      </c>
-      <c r="L3" s="95" t="s">
-        <v>232</v>
-      </c>
-      <c r="M3" s="95" t="s">
+    </row>
+    <row r="10" spans="1:41">
+      <c r="G10" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="M10" s="95" t="s">
         <v>239</v>
       </c>
-      <c r="N3" s="95" t="s">
-        <v>258</v>
-      </c>
-      <c r="O3" s="95" t="s">
-        <v>266</v>
-      </c>
-      <c r="P3" s="95" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q3" s="95" t="s">
-        <v>279</v>
-      </c>
-      <c r="R3" s="95" t="s">
+      <c r="N10" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="R10" s="95" t="s">
         <v>284</v>
       </c>
-      <c r="S3" s="95" t="s">
-        <v>293</v>
-      </c>
-      <c r="T3" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="U3" t="s">
-        <v>297</v>
-      </c>
-      <c r="V3" s="95" t="s">
-        <v>301</v>
-      </c>
-      <c r="W3" s="95" t="s">
-        <v>308</v>
-      </c>
-      <c r="X3" s="95" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y3" s="95" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z3" s="95" t="s">
+      <c r="Z10" s="95" t="s">
         <v>316</v>
       </c>
-      <c r="AA3" s="95" t="s">
-        <v>325</v>
-      </c>
-      <c r="AB3" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="AC3" s="95" t="s">
-        <v>336</v>
-      </c>
-      <c r="AD3" s="95" t="s">
+      <c r="AD10" s="95" t="s">
         <v>341</v>
       </c>
-      <c r="AE3" s="95" t="s">
-        <v>354</v>
-      </c>
-      <c r="AF3" s="95" t="s">
-        <v>362</v>
-      </c>
-      <c r="AG3" s="95" t="s">
-        <v>365</v>
-      </c>
-      <c r="AH3" s="95" t="s">
-        <v>373</v>
-      </c>
-      <c r="AI3" s="95" t="s">
+      <c r="AE10" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AG10" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AI10" s="95" t="s">
         <v>378</v>
       </c>
-      <c r="AJ3" s="95" t="s">
-        <v>394</v>
-      </c>
-      <c r="AK3" s="95" t="s">
-        <v>398</v>
-      </c>
-      <c r="AL3" s="95" t="s">
+      <c r="AL10" s="95" t="s">
         <v>402</v>
       </c>
-      <c r="AM3" s="95" t="s">
-        <v>411</v>
-      </c>
-      <c r="AN3" s="95" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A4" s="95" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="95" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="95" t="s">
-        <v>205</v>
-      </c>
-      <c r="F4" s="95" t="s">
-        <v>209</v>
-      </c>
-      <c r="G4" s="95" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="I4" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="K4" s="95" t="s">
-        <v>229</v>
-      </c>
-      <c r="L4" s="95" t="s">
-        <v>233</v>
-      </c>
-      <c r="M4" s="95" t="s">
+    </row>
+    <row r="11" spans="1:41">
+      <c r="M11" s="95" t="s">
         <v>240</v>
       </c>
-      <c r="N4" s="95" t="s">
-        <v>259</v>
-      </c>
-      <c r="O4" s="95" t="s">
-        <v>267</v>
-      </c>
-      <c r="P4" s="95" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q4" s="95" t="s">
-        <v>280</v>
-      </c>
-      <c r="R4" s="95" t="s">
-        <v>285</v>
-      </c>
-      <c r="S4" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="U4" t="s">
-        <v>298</v>
-      </c>
-      <c r="V4" t="s">
-        <v>302</v>
-      </c>
-      <c r="W4" t="s">
-        <v>537</v>
-      </c>
-      <c r="X4" s="95" t="s">
-        <v>311</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>537</v>
-      </c>
-      <c r="Z4" s="95" t="s">
-        <v>317</v>
-      </c>
-      <c r="AA4" s="95" t="s">
-        <v>326</v>
-      </c>
-      <c r="AB4" s="95" t="s">
-        <v>330</v>
-      </c>
-      <c r="AC4" s="95" t="s">
-        <v>337</v>
-      </c>
-      <c r="AD4" s="95" t="s">
+      <c r="R11" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z11" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AD11" s="95" t="s">
         <v>342</v>
       </c>
-      <c r="AE4" s="95" t="s">
-        <v>355</v>
-      </c>
-      <c r="AF4" s="95" t="s">
-        <v>363</v>
-      </c>
-      <c r="AG4" s="95" t="s">
-        <v>366</v>
-      </c>
-      <c r="AH4" s="95" t="s">
-        <v>374</v>
-      </c>
-      <c r="AI4" s="95" t="s">
+      <c r="AI11" s="95" t="s">
         <v>379</v>
       </c>
-      <c r="AJ4" s="95" t="s">
-        <v>395</v>
-      </c>
-      <c r="AK4" s="95" t="s">
-        <v>399</v>
-      </c>
-      <c r="AL4" s="95" t="s">
-        <v>403</v>
-      </c>
-      <c r="AM4" s="95" t="s">
-        <v>412</v>
-      </c>
-      <c r="AN4" s="95" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A5" s="95" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="95" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="95" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>199</v>
-      </c>
-      <c r="E5" s="95" t="s">
-        <v>206</v>
-      </c>
-      <c r="F5" s="95" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5" s="95" t="s">
-        <v>214</v>
-      </c>
-      <c r="H5" s="95" t="s">
-        <v>222</v>
-      </c>
-      <c r="K5" s="95" t="s">
-        <v>230</v>
-      </c>
-      <c r="L5" s="95" t="s">
-        <v>234</v>
-      </c>
-      <c r="M5" s="95" t="s">
+      <c r="AL11" s="116" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="M12" s="95" t="s">
         <v>241</v>
       </c>
-      <c r="N5" s="95" t="s">
-        <v>260</v>
-      </c>
-      <c r="O5" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="P5" s="95" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q5" s="95" t="s">
-        <v>281</v>
-      </c>
-      <c r="R5" s="95" t="s">
-        <v>286</v>
-      </c>
-      <c r="S5" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="U5" t="s">
-        <v>299</v>
-      </c>
-      <c r="V5" t="s">
-        <v>303</v>
-      </c>
-      <c r="X5" s="95" t="s">
-        <v>312</v>
-      </c>
-      <c r="Z5" s="95" t="s">
-        <v>318</v>
-      </c>
-      <c r="AA5" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="AB5" s="95" t="s">
-        <v>331</v>
-      </c>
-      <c r="AC5" s="95" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD5" s="95" t="s">
+      <c r="AD12" s="95" t="s">
         <v>343</v>
       </c>
-      <c r="AE5" s="95" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF5" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AG5" s="95" t="s">
-        <v>367</v>
-      </c>
-      <c r="AH5" s="95" t="s">
-        <v>375</v>
-      </c>
-      <c r="AI5" s="95" t="s">
+      <c r="AI12" s="95" t="s">
         <v>380</v>
       </c>
-      <c r="AJ5" s="95" t="s">
-        <v>396</v>
-      </c>
-      <c r="AK5" s="95" t="s">
-        <v>400</v>
-      </c>
-      <c r="AL5" s="95" t="s">
-        <v>404</v>
-      </c>
-      <c r="AM5" s="95" t="s">
-        <v>413</v>
-      </c>
-      <c r="AN5" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A6" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>194</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="F6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="G6" s="95" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="95" t="s">
-        <v>223</v>
-      </c>
-      <c r="K6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="L6" s="95" t="s">
-        <v>235</v>
-      </c>
-      <c r="M6" s="95" t="s">
+    </row>
+    <row r="13" spans="1:41">
+      <c r="M13" s="95" t="s">
         <v>242</v>
       </c>
-      <c r="N6" s="95" t="s">
-        <v>261</v>
-      </c>
-      <c r="O6" s="95" t="s">
-        <v>269</v>
-      </c>
-      <c r="P6" s="95" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q6" s="95" t="s">
-        <v>282</v>
-      </c>
-      <c r="R6" s="95" t="s">
-        <v>287</v>
-      </c>
-      <c r="U6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="V6" t="s">
-        <v>304</v>
-      </c>
-      <c r="X6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="Z6" s="95" t="s">
-        <v>319</v>
-      </c>
-      <c r="AA6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AB6" s="95" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC6" s="95" t="s">
-        <v>339</v>
-      </c>
-      <c r="AD6" s="95" t="s">
+      <c r="AD13" s="95" t="s">
         <v>344</v>
       </c>
-      <c r="AE6" s="95" t="s">
-        <v>357</v>
-      </c>
-      <c r="AG6" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="AH6" s="95" t="s">
-        <v>376</v>
-      </c>
-      <c r="AI6" s="95" t="s">
+      <c r="AI13" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="AJ6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AK6" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AL6" s="95" t="s">
-        <v>405</v>
-      </c>
-      <c r="AM6" s="95" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="A7" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>201</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>216</v>
-      </c>
-      <c r="H7" s="95" t="s">
-        <v>224</v>
-      </c>
-      <c r="L7" s="95" t="s">
-        <v>236</v>
-      </c>
-      <c r="M7" s="95" t="s">
+    </row>
+    <row r="14" spans="1:41">
+      <c r="M14" s="95" t="s">
         <v>243</v>
       </c>
-      <c r="N7" s="95" t="s">
-        <v>262</v>
-      </c>
-      <c r="O7" s="95" t="s">
-        <v>270</v>
-      </c>
-      <c r="P7" s="95" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q7" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="R7" s="95" t="s">
-        <v>288</v>
-      </c>
-      <c r="V7" s="95" t="s">
-        <v>305</v>
-      </c>
-      <c r="Z7" s="95" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB7" s="95" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC7" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AD7" s="95" t="s">
+      <c r="AD14" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="AE7" s="95" t="s">
-        <v>358</v>
-      </c>
-      <c r="AG7" s="95" t="s">
-        <v>369</v>
-      </c>
-      <c r="AH7" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AI7" s="95" t="s">
+      <c r="AI14" s="95" t="s">
         <v>382</v>
       </c>
-      <c r="AL7" s="95" t="s">
-        <v>406</v>
-      </c>
-      <c r="AM7" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="B8" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="C8" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="H8" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="L8" s="95" t="s">
-        <v>237</v>
-      </c>
-      <c r="M8" s="95" t="s">
+    </row>
+    <row r="15" spans="1:41">
+      <c r="M15" s="95" t="s">
         <v>244</v>
       </c>
-      <c r="N8" s="95" t="s">
-        <v>263</v>
-      </c>
-      <c r="O8" s="95" t="s">
-        <v>271</v>
-      </c>
-      <c r="P8" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="R8" s="95" t="s">
-        <v>289</v>
-      </c>
-      <c r="V8" s="95" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z8" s="95" t="s">
-        <v>321</v>
-      </c>
-      <c r="AB8" s="95" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD8" s="95" t="s">
-        <v>346</v>
-      </c>
-      <c r="AE8" s="95" t="s">
-        <v>359</v>
-      </c>
-      <c r="AG8" s="95" t="s">
-        <v>370</v>
-      </c>
-      <c r="AI8" s="95" t="s">
+      <c r="AD15" s="116" t="s">
+        <v>527</v>
+      </c>
+      <c r="AI15" s="95" t="s">
         <v>383</v>
       </c>
-      <c r="AL8" s="95" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="D9" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="G9" s="95" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="M9" s="95" t="s">
+    </row>
+    <row r="16" spans="1:41">
+      <c r="M16" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="N9" s="95" t="s">
-        <v>264</v>
-      </c>
-      <c r="O9" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="R9" s="95" t="s">
-        <v>290</v>
-      </c>
-      <c r="V9" t="s">
-        <v>537</v>
-      </c>
-      <c r="Z9" s="95" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB9" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AD9" s="95" t="s">
-        <v>347</v>
-      </c>
-      <c r="AE9" s="95" t="s">
-        <v>360</v>
-      </c>
-      <c r="AG9" s="95" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI9" s="95" t="s">
+      <c r="AI16" s="95" t="s">
         <v>384</v>
       </c>
-      <c r="AL9" s="95" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="G10" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="M10" s="95" t="s">
+    </row>
+    <row r="17" spans="13:35">
+      <c r="M17" s="95" t="s">
         <v>246</v>
       </c>
-      <c r="N10" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="R10" s="95" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z10" s="95" t="s">
-        <v>323</v>
-      </c>
-      <c r="AD10" s="95" t="s">
-        <v>348</v>
-      </c>
-      <c r="AE10" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AG10" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AI10" s="95" t="s">
+      <c r="AI17" s="95" t="s">
         <v>385</v>
       </c>
-      <c r="AL10" s="95" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M11" s="95" t="s">
+    </row>
+    <row r="18" spans="13:35">
+      <c r="M18" s="95" t="s">
         <v>247</v>
       </c>
-      <c r="R11" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="Z11" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AD11" s="95" t="s">
-        <v>349</v>
-      </c>
-      <c r="AI11" s="95" t="s">
-        <v>386</v>
-      </c>
-      <c r="AL11" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M12" s="95" t="s">
+      <c r="AI18" s="116" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="19" spans="13:35">
+      <c r="M19" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="AD12" s="95" t="s">
-        <v>350</v>
-      </c>
-      <c r="AI12" s="95" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M13" s="95" t="s">
+    </row>
+    <row r="20" spans="13:35">
+      <c r="M20" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="AD13" s="95" t="s">
-        <v>351</v>
-      </c>
-      <c r="AI13" s="95" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M14" s="95" t="s">
-        <v>250</v>
-      </c>
-      <c r="AD14" s="95" t="s">
-        <v>352</v>
-      </c>
-      <c r="AI14" s="95" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M15" s="95" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD15" s="116" t="s">
-        <v>537</v>
-      </c>
-      <c r="AI15" s="95" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
-      <c r="M16" s="95" t="s">
-        <v>252</v>
-      </c>
-      <c r="AI16" s="95" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="17" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M17" s="95" t="s">
-        <v>253</v>
-      </c>
-      <c r="AI17" s="95" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="18" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M18" s="95" t="s">
-        <v>254</v>
-      </c>
-      <c r="AI18" s="116" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="19" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M19" s="95" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="13:35" x14ac:dyDescent="0.15">
-      <c r="M20" s="95" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="21" spans="13:35" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="13:35">
       <c r="M21" s="116" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/assetImport/APM_Asset_TieFaces_Template.xlsx
@@ -113,7 +113,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>tie:each(items="assetList", var="asset")</t>
+          <t>tie:each(items="assetList", var="asset", length="1" allowAdd="False")</t>
         </r>
       </text>
     </comment>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="548">
   <si>
     <t>设备列表</t>
   </si>
@@ -518,6 +518,24 @@
       <t>设备型号</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>XXXX</t>
+  </si>
+  <si>
+    <t>XXX医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>XX医疗设备有限公司</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>平均年限</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -810,6 +828,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>放射科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>眼科手术用其他器械</t>
   </si>
   <si>
@@ -1941,6 +1963,12 @@
   </si>
   <si>
     <t>非计量设备</t>
+  </si>
+  <si>
+    <t>急救设备</t>
+  </si>
+  <si>
+    <t>二级</t>
   </si>
   <si>
     <t>医用CT</t>
@@ -2321,6 +2349,10 @@
   </si>
   <si>
     <t>设备分类</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -4946,7 +4978,7 @@
     <col min="53" max="53" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="27" customHeight="1">
+    <row r="1" spans="1:53" ht="27">
       <c r="A1" s="24" t="s">
         <v>43</v>
       </c>
@@ -4955,7 +4987,7 @@
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="123" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E1" s="124"/>
       <c r="F1" s="124"/>
@@ -4974,7 +5006,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="D2" s="124"/>
       <c r="E2" s="124"/>
@@ -5057,8 +5089,14 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:53" ht="21">
-      <c r="A5" s="120"/>
-      <c r="B5" s="121"/>
+      <c r="A5" s="120">
+        <f>COUNTA('Asset List'!$B$7:$B$100)</f>
+        <v>1</v>
+      </c>
+      <c r="B5" s="121">
+        <f>SUM('Asset List'!$Y$7:$Y$100)</f>
+        <v>0</v>
+      </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -5078,43 +5116,43 @@
         <v>111</v>
       </c>
       <c r="E6" s="118" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="K6" s="31" t="s">
         <v>112</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="M6" s="30" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="N6" s="93" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="O6" s="93" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>36</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="R6" s="30" t="s">
         <v>113</v>
@@ -5126,7 +5164,7 @@
         <v>86</v>
       </c>
       <c r="U6" s="30" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>38</v>
@@ -5150,7 +5188,7 @@
         <v>21</v>
       </c>
       <c r="AC6" s="30" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>23</v>
@@ -5159,10 +5197,10 @@
         <v>24</v>
       </c>
       <c r="AF6" s="93" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="AG6" s="93" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="AH6" s="30" t="s">
         <v>26</v>
@@ -5186,77 +5224,105 @@
         <v>32</v>
       </c>
       <c r="AO6" s="32" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="AP6" s="32" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="AQ6" s="32" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="AR6" s="32" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="AS6" s="32" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="AT6" s="32" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="AU6" s="32" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="AV6" s="32" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="AW6" s="32" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="AX6" s="109" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="AY6" s="32" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="AZ6" s="32" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="BA6" s="109" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:53" ht="15.75">
       <c r="A7" s="35" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>537</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="34"/>
+        <v>547</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="110" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="34"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="37"/>
+      <c r="G7" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>115</v>
+      </c>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
       <c r="K7" s="16"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
+      <c r="L7" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>426</v>
+      </c>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
+      <c r="R7" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S7" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
       <c r="V7" s="28"/>
       <c r="W7" s="17"/>
       <c r="X7" s="17"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="36"/>
+      <c r="Y7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="AB7" s="19"/>
       <c r="AC7" s="20"/>
       <c r="AD7" s="21"/>
@@ -5275,14 +5341,30 @@
       <c r="AQ7" s="114"/>
       <c r="AR7" s="114"/>
       <c r="AS7" s="114"/>
-      <c r="AT7" s="23"/>
-      <c r="AU7" s="23"/>
-      <c r="AV7" s="23"/>
-      <c r="AW7" s="23"/>
-      <c r="AX7" s="23"/>
-      <c r="AY7" s="23"/>
-      <c r="AZ7" s="23"/>
-      <c r="BA7" s="23"/>
+      <c r="AT7" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="AU7" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="AV7" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="AW7" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="AX7" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="AY7" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="AZ7" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="BA7" s="23" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="8" spans="1:53" s="105" customFormat="1" ht="15.75">
       <c r="A8" s="35"/>
@@ -10400,6 +10482,9 @@
       <c r="BA100" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:L2"/>
+  </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="D1 E4:F6 P7:R7">
     <cfRule type="expression" dxfId="107" priority="79">
@@ -11110,7 +11195,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="119" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -11545,7 +11630,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1">
       <c r="A1" s="125" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -11553,16 +11638,16 @@
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="58" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
@@ -11570,11 +11655,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="63" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" thickBot="1">
@@ -11582,11 +11667,11 @@
         <v>2</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C4" s="66"/>
       <c r="D4" s="67" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
@@ -11597,7 +11682,7 @@
     </row>
     <row r="6" spans="1:4" s="71" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="126" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B6" s="127"/>
       <c r="C6" s="127"/>
@@ -11605,16 +11690,16 @@
     </row>
     <row r="7" spans="1:4" s="71" customFormat="1" ht="17.25" thickBot="1">
       <c r="A7" s="72" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
@@ -11622,7 +11707,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C8" s="76"/>
       <c r="D8" s="77"/>
@@ -11632,7 +11717,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C9" s="78"/>
       <c r="D9" s="79"/>
@@ -11642,7 +11727,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C10" s="78"/>
       <c r="D10" s="79"/>
@@ -11652,7 +11737,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C11" s="78"/>
       <c r="D11" s="79"/>
@@ -11662,7 +11747,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C12" s="78"/>
       <c r="D12" s="79"/>
@@ -11672,7 +11757,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C13" s="78"/>
       <c r="D13" s="79"/>
@@ -11682,7 +11767,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="79"/>
@@ -11692,7 +11777,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="79"/>
@@ -11702,11 +11787,11 @@
         <v>11</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="79" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5">
@@ -11714,7 +11799,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="79"/>
@@ -11724,7 +11809,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C18" s="78"/>
       <c r="D18" s="79"/>
@@ -11734,7 +11819,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C19" s="78"/>
       <c r="D19" s="79"/>
@@ -11744,7 +11829,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="79"/>
@@ -11754,7 +11839,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C21" s="80"/>
       <c r="D21" s="81"/>
@@ -11764,7 +11849,7 @@
     </row>
     <row r="23" spans="1:4" ht="16.5" thickBot="1">
       <c r="A23" s="129" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B23" s="130"/>
       <c r="C23" s="130"/>
@@ -11772,16 +11857,16 @@
     </row>
     <row r="24" spans="1:4" ht="17.25" thickBot="1">
       <c r="A24" s="83" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B24" s="84" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C24" s="84" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D24" s="84" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16.5" thickBot="1">
@@ -11789,11 +11874,11 @@
         <v>17</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C25" s="86"/>
       <c r="D25" s="87" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.5" thickBot="1">
@@ -11801,11 +11886,11 @@
         <v>18</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="63" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11813,11 +11898,11 @@
         <v>19</v>
       </c>
       <c r="B27" s="85" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C27" s="88"/>
       <c r="D27" s="89" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" thickBot="1">
@@ -11825,11 +11910,11 @@
         <v>20</v>
       </c>
       <c r="B28" s="90" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C28" s="91"/>
       <c r="D28" s="92" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -11864,23 +11949,23 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="132" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B1" s="132" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C1" s="132"/>
       <c r="D1" s="132" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
       <c r="B2" s="38" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D2" s="132"/>
     </row>
@@ -11890,7 +11975,7 @@
       </c>
       <c r="B3" s="40"/>
       <c r="C3" s="40" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D3" s="41"/>
     </row>
@@ -11899,10 +11984,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D4" s="41"/>
     </row>
@@ -11916,19 +12001,19 @@
     </row>
     <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="45" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="43" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="46"/>
@@ -11936,11 +12021,11 @@
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="45" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D8" s="41"/>
     </row>
@@ -11950,19 +12035,19 @@
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="45" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -11980,7 +12065,7 @@
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D12" s="41"/>
     </row>
@@ -11989,10 +12074,10 @@
         <v>35</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D13" s="41"/>
     </row>
@@ -12006,11 +12091,11 @@
     </row>
     <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="45" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B15" s="47"/>
       <c r="C15" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D15" s="41"/>
     </row>
@@ -12024,11 +12109,11 @@
     </row>
     <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="45" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D17" s="41"/>
     </row>
@@ -12038,7 +12123,7 @@
       </c>
       <c r="B18" s="47"/>
       <c r="C18" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D18" s="41"/>
     </row>
@@ -12056,7 +12141,7 @@
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D20" s="41"/>
     </row>
@@ -12066,7 +12151,7 @@
       </c>
       <c r="B21" s="47"/>
       <c r="C21" s="47" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D21" s="41"/>
     </row>
@@ -12124,7 +12209,7 @@
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D28" s="41"/>
     </row>
@@ -12134,7 +12219,7 @@
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D29" s="41"/>
     </row>
@@ -12188,44 +12273,44 @@
     </row>
     <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="50" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B36" s="51"/>
       <c r="C36" s="51" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D36" s="41"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="52" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="53"/>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="55"/>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="56"/>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -12270,472 +12355,472 @@
   <sheetData>
     <row r="1" spans="1:13" s="27" customFormat="1">
       <c r="A1" s="96" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D1" s="96" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F1" s="96" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="I1" s="100" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="J1" s="102" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="K1" s="104" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="M1" s="122" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="95" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B2" s="107" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C2" s="95" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="D2" s="95" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E2" s="98" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="G2" s="97" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="H2" s="95" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="I2" s="99" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="J2" s="101" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="K2" s="103" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="L2" s="107" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="M2" s="116" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.25" customHeight="1">
       <c r="A3" s="95" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B3" s="107" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C3" s="95" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D3" s="95" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E3" s="98" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F3" s="107" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G3" s="97" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="H3" s="95" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="I3" s="99" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K3" s="103" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="L3" s="107" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="M3" s="116" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="95" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B4" s="107" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E4" s="98" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="F4" s="107" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G4" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="H4" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="I4" s="99" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="J4" s="101" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="K4" s="103" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="L4" s="107" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="M4" s="116" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="95" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B5" s="107" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C5" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="D5" s="95" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="E5" s="98" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="F5" s="107" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="I5" s="99" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="J5" s="101" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="K5" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="L5" s="107" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="M5" s="116" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="116" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="B6" s="116" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="D6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="E6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="I6" s="99" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="J6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="L6" s="107" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="M6" s="116" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="116" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B7" s="116" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="I7" s="99" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="L7" s="107" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="M7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="116" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B8" s="116" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="I8" s="99" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="L8" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="95" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B9" s="107" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="I9" s="99" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="95" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B10" s="107" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="I10" s="99" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="117" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="B11" s="117" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="H11" s="107"/>
       <c r="I11" s="99" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="117" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="H12" s="107"/>
       <c r="I12" s="99" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="117" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="H13" s="107"/>
       <c r="I13" s="99" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="95" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="H14" s="107"/>
       <c r="I14" s="99" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="B15" s="116"/>
       <c r="H15" s="107"/>
       <c r="I15" s="99" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="B16" s="107"/>
       <c r="H16" s="107"/>
       <c r="I16" s="99" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="107"/>
       <c r="H17" s="107"/>
       <c r="I17" s="99" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="107"/>
       <c r="H18" s="107"/>
       <c r="I18" s="99" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="107"/>
       <c r="H19" s="107"/>
       <c r="I19" s="99" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="107"/>
       <c r="H20" s="107"/>
       <c r="I20" s="99" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="107"/>
       <c r="H21" s="107"/>
       <c r="I21" s="99" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="107"/>
       <c r="H22" s="107"/>
       <c r="I22" s="99" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="107"/>
       <c r="H23" s="107"/>
       <c r="I23" s="99" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="107"/>
       <c r="H24" s="107"/>
       <c r="I24" s="99" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="107"/>
       <c r="H25" s="107"/>
       <c r="I25" s="99" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" spans="2:9">
       <c r="H26" s="107"/>
       <c r="I26" s="99" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="H27" s="107"/>
       <c r="I27" s="99" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="2:9">
       <c r="H28" s="107"/>
       <c r="I28" s="99" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="2:9">
       <c r="H29" s="107"/>
       <c r="I29" s="99" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="2:9">
       <c r="H30" s="107"/>
       <c r="I30" s="99" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="2:9">
       <c r="H31" s="107"/>
       <c r="I31" s="99" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="2:9">
       <c r="H32" s="107"/>
       <c r="I32" s="99" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="H33" s="107"/>
       <c r="I33" s="99" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34" spans="8:9">
       <c r="H34" s="107"/>
       <c r="I34" s="115" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="35" spans="8:9">
       <c r="I35" s="115" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" spans="8:9">
       <c r="I36" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -12928,10 +13013,10 @@
   <sheetData>
     <row r="1" spans="1:41">
       <c r="A1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s">
         <v>46</v>
@@ -12946,7 +13031,7 @@
         <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="H1" t="s">
         <v>50</v>
@@ -12961,7 +13046,7 @@
         <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="M1" t="s">
         <v>54</v>
@@ -12994,7 +13079,7 @@
         <v>63</v>
       </c>
       <c r="W1" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="X1" t="s">
         <v>64</v>
@@ -13048,884 +13133,884 @@
         <v>80</v>
       </c>
       <c r="AO1" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:41">
       <c r="A2" s="95" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B2" s="95" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C2" s="95" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D2" s="95" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E2" s="95" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F2" s="95" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G2" s="95" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H2" s="95" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="I2" s="95" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J2" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="K2" s="95" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="L2" s="95" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="M2" s="95" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="N2" s="95" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O2" s="95" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="P2" s="95" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="Q2" s="95" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="R2" s="95" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="S2" s="95" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="T2" s="95" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="U2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="V2" s="95" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="W2" s="95" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="X2" s="95" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Y2" s="95" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="Z2" s="95" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="AA2" s="95" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AB2" s="95" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AC2" s="95" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AD2" s="95" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AE2" s="95" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AF2" s="95" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AG2" s="95" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="AH2" s="95" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AI2" s="95" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AJ2" s="95" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AK2" s="95" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AL2" s="95" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AM2" s="95" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AN2" s="95" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:41">
       <c r="A3" s="95" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B3" s="95" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C3" s="95" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D3" s="95" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E3" s="95" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F3" s="95" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G3" s="95" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H3" s="95" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I3" s="95" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="K3" s="95" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="L3" s="95" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="M3" s="95" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="N3" s="95" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="O3" s="95" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="P3" s="95" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Q3" s="95" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="R3" s="95" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="S3" s="95" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="T3" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="U3" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="V3" s="95" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="W3" s="95" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="X3" s="95" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="Y3" s="95" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="Z3" s="95" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AA3" s="95" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AB3" s="95" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="AC3" s="95" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AD3" s="95" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AE3" s="95" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AF3" s="95" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AG3" s="95" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AH3" s="95" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AI3" s="95" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AJ3" s="95" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="AK3" s="95" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AL3" s="95" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AM3" s="95" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AN3" s="95" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" s="95" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B4" s="95" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E4" s="95" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F4" s="95" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G4" s="95" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H4" s="95" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="I4" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="K4" s="95" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L4" s="95" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M4" s="95" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N4" s="95" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="O4" s="95" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="P4" s="95" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="Q4" s="95" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="R4" s="95" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="S4" s="95" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="U4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="V4" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="W4" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="X4" s="95" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="Y4" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="Z4" s="95" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AA4" s="95" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AB4" s="95" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AC4" s="95" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AD4" s="95" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AE4" s="95" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AF4" s="95" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AG4" s="95" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AH4" s="95" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AI4" s="95" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AJ4" s="95" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AK4" s="95" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AL4" s="95" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AM4" s="95" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN4" s="95" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:41">
       <c r="A5" s="95" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B5" s="95" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C5" s="95" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D5" s="95" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E5" s="95" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F5" s="95" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G5" s="95" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H5" s="95" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K5" s="95" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="L5" s="95" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M5" s="95" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="N5" s="95" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="O5" s="95" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="P5" s="95" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="Q5" s="95" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="R5" s="95" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="S5" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="U5" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="V5" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="X5" s="95" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Z5" s="95" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AA5" s="95" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AB5" s="95" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AC5" s="95" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AE5" s="95" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AF5" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AG5" s="95" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="AH5" s="95" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="AI5" s="95" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AJ5" s="95" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AK5" s="95" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AL5" s="95" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AM5" s="95" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AN5" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:41">
       <c r="A6" s="95" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B6" s="95" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C6" s="95" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D6" s="95" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="G6" s="95" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H6" s="95" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="K6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="L6" s="95" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="M6" s="95" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N6" s="95" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="O6" s="95" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P6" s="95" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="Q6" s="95" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="R6" s="95" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="U6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="V6" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="X6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="Z6" s="95" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AA6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AB6" s="95" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AC6" s="95" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AE6" s="95" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG6" s="95" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AH6" s="95" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AI6" s="95" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AJ6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AK6" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AL6" s="95" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AM6" s="95" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C7" s="95" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D7" s="95" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H7" s="95" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="L7" s="95" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="M7" s="95" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N7" s="95" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O7" s="95" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="P7" s="95" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="Q7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="R7" s="95" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="V7" s="95" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="Z7" s="95" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="AB7" s="95" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AC7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AD7" s="95" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AE7" s="95" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AG7" s="95" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AH7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AI7" s="95" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AL7" s="95" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AM7" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:41">
       <c r="B8" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="C8" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="D8" s="95" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G8" s="95" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H8" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="L8" s="95" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="M8" s="95" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N8" s="95" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="O8" s="95" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="P8" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="R8" s="95" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="V8" s="95" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="Z8" s="95" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AB8" s="95" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AD8" s="95" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AE8" s="95" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AG8" s="95" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AI8" s="95" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AL8" s="95" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:41">
       <c r="D9" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="G9" s="95" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="L9" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="M9" s="95" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N9" s="95" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="O9" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="R9" s="95" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="V9" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="Z9" s="95" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AB9" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AD9" s="95" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AE9" s="95" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AG9" s="95" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AI9" s="95" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AL9" s="95" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:41">
       <c r="G10" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="M10" s="95" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="N10" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="R10" s="95" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="Z10" s="95" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AD10" s="95" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AE10" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AG10" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AI10" s="95" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AL10" s="95" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:41">
       <c r="M11" s="95" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="R11" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="Z11" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AD11" s="95" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AI11" s="95" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AL11" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" spans="1:41">
       <c r="M12" s="95" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AD12" s="95" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AI12" s="95" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:41">
       <c r="M13" s="95" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AD13" s="95" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AI13" s="95" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:41">
       <c r="M14" s="95" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AD14" s="95" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AI14" s="95" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:41">
       <c r="M15" s="95" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AD15" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="AI15" s="95" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:41">
       <c r="M16" s="95" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AI16" s="95" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="13:35">
       <c r="M17" s="95" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AI17" s="95" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="13:35">
       <c r="M18" s="95" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AI18" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="13:35">
       <c r="M19" s="95" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="13:35">
       <c r="M20" s="95" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="13:35">
       <c r="M21" s="116" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
